--- a/Modeling/Lab1/УИР_1_вариант_16_расчеты.xlsx
+++ b/Modeling/Lab1/УИР_1_вариант_16_расчеты.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итоги" sheetId="1" r:id="Rf9da28b8192d4345"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статистика" sheetId="2" r:id="Rf83da5268dba4d3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Распределение" sheetId="3" r:id="Re7c6550299604062"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Автокорреляция" sheetId="4" r:id="R9bb061b960824592"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Генератор" sheetId="5" r:id="R17bed049ba7e4a9a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Исходные данные" sheetId="6" r:id="Rf20f2aa0264f4ef0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Итоги" sheetId="1" r:id="Rdd3f3782bbd6424f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Статистика" sheetId="2" r:id="R3ef6fa7b18084123"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Распределение" sheetId="3" r:id="R51971bcea4524a91"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Автокорреляция" sheetId="4" r:id="R3694c69a07764a87"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Генератор" sheetId="5" r:id="Rb93c0cec394548d8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Исходные данные" sheetId="6" r:id="Rcf258419fb8248e1"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -25,7 +25,7 @@
     <x:numFmt numFmtId="203" formatCode="0.000"/>
     <x:numFmt numFmtId="204" formatCode="0.00"/>
   </x:numFmts>
-  <x:fonts count="6">
+  <x:fonts count="7">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -56,6 +56,10 @@
       <x:b/>
       <x:sz val="11"/>
       <x:color rgb="FF000000"/>
+      <x:name val="Arial"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
       <x:name val="Arial"/>
     </x:font>
   </x:fonts>
@@ -99,7 +103,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="27">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -164,6 +168,12 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="201" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -1057,7 +1067,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re150423f33b3406d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rc558f06be482421d"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1087,7 +1097,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R8e24034e2a2b492a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R0453fa4f3d914992"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1122,7 +1132,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R1dbfefa548e244c1"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rd3d1cfd0c04847ca"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1157,7 +1167,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R011b1e9b497a407a"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="R6e9aa089038642ca"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1192,7 +1202,7 @@
       </xdr:xfrm>
       <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Re55bc367e89d4e2d"/>
+          <c:chart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" r:id="Rcfaec6701f7e4f2e"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -1579,7 +1589,7 @@
       </x:c>
       <x:c r="E11" s="23" t="n">
         <x:f>'Автокорреляция'!B17</x:f>
-        <x:v>-0.03611636453935302</x:v>
+        <x:v>-0.036073946962238944</x:v>
       </x:c>
       <x:c r="F11" s="13"/>
       <x:c r="G11" s="13"/>
@@ -1609,7 +1619,7 @@
     </x:row>
     <x:row r="14" ht="44" customHeight="1">
       <x:c r="A14" s="26" t="str">
-        <x:v>1. Последовательность не имеет выраженного тренда или периодичности. Проверка Льюнга–Бокса дает p=0.307, поэтому оснований отвергать случайность ряда нет.</x:v>
+        <x:v>1. Совместная проверка 10 лагов: Q=11,646; p=0,309. Значимая серийная корреляция не обнаружена.</x:v>
       </x:c>
       <x:c r="B14" s="13"/>
       <x:c r="C14" s="13"/>
@@ -1633,7 +1643,7 @@
     </x:row>
     <x:row r="16" ht="44" customHeight="1">
       <x:c r="A16" s="26" t="str">
-        <x:v>3. Для воспроизводимой контрольной реализации выбран seed 8141. При n=300 отклонения составляют 0.10 % по среднему и 0.09 % по дисперсии.</x:v>
+        <x:v>3. Seed 8141. При n=300 отклонения: среднее 0.0483%, дисперсия 0.7153%.</x:v>
       </x:c>
       <x:c r="B16" s="13"/>
       <x:c r="C16" s="13"/>
@@ -2238,19 +2248,19 @@
       </x:c>
       <x:c r="B14" s="11" t="n">
         <x:f>AVERAGE('Генератор'!$E$12:$E$311)</x:f>
-        <x:v>8.02887831120667</x:v>
+        <x:v>8.016905917620546</x:v>
       </x:c>
       <x:c r="C14" s="11" t="n">
         <x:f>_xlfn.VAR.S('Генератор'!$E$12:$E$311)</x:f>
-        <x:v>509.988541356982</x:v>
+        <x:v>506.7800127840016</x:v>
       </x:c>
       <x:c r="D14" s="11" t="n">
         <x:f>_xlfn.STDEV.S('Генератор'!$E$12:$E$311)</x:f>
-        <x:v>22.58292588122677</x:v>
+        <x:v>22.511774980751774</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
         <x:f>D14/B14</x:f>
-        <x:v>2.8127124370169656</x:v>
+        <x:v>2.8080378155957417</x:v>
       </x:c>
       <x:c r="F14" s="13"/>
       <x:c r="G14" s="13"/>
@@ -2313,19 +2323,19 @@
       </x:c>
       <x:c r="B17" s="18" t="n">
         <x:f>ABS(B14-B13)/B13</x:f>
-        <x:v>0.0010098578470674668</x:v>
+        <x:v>0.00048281442136223745</x:v>
       </x:c>
       <x:c r="C17" s="18" t="n">
         <x:f>ABS(C14-C13)/C13</x:f>
-        <x:v>0.0008667179227748183</x:v>
+        <x:v>0.007152638926471477</x:v>
       </x:c>
       <x:c r="D17" s="18" t="n">
         <x:f>ABS(D14-D13)/D13</x:f>
-        <x:v>0.00043345290209665125</x:v>
+        <x:v>0.0035827374671149343</x:v>
       </x:c>
       <x:c r="E17" s="18" t="n">
         <x:f>ABS(E14-E13)/E13</x:f>
-        <x:v>0.0014418546809001837</x:v>
+        <x:v>0.0031014204562756402</x:v>
       </x:c>
       <x:c r="F17" s="13"/>
       <x:c r="G17" s="13"/>
@@ -2427,59 +2437,59 @@
       </x:c>
       <x:c r="B21" s="11" t="n">
         <x:f>AVERAGE('Генератор'!$E$12:$E$21)</x:f>
-        <x:v>13.725176453729778</x:v>
+        <x:v>13.698271589862912</x:v>
       </x:c>
       <x:c r="C21" s="18" t="n">
         <x:f>ABS(B21-B5)/ABS(B5)</x:f>
-        <x:v>2.381982559430978</x:v>
+        <x:v>2.375353006749571</x:v>
       </x:c>
       <x:c r="D21" s="11" t="n">
         <x:f>_xlfn.VAR.S('Генератор'!$E$12:$E$21)</x:f>
-        <x:v>726.4950907793614</x:v>
+        <x:v>721.8828792748014</x:v>
       </x:c>
       <x:c r="E21" s="18" t="n">
         <x:f>ABS(D21-D5)/ABS(D5)</x:f>
-        <x:v>49.71110832924316</x:v>
+        <x:v>49.38916484990842</x:v>
       </x:c>
       <x:c r="F21" s="11" t="n">
         <x:f>_xlfn.STDEV.S('Генератор'!$E$12:$E$21)</x:f>
-        <x:v>26.953572875953967</x:v>
+        <x:v>26.867878205671573</x:v>
       </x:c>
       <x:c r="G21" s="18" t="n">
         <x:f>ABS(F21-F5)/ABS(F5)</x:f>
-        <x:v>6.121173241063804</x:v>
+        <x:v>6.09853258426757</x:v>
       </x:c>
       <x:c r="H21" s="11" t="n">
         <x:f>F21/B21</x:f>
-        <x:v>1.9638051989218257</x:v>
+        <x:v>1.9614064467486922</x:v>
       </x:c>
       <x:c r="I21" s="18" t="n">
         <x:f>ABS(H21-H5)/ABS(H5)</x:f>
-        <x:v>1.105620923799781</x:v>
+        <x:v>1.1030489463095834</x:v>
       </x:c>
       <x:c r="J21" s="11" t="n">
         <x:f>1.643*F21/SQRT(A21)</x:f>
-        <x:v>14.00405814865554</x:v>
+        <x:v>13.959534435558671</x:v>
       </x:c>
       <x:c r="K21" s="18" t="n">
         <x:f>ABS(J21-J5)/ABS(J5)</x:f>
-        <x:v>6.121173241063804</x:v>
+        <x:v>6.098532584267569</x:v>
       </x:c>
       <x:c r="L21" s="11" t="n">
         <x:f>1.96*F21/SQRT(A21)</x:f>
-        <x:v>16.70599754800052</x:v>
+        <x:v>16.652883441080338</x:v>
       </x:c>
       <x:c r="M21" s="18" t="n">
         <x:f>ABS(L21-L5)/ABS(L5)</x:f>
-        <x:v>6.121173241063803</x:v>
+        <x:v>6.098532584267569</x:v>
       </x:c>
       <x:c r="N21" s="11" t="n">
         <x:f>2.576*F21/SQRT(A21)</x:f>
-        <x:v>21.956453920229258</x:v>
+        <x:v>21.886646808277014</x:v>
       </x:c>
       <x:c r="O21" s="18" t="n">
         <x:f>ABS(N21-N5)/ABS(N5)</x:f>
-        <x:v>6.121173241063803</x:v>
+        <x:v>6.098532584267568</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2488,59 +2498,59 @@
       </x:c>
       <x:c r="B22" s="11" t="n">
         <x:f>AVERAGE('Генератор'!$E$12:$E$31)</x:f>
-        <x:v>18.105175909752887</x:v>
+        <x:v>18.066170310667182</x:v>
       </x:c>
       <x:c r="C22" s="18" t="n">
         <x:f>ABS(B22-B6)/ABS(B6)</x:f>
-        <x:v>1.2891952404181448</x:v>
+        <x:v>1.284263422455053</x:v>
       </x:c>
       <x:c r="D22" s="11" t="n">
         <x:f>_xlfn.VAR.S('Генератор'!$E$12:$E$31)</x:f>
-        <x:v>1577.3603599905991</x:v>
+        <x:v>1567.1920125957301</x:v>
       </x:c>
       <x:c r="E22" s="18" t="n">
         <x:f>ABS(D22-D6)/ABS(D6)</x:f>
-        <x:v>7.1756626123002984</x:v>
+        <x:v>7.122958753541222</x:v>
       </x:c>
       <x:c r="F22" s="11" t="n">
         <x:f>_xlfn.STDEV.S('Генератор'!$E$12:$E$31)</x:f>
-        <x:v>39.71599627342362</x:v>
+        <x:v>39.58777605013611</x:v>
       </x:c>
       <x:c r="G22" s="18" t="n">
         <x:f>ABS(F22-F6)/ABS(F6)</x:f>
-        <x:v>1.8593115626493553</x:v>
+        <x:v>1.850080481941031</x:v>
       </x:c>
       <x:c r="H22" s="11" t="n">
         <x:f>F22/B22</x:f>
-        <x:v>2.1936266441923618</x:v>
+        <x:v>2.1912655183351992</x:v>
       </x:c>
       <x:c r="I22" s="18" t="n">
         <x:f>ABS(H22-H6)/ABS(H6)</x:f>
-        <x:v>0.24904661348460275</x:v>
+        <x:v>0.24770219315505046</x:v>
       </x:c>
       <x:c r="J22" s="11" t="n">
         <x:f>1.643*F22/SQRT(A22)</x:f>
-        <x:v>14.591099763925031</x:v>
+        <x:v>14.543993452985205</x:v>
       </x:c>
       <x:c r="K22" s="18" t="n">
         <x:f>ABS(J22-J6)/ABS(J6)</x:f>
-        <x:v>1.8593115626493555</x:v>
+        <x:v>1.8500804819410308</x:v>
       </x:c>
       <x:c r="L22" s="11" t="n">
         <x:f>1.96*F22/SQRT(A22)</x:f>
-        <x:v>17.406302822454695</x:v>
+        <x:v>17.35010783192392</x:v>
       </x:c>
       <x:c r="M22" s="18" t="n">
         <x:f>ABS(L22-L6)/ABS(L6)</x:f>
-        <x:v>1.8593115626493553</x:v>
+        <x:v>1.850080481941031</x:v>
       </x:c>
       <x:c r="N22" s="11" t="n">
         <x:f>2.576*F22/SQRT(A22)</x:f>
-        <x:v>22.87685513808331</x:v>
+        <x:v>22.8029988648143</x:v>
       </x:c>
       <x:c r="O22" s="18" t="n">
         <x:f>ABS(N22-N6)/ABS(N6)</x:f>
-        <x:v>1.8593115626493553</x:v>
+        <x:v>1.8500804819410317</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2549,59 +2559,59 @@
       </x:c>
       <x:c r="B23" s="11" t="n">
         <x:f>AVERAGE('Генератор'!$E$12:$E$61)</x:f>
-        <x:v>11.625019427397012</x:v>
+        <x:v>11.605093952194471</x:v>
       </x:c>
       <x:c r="C23" s="18" t="n">
         <x:f>ABS(B23-B7)/ABS(B7)</x:f>
-        <x:v>0.6167252042379581</x:v>
+        <x:v>0.6139541105492502</x:v>
       </x:c>
       <x:c r="D23" s="11" t="n">
         <x:f>_xlfn.VAR.S('Генератор'!$E$12:$E$61)</x:f>
-        <x:v>700.5428721634003</x:v>
+        <x:v>696.1111097203584</x:v>
       </x:c>
       <x:c r="E23" s="18" t="n">
         <x:f>ABS(D23-D7)/ABS(D7)</x:f>
-        <x:v>4.175165131636919</x:v>
+        <x:v>4.142426089704909</x:v>
       </x:c>
       <x:c r="F23" s="11" t="n">
         <x:f>_xlfn.STDEV.S('Генератор'!$E$12:$E$61)</x:f>
-        <x:v>26.4677704418676</x:v>
+        <x:v>26.38391763405045</x:v>
       </x:c>
       <x:c r="G23" s="18" t="n">
         <x:f>ABS(F23-F7)/ABS(F7)</x:f>
-        <x:v>1.2748989277849065</x:v>
+        <x:v>1.2676917977769615</x:v>
       </x:c>
       <x:c r="H23" s="11" t="n">
         <x:f>F23/B23</x:f>
-        <x:v>2.2767936524467443</x:v>
+        <x:v>2.2734772973605586</x:v>
       </x:c>
       <x:c r="I23" s="18" t="n">
         <x:f>ABS(H23-H7)/ABS(H7)</x:f>
-        <x:v>0.40710302642753593</x:v>
+        <x:v>0.40505345409432714</x:v>
       </x:c>
       <x:c r="J23" s="11" t="n">
         <x:f>1.643*F23/SQRT(A23)</x:f>
-        <x:v>6.149926431622769</x:v>
+        <x:v>6.130442788287827</x:v>
       </x:c>
       <x:c r="K23" s="18" t="n">
         <x:f>ABS(J23-J7)/ABS(J7)</x:f>
-        <x:v>1.274898927784907</x:v>
+        <x:v>1.267691797776962</x:v>
       </x:c>
       <x:c r="L23" s="11" t="n">
         <x:f>1.96*F23/SQRT(A23)</x:f>
-        <x:v>7.336491665234709</x:v>
+        <x:v>7.3132488527353265</x:v>
       </x:c>
       <x:c r="M23" s="18" t="n">
         <x:f>ABS(L23-L7)/ABS(L7)</x:f>
-        <x:v>1.2748989277849063</x:v>
+        <x:v>1.2676917977769615</x:v>
       </x:c>
       <x:c r="N23" s="11" t="n">
         <x:f>2.576*F23/SQRT(A23)</x:f>
-        <x:v>9.642246188594191</x:v>
+        <x:v>9.611698492166429</x:v>
       </x:c>
       <x:c r="O23" s="18" t="n">
         <x:f>ABS(N23-N7)/ABS(N7)</x:f>
-        <x:v>1.274898927784907</x:v>
+        <x:v>1.2676917977769617</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2610,59 +2620,59 @@
       </x:c>
       <x:c r="B24" s="11" t="n">
         <x:f>AVERAGE('Генератор'!$E$12:$E$111)</x:f>
-        <x:v>9.800037180943997</x:v>
+        <x:v>9.781985852043267</x:v>
       </x:c>
       <x:c r="C24" s="18" t="n">
         <x:f>ABS(B24-B8)/ABS(B8)</x:f>
-        <x:v>0.26111543611953447</x:v>
+        <x:v>0.2587925051858185</x:v>
       </x:c>
       <x:c r="D24" s="11" t="n">
         <x:f>_xlfn.VAR.S('Генератор'!$E$12:$E$111)</x:f>
-        <x:v>570.4541924317468</x:v>
+        <x:v>566.8433393446313</x:v>
       </x:c>
       <x:c r="E24" s="18" t="n">
         <x:f>ABS(D24-D8)/ABS(D8)</x:f>
-        <x:v>0.34136255326481474</x:v>
+        <x:v>0.3328720150574425</x:v>
       </x:c>
       <x:c r="F24" s="11" t="n">
         <x:f>_xlfn.STDEV.S('Генератор'!$E$12:$E$111)</x:f>
-        <x:v>23.8841828922772</x:v>
+        <x:v>23.808472007767136</x:v>
       </x:c>
       <x:c r="G24" s="18" t="n">
         <x:f>ABS(F24-F8)/ABS(F8)</x:f>
-        <x:v>0.15817207411714715</x:v>
+        <x:v>0.15450076442479777</x:v>
       </x:c>
       <x:c r="H24" s="11" t="n">
         <x:f>F24/B24</x:f>
-        <x:v>2.437152273128063</x:v>
+        <x:v>2.4339098796379885</x:v>
       </x:c>
       <x:c r="I24" s="18" t="n">
         <x:f>ABS(H24-H8)/ABS(H8)</x:f>
-        <x:v>0.08162881767520445</x:v>
+        <x:v>0.08285062099700513</x:v>
       </x:c>
       <x:c r="J24" s="11" t="n">
         <x:f>1.643*F24/SQRT(A24)</x:f>
-        <x:v>3.9241712492011436</x:v>
+        <x:v>3.9117319508761406</x:v>
       </x:c>
       <x:c r="K24" s="18" t="n">
         <x:f>ABS(J24-J8)/ABS(J8)</x:f>
-        <x:v>0.15817207411714715</x:v>
+        <x:v>0.15450076442479782</x:v>
       </x:c>
       <x:c r="L24" s="11" t="n">
         <x:f>1.96*F24/SQRT(A24)</x:f>
-        <x:v>4.681299846886331</x:v>
+        <x:v>4.666460513522359</x:v>
       </x:c>
       <x:c r="M24" s="18" t="n">
         <x:f>ABS(L24-L8)/ABS(L8)</x:f>
-        <x:v>0.1581720741171471</x:v>
+        <x:v>0.15450076442479768</x:v>
       </x:c>
       <x:c r="N24" s="11" t="n">
         <x:f>2.576*F24/SQRT(A24)</x:f>
-        <x:v>6.1525655130506065</x:v>
+        <x:v>6.1330623892008145</x:v>
       </x:c>
       <x:c r="O24" s="18" t="n">
         <x:f>ABS(N24-N8)/ABS(N8)</x:f>
-        <x:v>0.15817207411714718</x:v>
+        <x:v>0.1545007644247978</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2671,59 +2681,59 @@
       </x:c>
       <x:c r="B25" s="11" t="n">
         <x:f>AVERAGE('Генератор'!$E$12:$E$211)</x:f>
-        <x:v>7.341494636024806</x:v>
+        <x:v>7.330654390757552</x:v>
       </x:c>
       <x:c r="C25" s="18" t="n">
         <x:f>ABS(B25-B9)/ABS(B9)</x:f>
-        <x:v>0.06914256354371134</x:v>
+        <x:v>0.06756389759228451</x:v>
       </x:c>
       <x:c r="D25" s="11" t="n">
         <x:f>_xlfn.VAR.S('Генератор'!$E$12:$E$211)</x:f>
-        <x:v>309.81589365078014</x:v>
+        <x:v>307.8747698556753</x:v>
       </x:c>
       <x:c r="E25" s="18" t="n">
         <x:f>ABS(D25-D9)/ABS(D9)</x:f>
-        <x:v>0.07802010344107603</x:v>
+        <x:v>0.07126586481976903</x:v>
       </x:c>
       <x:c r="F25" s="11" t="n">
         <x:f>_xlfn.STDEV.S('Генератор'!$E$12:$E$211)</x:f>
-        <x:v>17.601587816182384</x:v>
+        <x:v>17.54636058718945</x:v>
       </x:c>
       <x:c r="G25" s="18" t="n">
         <x:f>ABS(F25-F9)/ABS(F9)</x:f>
-        <x:v>0.038277469389120404</x:v>
+        <x:v>0.03501974127055609</x:v>
       </x:c>
       <x:c r="H25" s="11" t="n">
         <x:f>F25/B25</x:f>
-        <x:v>2.397548277132993</x:v>
+        <x:v>2.393559926834336</x:v>
       </x:c>
       <x:c r="I25" s="18" t="n">
         <x:f>ABS(H25-H9)/ABS(H9)</x:f>
-        <x:v>0.02886901635670322</x:v>
+        <x:v>0.030484504389036098</x:v>
       </x:c>
       <x:c r="J25" s="11" t="n">
         <x:f>1.643*F25/SQRT(A25)</x:f>
-        <x:v>2.0449110057649267</x:v>
+        <x:v>2.0384948364076534</x:v>
       </x:c>
       <x:c r="K25" s="18" t="n">
         <x:f>ABS(J25-J9)/ABS(J9)</x:f>
-        <x:v>0.03827746938912039</x:v>
+        <x:v>0.035019741270556216</x:v>
       </x:c>
       <x:c r="L25" s="11" t="n">
         <x:f>1.96*F25/SQRT(A25)</x:f>
-        <x:v>2.4394556124767233</x:v>
+        <x:v>2.431801509043822</x:v>
       </x:c>
       <x:c r="M25" s="18" t="n">
         <x:f>ABS(L25-L9)/ABS(L9)</x:f>
-        <x:v>0.03827746938912044</x:v>
+        <x:v>0.035019741270555925</x:v>
       </x:c>
       <x:c r="N25" s="11" t="n">
         <x:f>2.576*F25/SQRT(A25)</x:f>
-        <x:v>3.2061416621122647</x:v>
+        <x:v>3.196081983314738</x:v>
       </x:c>
       <x:c r="O25" s="18" t="n">
         <x:f>ABS(N25-N9)/ABS(N9)</x:f>
-        <x:v>0.038277469389120335</x:v>
+        <x:v>0.035019741270556105</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2732,59 +2742,59 @@
       </x:c>
       <x:c r="B26" s="11" t="n">
         <x:f>AVERAGE('Генератор'!$E$12:$E$311)</x:f>
-        <x:v>8.02887831120667</x:v>
+        <x:v>8.016905917620546</x:v>
       </x:c>
       <x:c r="C26" s="18" t="n">
         <x:f>ABS(B26-B10)/ABS(B10)</x:f>
-        <x:v>0.0010098578470674668</x:v>
+        <x:v>0.00048281442136223745</x:v>
       </x:c>
       <x:c r="D26" s="11" t="n">
         <x:f>_xlfn.VAR.S('Генератор'!$E$12:$E$311)</x:f>
-        <x:v>509.988541356982</x:v>
+        <x:v>506.7800127840016</x:v>
       </x:c>
       <x:c r="E26" s="18" t="n">
         <x:f>ABS(D26-D10)/ABS(D10)</x:f>
-        <x:v>0.0008667179227748183</x:v>
+        <x:v>0.007152638926471477</x:v>
       </x:c>
       <x:c r="F26" s="11" t="n">
         <x:f>_xlfn.STDEV.S('Генератор'!$E$12:$E$311)</x:f>
-        <x:v>22.58292588122677</x:v>
+        <x:v>22.511774980751774</x:v>
       </x:c>
       <x:c r="G26" s="18" t="n">
         <x:f>ABS(F26-F10)/ABS(F10)</x:f>
-        <x:v>0.00043345290209665125</x:v>
+        <x:v>0.0035827374671149343</x:v>
       </x:c>
       <x:c r="H26" s="11" t="n">
         <x:f>F26/B26</x:f>
-        <x:v>2.8127124370169656</x:v>
+        <x:v>2.8080378155957417</x:v>
       </x:c>
       <x:c r="I26" s="18" t="n">
         <x:f>ABS(H26-H10)/ABS(H10)</x:f>
-        <x:v>0.0014418546809001837</x:v>
+        <x:v>0.0031014204562756402</x:v>
       </x:c>
       <x:c r="J26" s="11" t="n">
         <x:f>1.643*F26/SQRT(A26)</x:f>
-        <x:v>2.14218584470595</x:v>
+        <x:v>2.1354365663955464</x:v>
       </x:c>
       <x:c r="K26" s="18" t="n">
         <x:f>ABS(J26-J10)/ABS(J10)</x:f>
-        <x:v>0.000433452902096561</x:v>
+        <x:v>0.003582737467114809</x:v>
       </x:c>
       <x:c r="L26" s="11" t="n">
         <x:f>1.96*F26/SQRT(A26)</x:f>
-        <x:v>2.5554986339766654</x:v>
+        <x:v>2.54744715163437</x:v>
       </x:c>
       <x:c r="M26" s="18" t="n">
         <x:f>ABS(L26-L10)/ABS(L10)</x:f>
-        <x:v>0.0004334529020967162</x:v>
+        <x:v>0.0035827374671149994</x:v>
       </x:c>
       <x:c r="N26" s="11" t="n">
         <x:f>2.576*F26/SQRT(A26)</x:f>
-        <x:v>3.3586553475121894</x:v>
+        <x:v>3.348073399290887</x:v>
       </x:c>
       <x:c r="O26" s="18" t="n">
         <x:f>ABS(N26-N10)/ABS(N10)</x:f>
-        <x:v>0.0004334529020966746</x:v>
+        <x:v>0.0035827374671149347</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2856,6 +2866,8 @@
     <x:col min="3" max="3" width="18" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="22" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1">
@@ -2950,10 +2962,12 @@
         <x:v>276</x:v>
       </x:c>
       <x:c r="C5" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;0,'Генератор'!$E$12:$E$311,"&lt;"&amp;E5)</x:f>
         <x:v>283</x:v>
       </x:c>
       <x:c r="D5" s="24" t="n">
-        <x:v>282.9887363473299</x:v>
+        <x:f>300*($B$23*(EXP(-0/$B$24)-EXP(-E5/$B$24))+(1-$B$23)*(EXP(-0/$B$25)-EXP(-E5/$B$25)))</x:f>
+        <x:v>282.9554416014811</x:v>
       </x:c>
       <x:c r="E5" s="24" t="n">
         <x:v>18.729195992191432</x:v>
@@ -2978,10 +2992,12 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="C6" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E5,'Генератор'!$E$12:$E$311,"&lt;"&amp;E6)</x:f>
         <x:v>8</x:v>
       </x:c>
       <x:c r="D6" s="24" t="n">
-        <x:v>6.728142508477672</x:v>
+        <x:f>300*($B$23*(EXP(-E5/$B$24)-EXP(-E6/$B$24))+(1-$B$23)*(EXP(-E5/$B$25)-EXP(-E6/$B$25)))</x:f>
+        <x:v>6.746990988514499</x:v>
       </x:c>
       <x:c r="E6" s="24" t="n">
         <x:v>37.458391984382864</x:v>
@@ -3006,10 +3022,12 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C7" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E6,'Генератор'!$E$12:$E$311,"&lt;"&amp;E7)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="D7" s="24" t="n">
-        <x:v>2.527152465006239</x:v>
+        <x:f>300*($B$23*(EXP(-E6/$B$24)-EXP(-E7/$B$24))+(1-$B$23)*(EXP(-E6/$B$25)-EXP(-E7/$B$25)))</x:f>
+        <x:v>2.53754657067952</x:v>
       </x:c>
       <x:c r="E7" s="24" t="n">
         <x:v>56.18758797657429</x:v>
@@ -3034,10 +3052,12 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="C8" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E7,'Генератор'!$E$12:$E$311,"&lt;"&amp;E8)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D8" s="24" t="n">
-        <x:v>1.8822143902015942</x:v>
+        <x:f>300*($B$23*(EXP(-E7/$B$24)-EXP(-E8/$B$24))+(1-$B$23)*(EXP(-E7/$B$25)-EXP(-E8/$B$25)))</x:f>
+        <x:v>1.888373800485436</x:v>
       </x:c>
       <x:c r="E8" s="24" t="n">
         <x:v>74.91678396876573</x:v>
@@ -3062,10 +3082,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C9" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E8,'Генератор'!$E$12:$E$311,"&lt;"&amp;E9)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="D9" s="24" t="n">
-        <x:v>1.4251430116659012</x:v>
+        <x:f>300*($B$23*(EXP(-E8/$B$24)-EXP(-E9/$B$24))+(1-$B$23)*(EXP(-E8/$B$25)-EXP(-E9/$B$25)))</x:f>
+        <x:v>1.4285479053345354</x:v>
       </x:c>
       <x:c r="E9" s="24" t="n">
         <x:v>93.64597996095716</x:v>
@@ -3090,10 +3112,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C10" s="10" t="n">
-        <x:v>0</x:v>
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E9,'Генератор'!$E$12:$E$311,"&lt;"&amp;E10)</x:f>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D10" s="24" t="n">
-        <x:v>1.0793583466931294</x:v>
+        <x:f>300*($B$23*(EXP(-E9/$B$24)-EXP(-E10/$B$24))+(1-$B$23)*(EXP(-E9/$B$25)-EXP(-E10/$B$25)))</x:f>
+        <x:v>1.0809843198092142</x:v>
       </x:c>
       <x:c r="E10" s="24" t="n">
         <x:v>112.37517595314858</x:v>
@@ -3118,10 +3142,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C11" s="10" t="n">
-        <x:v>1</x:v>
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E10,'Генератор'!$E$12:$E$311,"&lt;"&amp;E11)</x:f>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="24" t="n">
-        <x:v>0.817475577006462</x:v>
+        <x:f>300*($B$23*(EXP(-E10/$B$24)-EXP(-E11/$B$24))+(1-$B$23)*(EXP(-E10/$B$25)-EXP(-E11/$B$25)))</x:f>
+        <x:v>0.8179860686380246</x:v>
       </x:c>
       <x:c r="E11" s="24" t="n">
         <x:v>131.10437194534003</x:v>
@@ -3146,10 +3172,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C12" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E11,'Генератор'!$E$12:$E$311,"&lt;"&amp;E12)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D12" s="24" t="n">
-        <x:v>0.6191329964241435</x:v>
+        <x:f>300*($B$23*(EXP(-E11/$B$24)-EXP(-E12/$B$24))+(1-$B$23)*(EXP(-E11/$B$25)-EXP(-E12/$B$25)))</x:f>
+        <x:v>0.6189740635586023</x:v>
       </x:c>
       <x:c r="E12" s="24" t="n">
         <x:v>149.83356793753146</x:v>
@@ -3174,10 +3202,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C13" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E12,'Генератор'!$E$12:$E$311,"&lt;"&amp;E13)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D13" s="24" t="n">
-        <x:v>0.4689139082520424</x:v>
+        <x:f>300*($B$23*(EXP(-E12/$B$24)-EXP(-E13/$B$24))+(1-$B$23)*(EXP(-E12/$B$25)-EXP(-E13/$B$25)))</x:f>
+        <x:v>0.4683807053725127</x:v>
       </x:c>
       <x:c r="E13" s="24" t="n">
         <x:v>168.56276392972288</x:v>
@@ -3202,10 +3232,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C14" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E13,'Генератор'!$E$12:$E$311,"&lt;"&amp;E14)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D14" s="24" t="n">
-        <x:v>0.3551421982456006</x:v>
+        <x:f>300*($B$23*(EXP(-E13/$B$24)-EXP(-E14/$B$24))+(1-$B$23)*(EXP(-E13/$B$25)-EXP(-E14/$B$25)))</x:f>
+        <x:v>0.3544259736963097</x:v>
       </x:c>
       <x:c r="E14" s="24" t="n">
         <x:v>187.29195992191433</x:v>
@@ -3230,10 +3262,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C15" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E14,'Генератор'!$E$12:$E$311,"&lt;"&amp;E15)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="24" t="n">
-        <x:v>0.2689747067748808</x:v>
+        <x:f>300*($B$23*(EXP(-E14/$B$24)-EXP(-E15/$B$24))+(1-$B$23)*(EXP(-E14/$B$25)-EXP(-E15/$B$25)))</x:f>
+        <x:v>0.2681958701324191</x:v>
       </x:c>
       <x:c r="E15" s="24" t="n">
         <x:v>206.02115591410575</x:v>
@@ -3258,10 +3292,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C16" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E15,'Генератор'!$E$12:$E$311,"&lt;"&amp;E16)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D16" s="24" t="n">
-        <x:v>0.20371387360338858</x:v>
+        <x:f>300*($B$23*(EXP(-E15/$B$24)-EXP(-E16/$B$24))+(1-$B$23)*(EXP(-E15/$B$25)-EXP(-E16/$B$25)))</x:f>
+        <x:v>0.2029451284451238</x:v>
       </x:c>
       <x:c r="E16" s="24" t="n">
         <x:v>224.75035190629717</x:v>
@@ -3286,10 +3322,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C17" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E16,'Генератор'!$E$12:$E$311,"&lt;"&amp;E17)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="24" t="n">
-        <x:v>0.1542871550864085</x:v>
+        <x:f>300*($B$23*(EXP(-E16/$B$24)-EXP(-E17/$B$24))+(1-$B$23)*(EXP(-E16/$B$25)-EXP(-E17/$B$25)))</x:f>
+        <x:v>0.15356957263835702</x:v>
       </x:c>
       <x:c r="E17" s="24" t="n">
         <x:v>243.47954789848862</x:v>
@@ -3314,10 +3352,12 @@
         <x:v>0</x:v>
       </x:c>
       <x:c r="C18" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E17,'Генератор'!$E$12:$E$311,"&lt;"&amp;E18)</x:f>
         <x:v>0</x:v>
       </x:c>
       <x:c r="D18" s="24" t="n">
-        <x:v>0.11685274941559758</x:v>
+        <x:f>300*($B$23*(EXP(-E17/$B$24)-EXP(-E18/$B$24))+(1-$B$23)*(EXP(-E17/$B$25)-EXP(-E18/$B$25)))</x:f>
+        <x:v>0.11620684773768594</x:v>
       </x:c>
       <x:c r="E18" s="24" t="n">
         <x:v>262.20874389068007</x:v>
@@ -3342,10 +3382,12 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C19" s="10" t="n">
+        <x:f>COUNTIFS('Генератор'!$E$12:$E$311,"&gt;="&amp;E18,'Генератор'!$E$12:$E$311,"&lt;="&amp;E19)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="D19" s="24" t="n">
-        <x:v>0.08850098401475602</x:v>
+        <x:f>300*($B$23*(EXP(-E18/$B$24)-EXP(-E19/$B$24))+(1-$B$23)*(EXP(-E18/$B$25)-EXP(-E19/$B$25)))</x:f>
+        <x:v>0.08793429081769007</x:v>
       </x:c>
       <x:c r="E19" s="24" t="n">
         <x:v>280.9379398828715</x:v>
@@ -3409,8 +3451,12 @@
       <x:c r="D22" s="13"/>
       <x:c r="E22" s="13"/>
       <x:c r="F22" s="13"/>
-      <x:c r="G22" s="13"/>
-      <x:c r="H22" s="13"/>
+      <x:c r="G22" s="27" t="str">
+        <x:v>Параметр модели</x:v>
+      </x:c>
+      <x:c r="H22" s="27" t="str">
+        <x:v>Значение</x:v>
+      </x:c>
       <x:c r="I22" s="13"/>
       <x:c r="J22" s="13"/>
       <x:c r="K22" s="13"/>
@@ -3422,17 +3468,23 @@
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="10" t="str">
-        <x:v>p</x:v>
+        <x:v>q</x:v>
       </x:c>
       <x:c r="B23" s="16" t="n">
-        <x:v>0.9404944635474064</x:v>
+        <x:f>(1+SQRT((H26^2-1)/(H26^2+1)))/2</x:f>
+        <x:v>0.9403058165037487</x:v>
       </x:c>
       <x:c r="C23" s="13"/>
       <x:c r="D23" s="13"/>
       <x:c r="E23" s="13"/>
       <x:c r="F23" s="13"/>
-      <x:c r="G23" s="13"/>
-      <x:c r="H23" s="13"/>
+      <x:c r="G23" s="27" t="str">
+        <x:v>α1</x:v>
+      </x:c>
+      <x:c r="H23" s="28" t="n">
+        <x:f>AVERAGE('Исходные данные'!B5:B304)</x:f>
+        <x:v>8.020778465134065</x:v>
+      </x:c>
       <x:c r="I23" s="13"/>
       <x:c r="J23" s="13"/>
       <x:c r="K23" s="13"/>
@@ -3444,17 +3496,23 @@
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="10" t="str">
-        <x:v>μ1</x:v>
+        <x:v>t1</x:v>
       </x:c>
       <x:c r="B24" s="16" t="n">
-        <x:v>0.23451450944211719</x:v>
+        <x:f>H23*(1-SQRT((1-B23)*(H26^2-1)/(2*B23)))</x:f>
+        <x:v>4.2649839681716415</x:v>
       </x:c>
       <x:c r="C24" s="13"/>
       <x:c r="D24" s="13"/>
       <x:c r="E24" s="13"/>
       <x:c r="F24" s="13"/>
-      <x:c r="G24" s="13"/>
-      <x:c r="H24" s="13"/>
+      <x:c r="G24" s="27" t="str">
+        <x:v>α2</x:v>
+      </x:c>
+      <x:c r="H24" s="28" t="n">
+        <x:f>SUMSQ('Исходные данные'!B5:B304)/COUNT('Исходные данные'!B5:B304)</x:f>
+        <x:v>573.0623917186392</x:v>
+      </x:c>
       <x:c r="I24" s="13"/>
       <x:c r="J24" s="13"/>
       <x:c r="K24" s="13"/>
@@ -3466,17 +3524,23 @@
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="10" t="str">
-        <x:v>μ2</x:v>
+        <x:v>t2</x:v>
       </x:c>
       <x:c r="B25" s="16" t="n">
-        <x:v>0.014837845655820388</x:v>
+        <x:f>H23*(1+SQRT(B23*(H26^2-1)/(2*(1-B23))))</x:f>
+        <x:v>67.18224452837813</x:v>
       </x:c>
       <x:c r="C25" s="13"/>
       <x:c r="D25" s="13"/>
       <x:c r="E25" s="13"/>
       <x:c r="F25" s="13"/>
-      <x:c r="G25" s="13"/>
-      <x:c r="H25" s="13"/>
+      <x:c r="G25" s="27" t="str">
+        <x:v>D*</x:v>
+      </x:c>
+      <x:c r="H25" s="28" t="n">
+        <x:f>H24-H23^2</x:f>
+        <x:v>508.7295045318809</x:v>
+      </x:c>
       <x:c r="I25" s="13"/>
       <x:c r="J25" s="13"/>
       <x:c r="K25" s="13"/>
@@ -3491,14 +3555,19 @@
         <x:v>Формула генерации</x:v>
       </x:c>
       <x:c r="B26" s="17" t="str">
-        <x:v>U1≤p: -ln(U2)/μ1; иначе -ln(U2)/μ2</x:v>
+        <x:v>U1≤q: -t1·ln(U2); иначе -t2·ln(U2)</x:v>
       </x:c>
       <x:c r="C26" s="13"/>
       <x:c r="D26" s="13"/>
       <x:c r="E26" s="13"/>
       <x:c r="F26" s="13"/>
-      <x:c r="G26" s="13"/>
-      <x:c r="H26" s="13"/>
+      <x:c r="G26" s="27" t="str">
+        <x:v>ν</x:v>
+      </x:c>
+      <x:c r="H26" s="28" t="n">
+        <x:f>SQRT(H25)/H23</x:f>
+        <x:v>2.8120752737822614</x:v>
+      </x:c>
       <x:c r="I26" s="13"/>
       <x:c r="J26" s="13"/>
       <x:c r="K26" s="13"/>
@@ -3519,8 +3588,13 @@
       <x:c r="D27" s="13"/>
       <x:c r="E27" s="13"/>
       <x:c r="F27" s="13"/>
-      <x:c r="G27" s="13"/>
-      <x:c r="H27" s="13"/>
+      <x:c r="G27" s="27" t="str">
+        <x:v>Условие q ≥</x:v>
+      </x:c>
+      <x:c r="H27" s="28" t="n">
+        <x:f>(H26^2-1)/(H26^2+1)</x:f>
+        <x:v>0.7754768481881311</x:v>
+      </x:c>
       <x:c r="I27" s="13"/>
       <x:c r="J27" s="13"/>
       <x:c r="K27" s="13"/>
@@ -3537,8 +3611,12 @@
       <x:c r="D28" s="13"/>
       <x:c r="E28" s="13"/>
       <x:c r="F28" s="13"/>
-      <x:c r="G28" s="13"/>
-      <x:c r="H28" s="13"/>
+      <x:c r="G28" s="27" t="str">
+        <x:v>Выбор q</x:v>
+      </x:c>
+      <x:c r="H28" s="27" t="str">
+        <x:v>q·t1=(1−q)·t2=α1/2</x:v>
+      </x:c>
       <x:c r="I28" s="13"/>
       <x:c r="J28" s="13"/>
       <x:c r="K28" s="13"/>
@@ -3730,7 +3808,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rca72fea4fbef4ad9"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32330039aa1149cb"/>
 </x:worksheet>
 </file>
 
@@ -3835,11 +3913,11 @@
       </x:c>
       <x:c r="C5" s="23" t="n">
         <x:f>CORREL('Генератор'!$E$12:$E$310,'Генератор'!$E$13:$E$311)</x:f>
-        <x:v>0.019398808885156566</x:v>
+        <x:v>0.019338458815015284</x:v>
       </x:c>
       <x:c r="D5" s="18" t="n">
         <x:f>IF(ABS(B5)&lt;0.000001,"н/д",ABS(C5-B5)/ABS(B5))</x:f>
-        <x:v>1.4734506245639851</x:v>
+        <x:v>1.4719777105015792</x:v>
       </x:c>
       <x:c r="E5" s="23" t="n">
         <x:v>0.11316065276116663</x:v>
@@ -3865,11 +3943,11 @@
       </x:c>
       <x:c r="C6" s="23" t="n">
         <x:f>CORREL('Генератор'!$E$12:$E$309,'Генератор'!$E$14:$E$311)</x:f>
-        <x:v>-0.03235827647769642</x:v>
+        <x:v>-0.03235815041026696</x:v>
       </x:c>
       <x:c r="D6" s="18" t="n">
         <x:f>IF(ABS(B6)&lt;0.000001,"н/д",ABS(C6-B6)/ABS(B6))</x:f>
-        <x:v>0.16150730819128262</x:v>
+        <x:v>0.16151057494803805</x:v>
       </x:c>
       <x:c r="E6" s="23" t="n">
         <x:v>0.11316065276116663</x:v>
@@ -3895,11 +3973,11 @@
       </x:c>
       <x:c r="C7" s="23" t="n">
         <x:f>CORREL('Генератор'!$E$12:$E$308,'Генератор'!$E$15:$E$311)</x:f>
-        <x:v>-0.008279308717996751</x:v>
+        <x:v>-0.008316684997080305</x:v>
       </x:c>
       <x:c r="D7" s="18" t="n">
         <x:f>IF(ABS(B7)&lt;0.000001,"н/д",ABS(C7-B7)/ABS(B7))</x:f>
-        <x:v>1.246769927782268</x:v>
+        <x:v>1.2478839509458406</x:v>
       </x:c>
       <x:c r="E7" s="23" t="n">
         <x:v>0.11316065276116663</x:v>
@@ -3925,11 +4003,11 @@
       </x:c>
       <x:c r="C8" s="23" t="n">
         <x:f>CORREL('Генератор'!$E$12:$E$307,'Генератор'!$E$16:$E$311)</x:f>
-        <x:v>-0.034614817564928055</x:v>
+        <x:v>-0.034699724099785244</x:v>
       </x:c>
       <x:c r="D8" s="18" t="n">
         <x:f>IF(ABS(B8)&lt;0.000001,"н/д",ABS(C8-B8)/ABS(B8))</x:f>
-        <x:v>0.1304342360812351</x:v>
+        <x:v>0.1283012820159335</x:v>
       </x:c>
       <x:c r="E8" s="23" t="n">
         <x:v>0.11316065276116663</x:v>
@@ -3955,11 +4033,11 @@
       </x:c>
       <x:c r="C9" s="23" t="n">
         <x:f>CORREL('Генератор'!$E$12:$E$306,'Генератор'!$E$17:$E$311)</x:f>
-        <x:v>-0.01786421281894183</x:v>
+        <x:v>-0.0179354546568628</x:v>
       </x:c>
       <x:c r="D9" s="18" t="n">
         <x:f>IF(ABS(B9)&lt;0.000001,"н/д",ABS(C9-B9)/ABS(B9))</x:f>
-        <x:v>0.6038068409274219</x:v>
+        <x:v>0.6022268368651036</x:v>
       </x:c>
       <x:c r="E9" s="23" t="n">
         <x:v>0.11316065276116663</x:v>
@@ -3985,11 +4063,11 @@
       </x:c>
       <x:c r="C10" s="23" t="n">
         <x:f>CORREL('Генератор'!$E$12:$E$305,'Генератор'!$E$18:$E$311)</x:f>
-        <x:v>-0.01643129630588</x:v>
+        <x:v>-0.016392731571964837</x:v>
       </x:c>
       <x:c r="D10" s="18" t="n">
         <x:f>IF(ABS(B10)&lt;0.000001,"н/д",ABS(C10-B10)/ABS(B10))</x:f>
-        <x:v>1.1213830762586907</x:v>
+        <x:v>1.1210981866218306</x:v>
       </x:c>
       <x:c r="E10" s="23" t="n">
         <x:v>0.11316065276116663</x:v>
@@ -4015,11 +4093,11 @@
       </x:c>
       <x:c r="C11" s="23" t="n">
         <x:f>CORREL('Генератор'!$E$12:$E$304,'Генератор'!$E$19:$E$311)</x:f>
-        <x:v>0.026406397993786298</x:v>
+        <x:v>0.026573320462622667</x:v>
       </x:c>
       <x:c r="D11" s="18" t="n">
         <x:f>IF(ABS(B11)&lt;0.000001,"н/д",ABS(C11-B11)/ABS(B11))</x:f>
-        <x:v>1.8994911087409883</x:v>
+        <x:v>1.9051770518447293</x:v>
       </x:c>
       <x:c r="E11" s="23" t="n">
         <x:v>0.11316065276116663</x:v>
@@ -4045,11 +4123,11 @@
       </x:c>
       <x:c r="C12" s="23" t="n">
         <x:f>CORREL('Генератор'!$E$12:$E$303,'Генератор'!$E$20:$E$311)</x:f>
-        <x:v>0.014529120390008164</x:v>
+        <x:v>0.01468214359719367</x:v>
       </x:c>
       <x:c r="D12" s="18" t="n">
         <x:f>IF(ABS(B12)&lt;0.000001,"н/д",ABS(C12-B12)/ABS(B12))</x:f>
-        <x:v>1.2540322276541593</x:v>
+        <x:v>1.2567077389831764</x:v>
       </x:c>
       <x:c r="E12" s="23" t="n">
         <x:v>0.11316065276116663</x:v>
@@ -4075,11 +4153,11 @@
       </x:c>
       <x:c r="C13" s="23" t="n">
         <x:f>CORREL('Генератор'!$E$12:$E$302,'Генератор'!$E$21:$E$311)</x:f>
-        <x:v>-0.01647827638455016</x:v>
+        <x:v>-0.016440110077217535</x:v>
       </x:c>
       <x:c r="D13" s="18" t="n">
         <x:f>IF(ABS(B13)&lt;0.000001,"н/д",ABS(C13-B13)/ABS(B13))</x:f>
-        <x:v>0.3905261145058493</x:v>
+        <x:v>0.39193775290067484</x:v>
       </x:c>
       <x:c r="E13" s="23" t="n">
         <x:v>0.11316065276116663</x:v>
@@ -4105,11 +4183,11 @@
       </x:c>
       <x:c r="C14" s="23" t="n">
         <x:f>CORREL('Генератор'!$E$12:$E$301,'Генератор'!$E$22:$E$311)</x:f>
-        <x:v>-0.00965692969542248</x:v>
+        <x:v>-0.009577055379325721</x:v>
       </x:c>
       <x:c r="D14" s="18" t="n">
         <x:f>IF(ABS(B14)&lt;0.000001,"н/д",ABS(C14-B14)/ABS(B14))</x:f>
-        <x:v>1.1174353343622723</x:v>
+        <x:v>1.1164640042072824</x:v>
       </x:c>
       <x:c r="E14" s="23" t="n">
         <x:v>0.11316065276116663</x:v>
@@ -4168,7 +4246,8 @@
         <x:v>Коэффициент корреляции рядов</x:v>
       </x:c>
       <x:c r="B17" s="23" t="n">
-        <x:v>-0.03611636453935302</x:v>
+        <x:f>CORREL('Исходные данные'!B5:B304,'Генератор'!E12:E311)</x:f>
+        <x:v>-0.036073946962238944</x:v>
       </x:c>
       <x:c r="C17" s="13"/>
       <x:c r="D17" s="13"/>
@@ -4189,7 +4268,7 @@
         <x:v>Критерий Льюнга–Бокса Q(10)</x:v>
       </x:c>
       <x:c r="B18" s="23" t="n">
-        <x:v>11.682742281863302</x:v>
+        <x:v>11.645951302168012</x:v>
       </x:c>
       <x:c r="C18" s="13"/>
       <x:c r="D18" s="13"/>
@@ -4210,7 +4289,7 @@
         <x:v>p-value</x:v>
       </x:c>
       <x:c r="B19" s="23" t="n">
-        <x:v>0.3068503436532233</x:v>
+        <x:v>0.3094501499187564</x:v>
       </x:c>
       <x:c r="C19" s="13"/>
       <x:c r="D19" s="13"/>
@@ -4231,7 +4310,7 @@
         <x:v>Вывод</x:v>
       </x:c>
       <x:c r="B20" s="17" t="str">
-        <x:v>При p &gt; 0,05 оснований отвергать случайность ряда нет</x:v>
+        <x:v>Значимая серийная корреляция не обнаружена; независимость не доказана</x:v>
       </x:c>
       <x:c r="C20" s="13"/>
       <x:c r="D20" s="13"/>
@@ -4266,7 +4345,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbaf152b156564644"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rcd9bf4c102de451c"/>
 </x:worksheet>
 </file>
 
@@ -4363,9 +4442,10 @@
     </x:row>
     <x:row r="5">
       <x:c r="A5" s="10" t="str">
-        <x:v>Математическое ожидание</x:v>
+        <x:v>Среднее t</x:v>
       </x:c>
       <x:c r="B5" s="16" t="n">
+        <x:f>'Распределение'!H23</x:f>
         <x:v>8.020778465134065</x:v>
       </x:c>
       <x:c r="C5" s="13"/>
@@ -4388,10 +4468,11 @@
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="10" t="str">
-        <x:v>Коэффициент вариации</x:v>
+        <x:v>ν модели</x:v>
       </x:c>
       <x:c r="B6" s="16" t="n">
-        <x:v>2.8167738155279216</x:v>
+        <x:f>'Распределение'!H26</x:f>
+        <x:v>2.8120752737822614</x:v>
       </x:c>
       <x:c r="C6" s="13"/>
       <x:c r="D6" s="13"/>
@@ -4413,10 +4494,11 @@
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="10" t="str">
-        <x:v>Вероятность ветви p</x:v>
+        <x:v>q (ветвь 1)</x:v>
       </x:c>
       <x:c r="B7" s="16" t="n">
-        <x:v>0.9404944635474064</x:v>
+        <x:f>'Распределение'!B23</x:f>
+        <x:v>0.9403058165037487</x:v>
       </x:c>
       <x:c r="C7" s="13"/>
       <x:c r="D7" s="13"/>
@@ -4438,10 +4520,11 @@
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="10" t="str">
-        <x:v>Интенсивность быстрой ветви μ1</x:v>
+        <x:v>Среднее t1</x:v>
       </x:c>
       <x:c r="B8" s="16" t="n">
-        <x:v>0.23451450944211719</x:v>
+        <x:f>'Распределение'!B24</x:f>
+        <x:v>4.2649839681716415</x:v>
       </x:c>
       <x:c r="C8" s="13"/>
       <x:c r="D8" s="13"/>
@@ -4463,10 +4546,11 @@
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="10" t="str">
-        <x:v>Интенсивность медленной ветви μ2</x:v>
+        <x:v>Среднее t2</x:v>
       </x:c>
       <x:c r="B9" s="16" t="n">
-        <x:v>0.014837845655820388</x:v>
+        <x:f>'Распределение'!B25</x:f>
+        <x:v>67.18224452837813</x:v>
       </x:c>
       <x:c r="C9" s="13"/>
       <x:c r="D9" s="13"/>
@@ -4488,7 +4572,7 @@
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="10" t="str">
-        <x:v>Фиксированное начальное состояние LCG</x:v>
+        <x:v>Seed LCG</x:v>
       </x:c>
       <x:c r="B10" s="10" t="n">
         <x:v>8141</x:v>
@@ -4545,11 +4629,12 @@
         <x:v>0.6979191022692248</x:v>
       </x:c>
       <x:c r="D12" s="10" t="n">
+        <x:f>IF(B12&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E12" s="11" t="n">
-        <x:f>IF(B12&lt;=$B$7,-LN(C12)/$B$8,-LN(C12)/$B$9)</x:f>
-        <x:v>1.533602688890932</x:v>
+        <x:f>IF(B12&lt;=$B$7,-$B$8*LN(C12),-$B$9*LN(C12))</x:f>
+        <x:v>1.5339103649770813</x:v>
       </x:c>
       <x:c r="F12" s="13"/>
       <x:c r="G12" s="13"/>
@@ -4573,11 +4658,12 @@
         <x:v>0.018101770780049264</x:v>
       </x:c>
       <x:c r="D13" s="10" t="n">
+        <x:f>IF(B13&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E13" s="11" t="n">
-        <x:f>IF(B13&lt;=$B$7,-LN(C13)/$B$8,-LN(C13)/$B$9)</x:f>
-        <x:v>17.106598316186457</x:v>
+        <x:f>IF(B13&lt;=$B$7,-$B$8*LN(C13),-$B$9*LN(C13))</x:f>
+        <x:v>17.110030294530898</x:v>
       </x:c>
       <x:c r="F13" s="13"/>
       <x:c r="G13" s="13"/>
@@ -4601,11 +4687,12 @@
         <x:v>0.7359764379216358</x:v>
       </x:c>
       <x:c r="D14" s="10" t="n">
+        <x:f>IF(B14&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E14" s="11" t="n">
-        <x:f>IF(B14&lt;=$B$7,-LN(C14)/$B$8,-LN(C14)/$B$9)</x:f>
-        <x:v>1.3071991800780414</x:v>
+        <x:f>IF(B14&lt;=$B$7,-$B$8*LN(C14),-$B$9*LN(C14))</x:f>
+        <x:v>1.3074614343962276</x:v>
       </x:c>
       <x:c r="F14" s="13"/>
       <x:c r="G14" s="13"/>
@@ -4629,11 +4716,12 @@
         <x:v>0.04129750037100166</x:v>
       </x:c>
       <x:c r="D15" s="10" t="n">
+        <x:f>IF(B15&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E15" s="11" t="n">
-        <x:f>IF(B15&lt;=$B$7,-LN(C15)/$B$8,-LN(C15)/$B$9)</x:f>
-        <x:v>13.58957836823289</x:v>
+        <x:f>IF(B15&lt;=$B$7,-$B$8*LN(C15),-$B$9*LN(C15))</x:f>
+        <x:v>13.592304751223116</x:v>
       </x:c>
       <x:c r="F15" s="13"/>
       <x:c r="G15" s="13"/>
@@ -4657,11 +4745,12 @@
         <x:v>0.26998353365343064</x:v>
       </x:c>
       <x:c r="D16" s="10" t="n">
+        <x:f>IF(B16&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E16" s="11" t="n">
-        <x:f>IF(B16&lt;=$B$7,-LN(C16)/$B$8,-LN(C16)/$B$9)</x:f>
-        <x:v>88.24692874458205</x:v>
+        <x:f>IF(B16&lt;=$B$7,-$B$8*LN(C16),-$B$9*LN(C16))</x:f>
+        <x:v>87.9680486051027</x:v>
       </x:c>
       <x:c r="F16" s="13"/>
       <x:c r="G16" s="13"/>
@@ -4685,11 +4774,12 @@
         <x:v>0.7934395730262622</x:v>
       </x:c>
       <x:c r="D17" s="10" t="n">
+        <x:f>IF(B17&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E17" s="11" t="n">
-        <x:f>IF(B17&lt;=$B$7,-LN(C17)/$B$8,-LN(C17)/$B$9)</x:f>
-        <x:v>0.9866250703281266</x:v>
+        <x:f>IF(B17&lt;=$B$7,-$B$8*LN(C17),-$B$9*LN(C17))</x:f>
+        <x:v>0.9868230100828846</x:v>
       </x:c>
       <x:c r="F17" s="13"/>
       <x:c r="G17" s="13"/>
@@ -4713,11 +4803,12 @@
         <x:v>0.6323819578392431</x:v>
       </x:c>
       <x:c r="D18" s="10" t="n">
+        <x:f>IF(B18&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E18" s="11" t="n">
-        <x:f>IF(B18&lt;=$B$7,-LN(C18)/$B$8,-LN(C18)/$B$9)</x:f>
-        <x:v>1.9540867846936898</x:v>
+        <x:f>IF(B18&lt;=$B$7,-$B$8*LN(C18),-$B$9*LN(C18))</x:f>
+        <x:v>1.9544788195918192</x:v>
       </x:c>
       <x:c r="F18" s="13"/>
       <x:c r="G18" s="13"/>
@@ -4741,11 +4832,12 @@
         <x:v>0.9959714034339413</x:v>
       </x:c>
       <x:c r="D19" s="10" t="n">
+        <x:f>IF(B19&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E19" s="11" t="n">
-        <x:f>IF(B19&lt;=$B$7,-LN(C19)/$B$8,-LN(C19)/$B$9)</x:f>
-        <x:v>0.017213149118268743</x:v>
+        <x:f>IF(B19&lt;=$B$7,-$B$8*LN(C19),-$B$9*LN(C19))</x:f>
+        <x:v>0.017216602473162663</x:v>
       </x:c>
       <x:c r="F19" s="13"/>
       <x:c r="G19" s="13"/>
@@ -4769,11 +4861,12 @@
         <x:v>0.05741152714472264</x:v>
       </x:c>
       <x:c r="D20" s="10" t="n">
+        <x:f>IF(B20&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E20" s="11" t="n">
-        <x:f>IF(B20&lt;=$B$7,-LN(C20)/$B$8,-LN(C20)/$B$9)</x:f>
-        <x:v>12.184790532916601</x:v>
+        <x:f>IF(B20&lt;=$B$7,-$B$8*LN(C20),-$B$9*LN(C20))</x:f>
+        <x:v>12.187235083052611</x:v>
       </x:c>
       <x:c r="F20" s="13"/>
       <x:c r="G20" s="13"/>
@@ -4797,11 +4890,12 @@
         <x:v>0.9265841174637899</x:v>
       </x:c>
       <x:c r="D21" s="10" t="n">
+        <x:f>IF(B21&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E21" s="11" t="n">
-        <x:f>IF(B21&lt;=$B$7,-LN(C21)/$B$8,-LN(C21)/$B$9)</x:f>
-        <x:v>0.3251417022707412</x:v>
+        <x:f>IF(B21&lt;=$B$7,-$B$8*LN(C21),-$B$9*LN(C21))</x:f>
+        <x:v>0.3252069331986231</x:v>
       </x:c>
       <x:c r="F21" s="13"/>
       <x:c r="G21" s="13"/>
@@ -4825,11 +4919,12 @@
         <x:v>0.5312689979327843</x:v>
       </x:c>
       <x:c r="D22" s="10" t="n">
+        <x:f>IF(B22&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E22" s="11" t="n">
-        <x:f>IF(B22&lt;=$B$7,-LN(C22)/$B$8,-LN(C22)/$B$9)</x:f>
-        <x:v>2.697004974544531</x:v>
+        <x:f>IF(B22&lt;=$B$7,-$B$8*LN(C22),-$B$9*LN(C22))</x:f>
+        <x:v>2.697546055973837</x:v>
       </x:c>
       <x:c r="F22" s="13"/>
       <x:c r="G22" s="13"/>
@@ -4853,11 +4948,12 @@
         <x:v>0.03353539982344955</x:v>
       </x:c>
       <x:c r="D23" s="10" t="n">
+        <x:f>IF(B23&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E23" s="11" t="n">
-        <x:f>IF(B23&lt;=$B$7,-LN(C23)/$B$8,-LN(C23)/$B$9)</x:f>
-        <x:v>14.47737154944596</x:v>
+        <x:f>IF(B23&lt;=$B$7,-$B$8*LN(C23),-$B$9*LN(C23))</x:f>
+        <x:v>14.480276044233515</x:v>
       </x:c>
       <x:c r="F23" s="13"/>
       <x:c r="G23" s="13"/>
@@ -4881,11 +4977,12 @@
         <x:v>0.049493320169858634</x:v>
       </x:c>
       <x:c r="D24" s="10" t="n">
+        <x:f>IF(B24&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E24" s="11" t="n">
-        <x:f>IF(B24&lt;=$B$7,-LN(C24)/$B$8,-LN(C24)/$B$9)</x:f>
-        <x:v>12.817618712495543</x:v>
+        <x:f>IF(B24&lt;=$B$7,-$B$8*LN(C24),-$B$9*LN(C24))</x:f>
+        <x:v>12.820190222566424</x:v>
       </x:c>
       <x:c r="F24" s="13"/>
       <x:c r="G24" s="13"/>
@@ -4909,11 +5006,12 @@
         <x:v>0.37125740421470255</x:v>
       </x:c>
       <x:c r="D25" s="10" t="n">
+        <x:f>IF(B25&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E25" s="11" t="n">
-        <x:f>IF(B25&lt;=$B$7,-LN(C25)/$B$8,-LN(C25)/$B$9)</x:f>
-        <x:v>4.2251528377010885</x:v>
+        <x:f>IF(B25&lt;=$B$7,-$B$8*LN(C25),-$B$9*LN(C25))</x:f>
+        <x:v>4.226000500852635</x:v>
       </x:c>
       <x:c r="F25" s="13"/>
       <x:c r="G25" s="13"/>
@@ -4937,11 +5035,12 @@
         <x:v>0.672202453832142</x:v>
       </x:c>
       <x:c r="D26" s="10" t="n">
+        <x:f>IF(B26&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E26" s="11" t="n">
-        <x:f>IF(B26&lt;=$B$7,-LN(C26)/$B$8,-LN(C26)/$B$9)</x:f>
-        <x:v>1.6936935552226375</x:v>
+        <x:f>IF(B26&lt;=$B$7,-$B$8*LN(C26),-$B$9*LN(C26))</x:f>
+        <x:v>1.6940333492305524</x:v>
       </x:c>
       <x:c r="F26" s="13"/>
       <x:c r="G26" s="13"/>
@@ -4965,11 +5064,12 @@
         <x:v>0.8728787259897217</x:v>
       </x:c>
       <x:c r="D27" s="10" t="n">
+        <x:f>IF(B27&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E27" s="11" t="n">
-        <x:f>IF(B27&lt;=$B$7,-LN(C27)/$B$8,-LN(C27)/$B$9)</x:f>
-        <x:v>0.5797451488516071</x:v>
+        <x:f>IF(B27&lt;=$B$7,-$B$8*LN(C27),-$B$9*LN(C27))</x:f>
+        <x:v>0.579861459105661</x:v>
       </x:c>
       <x:c r="F27" s="13"/>
       <x:c r="G27" s="13"/>
@@ -4993,11 +5093,12 @@
         <x:v>0.017806747811846435</x:v>
       </x:c>
       <x:c r="D28" s="10" t="n">
+        <x:f>IF(B28&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E28" s="11" t="n">
-        <x:f>IF(B28&lt;=$B$7,-LN(C28)/$B$8,-LN(C28)/$B$9)</x:f>
-        <x:v>17.176667714719077</x:v>
+        <x:f>IF(B28&lt;=$B$7,-$B$8*LN(C28),-$B$9*LN(C28))</x:f>
+        <x:v>17.180113750601667</x:v>
       </x:c>
       <x:c r="F28" s="13"/>
       <x:c r="G28" s="13"/>
@@ -5021,11 +5122,12 @@
         <x:v>0.7252854373073205</x:v>
       </x:c>
       <x:c r="D29" s="10" t="n">
+        <x:f>IF(B29&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E29" s="11" t="n">
-        <x:f>IF(B29&lt;=$B$7,-LN(C29)/$B$8,-LN(C29)/$B$9)</x:f>
-        <x:v>1.3695954068806595</x:v>
+        <x:f>IF(B29&lt;=$B$7,-$B$8*LN(C29),-$B$9*LN(C29))</x:f>
+        <x:v>1.3698701793216896</x:v>
       </x:c>
       <x:c r="F29" s="13"/>
       <x:c r="G29" s="13"/>
@@ -5049,11 +5151,12 @@
         <x:v>0.08582388132344931</x:v>
       </x:c>
       <x:c r="D30" s="10" t="n">
+        <x:f>IF(B30&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E30" s="11" t="n">
-        <x:f>IF(B30&lt;=$B$7,-LN(C30)/$B$8,-LN(C30)/$B$9)</x:f>
-        <x:v>165.48615149871662</x:v>
+        <x:f>IF(B30&lt;=$B$7,-$B$8*LN(C30),-$B$9*LN(C30))</x:f>
+        <x:v>164.96317804606036</x:v>
       </x:c>
       <x:c r="F30" s="13"/>
       <x:c r="G30" s="13"/>
@@ -5077,11 +5180,12 @@
         <x:v>0.3623461847892031</x:v>
       </x:c>
       <x:c r="D31" s="10" t="n">
+        <x:f>IF(B31&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E31" s="11" t="n">
-        <x:f>IF(B31&lt;=$B$7,-LN(C31)/$B$8,-LN(C31)/$B$9)</x:f>
-        <x:v>4.328752259182227</x:v>
+        <x:f>IF(B31&lt;=$B$7,-$B$8*LN(C31),-$B$9*LN(C31))</x:f>
+        <x:v>4.329620706768204</x:v>
       </x:c>
       <x:c r="F31" s="13"/>
       <x:c r="G31" s="13"/>
@@ -5105,11 +5209,12 @@
         <x:v>0.5494203678099439</x:v>
       </x:c>
       <x:c r="D32" s="10" t="n">
+        <x:f>IF(B32&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E32" s="11" t="n">
-        <x:f>IF(B32&lt;=$B$7,-LN(C32)/$B$8,-LN(C32)/$B$9)</x:f>
-        <x:v>2.553750020022383</x:v>
+        <x:f>IF(B32&lt;=$B$7,-$B$8*LN(C32),-$B$9*LN(C32))</x:f>
+        <x:v>2.5542623612023085</x:v>
       </x:c>
       <x:c r="F32" s="13"/>
       <x:c r="G32" s="13"/>
@@ -5133,11 +5238,12 @@
         <x:v>0.8419263496762142</x:v>
       </x:c>
       <x:c r="D33" s="10" t="n">
+        <x:f>IF(B33&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E33" s="11" t="n">
-        <x:f>IF(B33&lt;=$B$7,-LN(C33)/$B$8,-LN(C33)/$B$9)</x:f>
-        <x:v>0.7336976277853519</x:v>
+        <x:f>IF(B33&lt;=$B$7,-$B$8*LN(C33),-$B$9*LN(C33))</x:f>
+        <x:v>0.7338448244590204</x:v>
       </x:c>
       <x:c r="F33" s="13"/>
       <x:c r="G33" s="13"/>
@@ -5161,11 +5267,12 @@
         <x:v>0.9083046213490888</x:v>
       </x:c>
       <x:c r="D34" s="10" t="n">
+        <x:f>IF(B34&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E34" s="11" t="n">
-        <x:f>IF(B34&lt;=$B$7,-LN(C34)/$B$8,-LN(C34)/$B$9)</x:f>
-        <x:v>0.4101045637015083</x:v>
+        <x:f>IF(B34&lt;=$B$7,-$B$8*LN(C34),-$B$9*LN(C34))</x:f>
+        <x:v>0.4101868401398489</x:v>
       </x:c>
       <x:c r="F34" s="13"/>
       <x:c r="G34" s="13"/>
@@ -5189,11 +5296,12 @@
         <x:v>0.622316270484589</x:v>
       </x:c>
       <x:c r="D35" s="10" t="n">
+        <x:f>IF(B35&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E35" s="11" t="n">
-        <x:f>IF(B35&lt;=$B$7,-LN(C35)/$B$8,-LN(C35)/$B$9)</x:f>
-        <x:v>31.966018047763548</x:v>
+        <x:f>IF(B35&lt;=$B$7,-$B$8*LN(C35),-$B$9*LN(C35))</x:f>
+        <x:v>31.864998242331424</x:v>
       </x:c>
       <x:c r="F35" s="13"/>
       <x:c r="G35" s="13"/>
@@ -5217,11 +5325,12 @@
         <x:v>0.1425965855596587</x:v>
       </x:c>
       <x:c r="D36" s="10" t="n">
+        <x:f>IF(B36&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E36" s="11" t="n">
-        <x:f>IF(B36&lt;=$B$7,-LN(C36)/$B$8,-LN(C36)/$B$9)</x:f>
-        <x:v>8.305395346769638</x:v>
+        <x:f>IF(B36&lt;=$B$7,-$B$8*LN(C36),-$B$9*LN(C36))</x:f>
+        <x:v>8.307061600717109</x:v>
       </x:c>
       <x:c r="F36" s="13"/>
       <x:c r="G36" s="13"/>
@@ -5245,11 +5354,12 @@
         <x:v>0.003698528162203729</x:v>
       </x:c>
       <x:c r="D37" s="10" t="n">
+        <x:f>IF(B37&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E37" s="11" t="n">
-        <x:f>IF(B37&lt;=$B$7,-LN(C37)/$B$8,-LN(C37)/$B$9)</x:f>
-        <x:v>23.878353393968222</x:v>
+        <x:f>IF(B37&lt;=$B$7,-$B$8*LN(C37),-$B$9*LN(C37))</x:f>
+        <x:v>23.88314394263455</x:v>
       </x:c>
       <x:c r="F37" s="13"/>
       <x:c r="G37" s="13"/>
@@ -5273,11 +5383,12 @@
         <x:v>0.7582989250076935</x:v>
       </x:c>
       <x:c r="D38" s="10" t="n">
+        <x:f>IF(B38&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E38" s="11" t="n">
-        <x:f>IF(B38&lt;=$B$7,-LN(C38)/$B$8,-LN(C38)/$B$9)</x:f>
-        <x:v>1.17978888201426</x:v>
+        <x:f>IF(B38&lt;=$B$7,-$B$8*LN(C38),-$B$9*LN(C38))</x:f>
+        <x:v>1.1800255748867554</x:v>
       </x:c>
       <x:c r="F38" s="13"/>
       <x:c r="G38" s="13"/>
@@ -5301,11 +5412,12 @@
         <x:v>0.7502792937448248</x:v>
       </x:c>
       <x:c r="D39" s="10" t="n">
+        <x:f>IF(B39&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E39" s="11" t="n">
-        <x:f>IF(B39&lt;=$B$7,-LN(C39)/$B$8,-LN(C39)/$B$9)</x:f>
-        <x:v>1.2251256896473322</x:v>
+        <x:f>IF(B39&lt;=$B$7,-$B$8*LN(C39),-$B$9*LN(C39))</x:f>
+        <x:v>1.2253714781295524</x:v>
       </x:c>
       <x:c r="F39" s="13"/>
       <x:c r="G39" s="13"/>
@@ -5329,11 +5441,12 @@
         <x:v>0.3649947791127488</x:v>
       </x:c>
       <x:c r="D40" s="10" t="n">
+        <x:f>IF(B40&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E40" s="11" t="n">
-        <x:f>IF(B40&lt;=$B$7,-LN(C40)/$B$8,-LN(C40)/$B$9)</x:f>
-        <x:v>4.297696682820373</x:v>
+        <x:f>IF(B40&lt;=$B$7,-$B$8*LN(C40),-$B$9*LN(C40))</x:f>
+        <x:v>4.298558899941147</x:v>
       </x:c>
       <x:c r="F40" s="13"/>
       <x:c r="G40" s="13"/>
@@ -5357,11 +5470,12 @@
         <x:v>0.6587087385123596</x:v>
       </x:c>
       <x:c r="D41" s="10" t="n">
+        <x:f>IF(B41&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E41" s="11" t="n">
-        <x:f>IF(B41&lt;=$B$7,-LN(C41)/$B$8,-LN(C41)/$B$9)</x:f>
-        <x:v>1.7801619955872832</x:v>
+        <x:f>IF(B41&lt;=$B$7,-$B$8*LN(C41),-$B$9*LN(C41))</x:f>
+        <x:v>1.7805191371595308</x:v>
       </x:c>
       <x:c r="F41" s="13"/>
       <x:c r="G41" s="13"/>
@@ -5385,11 +5499,12 @@
         <x:v>0.176397078554146</x:v>
       </x:c>
       <x:c r="D42" s="10" t="n">
+        <x:f>IF(B42&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E42" s="11" t="n">
-        <x:f>IF(B42&lt;=$B$7,-LN(C42)/$B$8,-LN(C42)/$B$9)</x:f>
-        <x:v>7.398338384940139</x:v>
+        <x:f>IF(B42&lt;=$B$7,-$B$8*LN(C42),-$B$9*LN(C42))</x:f>
+        <x:v>7.399822662331392</x:v>
       </x:c>
       <x:c r="F42" s="13"/>
       <x:c r="G42" s="13"/>
@@ -5413,11 +5528,12 @@
         <x:v>0.08841550664510578</x:v>
       </x:c>
       <x:c r="D43" s="10" t="n">
+        <x:f>IF(B43&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E43" s="11" t="n">
-        <x:f>IF(B43&lt;=$B$7,-LN(C43)/$B$8,-LN(C43)/$B$9)</x:f>
-        <x:v>10.34353019757691</x:v>
+        <x:f>IF(B43&lt;=$B$7,-$B$8*LN(C43),-$B$9*LN(C43))</x:f>
+        <x:v>10.34560534840392</x:v>
       </x:c>
       <x:c r="F43" s="13"/>
       <x:c r="G43" s="13"/>
@@ -5441,11 +5557,12 @@
         <x:v>0.07437442417722195</x:v>
       </x:c>
       <x:c r="D44" s="10" t="n">
+        <x:f>IF(B44&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E44" s="11" t="n">
-        <x:f>IF(B44&lt;=$B$7,-LN(C44)/$B$8,-LN(C44)/$B$9)</x:f>
-        <x:v>11.080948310973097</x:v>
+        <x:f>IF(B44&lt;=$B$7,-$B$8*LN(C44),-$B$9*LN(C44))</x:f>
+        <x:v>11.083171404889036</x:v>
       </x:c>
       <x:c r="F44" s="13"/>
       <x:c r="G44" s="13"/>
@@ -5469,11 +5586,12 @@
         <x:v>0.719480250380002</x:v>
       </x:c>
       <x:c r="D45" s="10" t="n">
+        <x:f>IF(B45&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E45" s="11" t="n">
-        <x:f>IF(B45&lt;=$B$7,-LN(C45)/$B$8,-LN(C45)/$B$9)</x:f>
-        <x:v>1.4038628266723516</x:v>
+        <x:f>IF(B45&lt;=$B$7,-$B$8*LN(C45),-$B$9*LN(C45))</x:f>
+        <x:v>1.4041444739484876</x:v>
       </x:c>
       <x:c r="F45" s="13"/>
       <x:c r="G45" s="13"/>
@@ -5497,11 +5615,12 @@
         <x:v>0.12707852839957923</x:v>
       </x:c>
       <x:c r="D46" s="10" t="n">
+        <x:f>IF(B46&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E46" s="11" t="n">
-        <x:f>IF(B46&lt;=$B$7,-LN(C46)/$B$8,-LN(C46)/$B$9)</x:f>
-        <x:v>8.79668407155583</x:v>
+        <x:f>IF(B46&lt;=$B$7,-$B$8*LN(C46),-$B$9*LN(C46))</x:f>
+        <x:v>8.798448889357621</x:v>
       </x:c>
       <x:c r="F46" s="13"/>
       <x:c r="G46" s="13"/>
@@ -5525,11 +5644,12 @@
         <x:v>0.05367322766687721</x:v>
       </x:c>
       <x:c r="D47" s="10" t="n">
+        <x:f>IF(B47&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E47" s="11" t="n">
-        <x:f>IF(B47&lt;=$B$7,-LN(C47)/$B$8,-LN(C47)/$B$9)</x:f>
-        <x:v>12.471897634111532</x:v>
+        <x:f>IF(B47&lt;=$B$7,-$B$8*LN(C47),-$B$9*LN(C47))</x:f>
+        <x:v>12.474399784556828</x:v>
       </x:c>
       <x:c r="F47" s="13"/>
       <x:c r="G47" s="13"/>
@@ -5553,11 +5673,12 @@
         <x:v>0.701798219117336</x:v>
       </x:c>
       <x:c r="D48" s="10" t="n">
+        <x:f>IF(B48&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E48" s="11" t="n">
-        <x:f>IF(B48&lt;=$B$7,-LN(C48)/$B$8,-LN(C48)/$B$9)</x:f>
-        <x:v>1.5099677809764511</x:v>
+        <x:f>IF(B48&lt;=$B$7,-$B$8*LN(C48),-$B$9*LN(C48))</x:f>
+        <x:v>1.5102707153547144</x:v>
       </x:c>
       <x:c r="F48" s="13"/>
       <x:c r="G48" s="13"/>
@@ -5581,11 +5702,12 @@
         <x:v>0.42428096232470125</x:v>
       </x:c>
       <x:c r="D49" s="10" t="n">
+        <x:f>IF(B49&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E49" s="11" t="n">
-        <x:f>IF(B49&lt;=$B$7,-LN(C49)/$B$8,-LN(C49)/$B$9)</x:f>
-        <x:v>3.655890623787392</x:v>
+        <x:f>IF(B49&lt;=$B$7,-$B$8*LN(C49),-$B$9*LN(C49))</x:f>
+        <x:v>3.6566240798035197</x:v>
       </x:c>
       <x:c r="F49" s="13"/>
       <x:c r="G49" s="13"/>
@@ -5609,11 +5731,12 @@
         <x:v>0.563165006111376</x:v>
       </x:c>
       <x:c r="D50" s="10" t="n">
+        <x:f>IF(B50&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E50" s="11" t="n">
-        <x:f>IF(B50&lt;=$B$7,-LN(C50)/$B$8,-LN(C50)/$B$9)</x:f>
-        <x:v>2.4483884236835336</x:v>
+        <x:f>IF(B50&lt;=$B$7,-$B$8*LN(C50),-$B$9*LN(C50))</x:f>
+        <x:v>2.4488796268960926</x:v>
       </x:c>
       <x:c r="F50" s="13"/>
       <x:c r="G50" s="13"/>
@@ -5637,11 +5760,12 @@
         <x:v>0.5303469666978344</x:v>
       </x:c>
       <x:c r="D51" s="10" t="n">
+        <x:f>IF(B51&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E51" s="11" t="n">
-        <x:f>IF(B51&lt;=$B$7,-LN(C51)/$B$8,-LN(C51)/$B$9)</x:f>
-        <x:v>2.704411910335129</x:v>
+        <x:f>IF(B51&lt;=$B$7,-$B$8*LN(C51),-$B$9*LN(C51))</x:f>
+        <x:v>2.7049544777666643</x:v>
       </x:c>
       <x:c r="F51" s="13"/>
       <x:c r="G51" s="13"/>
@@ -5665,11 +5789,12 @@
         <x:v>0.5973352099535987</x:v>
       </x:c>
       <x:c r="D52" s="10" t="n">
+        <x:f>IF(B52&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E52" s="11" t="n">
-        <x:f>IF(B52&lt;=$B$7,-LN(C52)/$B$8,-LN(C52)/$B$9)</x:f>
-        <x:v>2.1972066192522552</x:v>
+        <x:f>IF(B52&lt;=$B$7,-$B$8*LN(C52),-$B$9*LN(C52))</x:f>
+        <x:v>2.1976474295990087</x:v>
       </x:c>
       <x:c r="F52" s="13"/>
       <x:c r="G52" s="13"/>
@@ -5693,11 +5818,12 @@
         <x:v>0.7609515268122777</x:v>
       </x:c>
       <x:c r="D53" s="10" t="n">
+        <x:f>IF(B53&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E53" s="11" t="n">
-        <x:f>IF(B53&lt;=$B$7,-LN(C53)/$B$8,-LN(C53)/$B$9)</x:f>
-        <x:v>1.1648985834512506</x:v>
+        <x:f>IF(B53&lt;=$B$7,-$B$8*LN(C53),-$B$9*LN(C53))</x:f>
+        <x:v>1.1651322889862716</x:v>
       </x:c>
       <x:c r="F53" s="13"/>
       <x:c r="G53" s="13"/>
@@ -5721,11 +5847,12 @@
         <x:v>0.052773653413169086</x:v>
       </x:c>
       <x:c r="D54" s="10" t="n">
+        <x:f>IF(B54&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E54" s="11" t="n">
-        <x:f>IF(B54&lt;=$B$7,-LN(C54)/$B$8,-LN(C54)/$B$9)</x:f>
-        <x:v>12.543970981544259</x:v>
+        <x:f>IF(B54&lt;=$B$7,-$B$8*LN(C54),-$B$9*LN(C54))</x:f>
+        <x:v>12.546487591566091</x:v>
       </x:c>
       <x:c r="F54" s="13"/>
       <x:c r="G54" s="13"/>
@@ -5749,11 +5876,12 @@
         <x:v>0.8251555500319228</x:v>
       </x:c>
       <x:c r="D55" s="10" t="n">
+        <x:f>IF(B55&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E55" s="11" t="n">
-        <x:f>IF(B55&lt;=$B$7,-LN(C55)/$B$8,-LN(C55)/$B$9)</x:f>
-        <x:v>0.819494560843446</x:v>
+        <x:f>IF(B55&lt;=$B$7,-$B$8*LN(C55),-$B$9*LN(C55))</x:f>
+        <x:v>0.8196589703615873</x:v>
       </x:c>
       <x:c r="F55" s="13"/>
       <x:c r="G55" s="13"/>
@@ -5777,11 +5905,12 @@
         <x:v>0.4382639153627679</x:v>
       </x:c>
       <x:c r="D56" s="10" t="n">
+        <x:f>IF(B56&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E56" s="11" t="n">
-        <x:f>IF(B56&lt;=$B$7,-LN(C56)/$B$8,-LN(C56)/$B$9)</x:f>
-        <x:v>3.517624583383026</x:v>
+        <x:f>IF(B56&lt;=$B$7,-$B$8*LN(C56),-$B$9*LN(C56))</x:f>
+        <x:v>3.5183303000410606</x:v>
       </x:c>
       <x:c r="F56" s="13"/>
       <x:c r="G56" s="13"/>
@@ -5805,11 +5934,12 @@
         <x:v>0.45323347521480173</x:v>
       </x:c>
       <x:c r="D57" s="10" t="n">
+        <x:f>IF(B57&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E57" s="11" t="n">
-        <x:f>IF(B57&lt;=$B$7,-LN(C57)/$B$8,-LN(C57)/$B$9)</x:f>
-        <x:v>3.3744090731456207</x:v>
+        <x:f>IF(B57&lt;=$B$7,-$B$8*LN(C57),-$B$9*LN(C57))</x:f>
+        <x:v>3.375086057467709</x:v>
       </x:c>
       <x:c r="F57" s="13"/>
       <x:c r="G57" s="13"/>
@@ -5833,11 +5963,12 @@
         <x:v>0.46877014718484133</x:v>
       </x:c>
       <x:c r="D58" s="10" t="n">
+        <x:f>IF(B58&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E58" s="11" t="n">
-        <x:f>IF(B58&lt;=$B$7,-LN(C58)/$B$8,-LN(C58)/$B$9)</x:f>
-        <x:v>3.230685912622242</x:v>
+        <x:f>IF(B58&lt;=$B$7,-$B$8*LN(C58),-$B$9*LN(C58))</x:f>
+        <x:v>3.231334062762023</x:v>
       </x:c>
       <x:c r="F58" s="13"/>
       <x:c r="G58" s="13"/>
@@ -5861,11 +5992,12 @@
         <x:v>0.1848202453693375</x:v>
       </x:c>
       <x:c r="D59" s="10" t="n">
+        <x:f>IF(B59&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E59" s="11" t="n">
-        <x:f>IF(B59&lt;=$B$7,-LN(C59)/$B$8,-LN(C59)/$B$9)</x:f>
-        <x:v>7.1994333183353545</x:v>
+        <x:f>IF(B59&lt;=$B$7,-$B$8*LN(C59),-$B$9*LN(C59))</x:f>
+        <x:v>7.200877690780659</x:v>
       </x:c>
       <x:c r="F59" s="13"/>
       <x:c r="G59" s="13"/>
@@ -5889,11 +6021,12 @@
         <x:v>0.6997754516778514</x:v>
       </x:c>
       <x:c r="D60" s="10" t="n">
+        <x:f>IF(B60&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E60" s="11" t="n">
-        <x:f>IF(B60&lt;=$B$7,-LN(C60)/$B$8,-LN(C60)/$B$9)</x:f>
-        <x:v>1.522275869272708</x:v>
+        <x:f>IF(B60&lt;=$B$7,-$B$8*LN(C60),-$B$9*LN(C60))</x:f>
+        <x:v>1.522581272937484</x:v>
       </x:c>
       <x:c r="F60" s="13"/>
       <x:c r="G60" s="13"/>
@@ -5917,11 +6050,12 @@
         <x:v>0.5095973428105935</x:v>
       </x:c>
       <x:c r="D61" s="10" t="n">
+        <x:f>IF(B61&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E61" s="11" t="n">
-        <x:f>IF(B61&lt;=$B$7,-LN(C61)/$B$8,-LN(C61)/$B$9)</x:f>
-        <x:v>45.433441258250575</x:v>
+        <x:f>IF(B61&lt;=$B$7,-$B$8*LN(C61),-$B$9*LN(C61))</x:f>
+        <x:v>45.28986136696845</x:v>
       </x:c>
       <x:c r="F61" s="13"/>
       <x:c r="G61" s="13"/>
@@ -5945,11 +6079,12 @@
         <x:v>0.7407218244625255</x:v>
       </x:c>
       <x:c r="D62" s="10" t="n">
+        <x:f>IF(B62&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E62" s="11" t="n">
-        <x:f>IF(B62&lt;=$B$7,-LN(C62)/$B$8,-LN(C62)/$B$9)</x:f>
-        <x:v>1.2797934356640768</x:v>
+        <x:f>IF(B62&lt;=$B$7,-$B$8*LN(C62),-$B$9*LN(C62))</x:f>
+        <x:v>1.2800501917575662</x:v>
       </x:c>
       <x:c r="F62" s="13"/>
       <x:c r="G62" s="13"/>
@@ -5973,11 +6108,12 @@
         <x:v>0.876142886816524</x:v>
       </x:c>
       <x:c r="D63" s="10" t="n">
+        <x:f>IF(B63&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E63" s="11" t="n">
-        <x:f>IF(B63&lt;=$B$7,-LN(C63)/$B$8,-LN(C63)/$B$9)</x:f>
-        <x:v>0.5638290306961905</x:v>
+        <x:f>IF(B63&lt;=$B$7,-$B$8*LN(C63),-$B$9*LN(C63))</x:f>
+        <x:v>0.5639421478096897</x:v>
       </x:c>
       <x:c r="F63" s="13"/>
       <x:c r="G63" s="13"/>
@@ -6001,11 +6137,12 @@
         <x:v>0.188176657888107</x:v>
       </x:c>
       <x:c r="D64" s="10" t="n">
+        <x:f>IF(B64&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E64" s="11" t="n">
-        <x:f>IF(B64&lt;=$B$7,-LN(C64)/$B$8,-LN(C64)/$B$9)</x:f>
-        <x:v>112.57524350190866</x:v>
+        <x:f>IF(B64&lt;=$B$7,-$B$8*LN(C64),-$B$9*LN(C64))</x:f>
+        <x:v>112.21948041693373</x:v>
       </x:c>
       <x:c r="F64" s="13"/>
       <x:c r="G64" s="13"/>
@@ -6029,11 +6166,12 @@
         <x:v>0.3345707937842235</x:v>
       </x:c>
       <x:c r="D65" s="10" t="n">
+        <x:f>IF(B65&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E65" s="11" t="n">
-        <x:f>IF(B65&lt;=$B$7,-LN(C65)/$B$8,-LN(C65)/$B$9)</x:f>
-        <x:v>73.7914928213679</x:v>
+        <x:f>IF(B65&lt;=$B$7,-$B$8*LN(C65),-$B$9*LN(C65))</x:f>
+        <x:v>73.55829511009144</x:v>
       </x:c>
       <x:c r="F65" s="13"/>
       <x:c r="G65" s="13"/>
@@ -6057,11 +6195,12 @@
         <x:v>0.6693508074386045</x:v>
       </x:c>
       <x:c r="D66" s="10" t="n">
+        <x:f>IF(B66&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E66" s="11" t="n">
-        <x:f>IF(B66&lt;=$B$7,-LN(C66)/$B$8,-LN(C66)/$B$9)</x:f>
-        <x:v>1.7118215047905334</x:v>
+        <x:f>IF(B66&lt;=$B$7,-$B$8*LN(C66),-$B$9*LN(C66))</x:f>
+        <x:v>1.7121649356834205</x:v>
       </x:c>
       <x:c r="F66" s="13"/>
       <x:c r="G66" s="13"/>
@@ -6085,11 +6224,12 @@
         <x:v>0.8285839998861775</x:v>
       </x:c>
       <x:c r="D67" s="10" t="n">
+        <x:f>IF(B67&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E67" s="11" t="n">
-        <x:f>IF(B67&lt;=$B$7,-LN(C67)/$B$8,-LN(C67)/$B$9)</x:f>
-        <x:v>0.8018141810881328</x:v>
+        <x:f>IF(B67&lt;=$B$7,-$B$8*LN(C67),-$B$9*LN(C67))</x:f>
+        <x:v>0.8019750435141335</x:v>
       </x:c>
       <x:c r="F67" s="13"/>
       <x:c r="G67" s="13"/>
@@ -6113,11 +6253,12 @@
         <x:v>0.6365932206390426</x:v>
       </x:c>
       <x:c r="D68" s="10" t="n">
+        <x:f>IF(B68&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E68" s="11" t="n">
-        <x:f>IF(B68&lt;=$B$7,-LN(C68)/$B$8,-LN(C68)/$B$9)</x:f>
-        <x:v>1.9257845264723779</x:v>
+        <x:f>IF(B68&lt;=$B$7,-$B$8*LN(C68),-$B$9*LN(C68))</x:f>
+        <x:v>1.9261708832844544</x:v>
       </x:c>
       <x:c r="F68" s="13"/>
       <x:c r="G68" s="13"/>
@@ -6141,11 +6282,12 @@
         <x:v>0.4025667462265119</x:v>
       </x:c>
       <x:c r="D69" s="10" t="n">
+        <x:f>IF(B69&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E69" s="11" t="n">
-        <x:f>IF(B69&lt;=$B$7,-LN(C69)/$B$8,-LN(C69)/$B$9)</x:f>
-        <x:v>3.8799064880974403</x:v>
+        <x:f>IF(B69&lt;=$B$7,-$B$8*LN(C69),-$B$9*LN(C69))</x:f>
+        <x:v>3.8806848868649504</x:v>
       </x:c>
       <x:c r="F69" s="13"/>
       <x:c r="G69" s="13"/>
@@ -6169,11 +6311,12 @@
         <x:v>0.8034871284617111</x:v>
       </x:c>
       <x:c r="D70" s="10" t="n">
+        <x:f>IF(B70&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E70" s="11" t="n">
-        <x:f>IF(B70&lt;=$B$7,-LN(C70)/$B$8,-LN(C70)/$B$9)</x:f>
-        <x:v>0.9329662108823151</x:v>
+        <x:f>IF(B70&lt;=$B$7,-$B$8*LN(C70),-$B$9*LN(C70))</x:f>
+        <x:v>0.9331533854317294</x:v>
       </x:c>
       <x:c r="F70" s="13"/>
       <x:c r="G70" s="13"/>
@@ -6197,11 +6340,12 @@
         <x:v>0.8393409264972433</x:v>
       </x:c>
       <x:c r="D71" s="10" t="n">
+        <x:f>IF(B71&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E71" s="11" t="n">
-        <x:f>IF(B71&lt;=$B$7,-LN(C71)/$B$8,-LN(C71)/$B$9)</x:f>
-        <x:v>0.7468122413524607</x:v>
+        <x:f>IF(B71&lt;=$B$7,-$B$8*LN(C71),-$B$9*LN(C71))</x:f>
+        <x:v>0.7469620691202209</x:v>
       </x:c>
       <x:c r="F71" s="13"/>
       <x:c r="G71" s="13"/>
@@ -6225,11 +6369,12 @@
         <x:v>0.36317279923241585</x:v>
       </x:c>
       <x:c r="D72" s="10" t="n">
+        <x:f>IF(B72&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E72" s="11" t="n">
-        <x:f>IF(B72&lt;=$B$7,-LN(C72)/$B$8,-LN(C72)/$B$9)</x:f>
-        <x:v>4.3190356513560415</x:v>
+        <x:f>IF(B72&lt;=$B$7,-$B$8*LN(C72),-$B$9*LN(C72))</x:f>
+        <x:v>4.319902149566285</x:v>
       </x:c>
       <x:c r="F72" s="13"/>
       <x:c r="G72" s="13"/>
@@ -6253,11 +6398,12 @@
         <x:v>0.49421149713452905</x:v>
       </x:c>
       <x:c r="D73" s="10" t="n">
+        <x:f>IF(B73&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E73" s="11" t="n">
-        <x:f>IF(B73&lt;=$B$7,-LN(C73)/$B$8,-LN(C73)/$B$9)</x:f>
-        <x:v>3.0053224563454513</x:v>
+        <x:f>IF(B73&lt;=$B$7,-$B$8*LN(C73),-$B$9*LN(C73))</x:f>
+        <x:v>3.0059253933758066</x:v>
       </x:c>
       <x:c r="F73" s="13"/>
       <x:c r="G73" s="13"/>
@@ -6281,11 +6427,12 @@
         <x:v>0.3795218550367281</x:v>
       </x:c>
       <x:c r="D74" s="10" t="n">
+        <x:f>IF(B74&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E74" s="11" t="n">
-        <x:f>IF(B74&lt;=$B$7,-LN(C74)/$B$8,-LN(C74)/$B$9)</x:f>
-        <x:v>4.131271438512763</x:v>
+        <x:f>IF(B74&lt;=$B$7,-$B$8*LN(C74),-$B$9*LN(C74))</x:f>
+        <x:v>4.132100266889388</x:v>
       </x:c>
       <x:c r="F74" s="13"/>
       <x:c r="G74" s="13"/>
@@ -6309,11 +6456,12 @@
         <x:v>0.3409259499749169</x:v>
       </x:c>
       <x:c r="D75" s="10" t="n">
+        <x:f>IF(B75&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E75" s="11" t="n">
-        <x:f>IF(B75&lt;=$B$7,-LN(C75)/$B$8,-LN(C75)/$B$9)</x:f>
-        <x:v>4.588585940115007</x:v>
+        <x:f>IF(B75&lt;=$B$7,-$B$8*LN(C75),-$B$9*LN(C75))</x:f>
+        <x:v>4.589506516332851</x:v>
       </x:c>
       <x:c r="F75" s="13"/>
       <x:c r="G75" s="13"/>
@@ -6337,11 +6485,12 @@
         <x:v>0.9917881506262347</x:v>
       </x:c>
       <x:c r="D76" s="10" t="n">
+        <x:f>IF(B76&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E76" s="11" t="n">
-        <x:f>IF(B76&lt;=$B$7,-LN(C76)/$B$8,-LN(C76)/$B$9)</x:f>
-        <x:v>0.035160947440133844</x:v>
+        <x:f>IF(B76&lt;=$B$7,-$B$8*LN(C76),-$B$9*LN(C76))</x:f>
+        <x:v>0.03516800153750342</x:v>
       </x:c>
       <x:c r="F76" s="13"/>
       <x:c r="G76" s="13"/>
@@ -6365,11 +6514,12 @@
         <x:v>0.4951728474115953</x:v>
       </x:c>
       <x:c r="D77" s="10" t="n">
+        <x:f>IF(B77&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E77" s="11" t="n">
-        <x:f>IF(B77&lt;=$B$7,-LN(C77)/$B$8,-LN(C77)/$B$9)</x:f>
-        <x:v>2.997035843738768</x:v>
+        <x:f>IF(B77&lt;=$B$7,-$B$8*LN(C77),-$B$9*LN(C77))</x:f>
+        <x:v>2.9976371182834267</x:v>
       </x:c>
       <x:c r="F77" s="13"/>
       <x:c r="G77" s="13"/>
@@ -6393,11 +6543,12 @@
         <x:v>0.3233602148247883</x:v>
       </x:c>
       <x:c r="D78" s="10" t="n">
+        <x:f>IF(B78&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E78" s="11" t="n">
-        <x:f>IF(B78&lt;=$B$7,-LN(C78)/$B$8,-LN(C78)/$B$9)</x:f>
-        <x:v>4.814151429952072</x:v>
+        <x:f>IF(B78&lt;=$B$7,-$B$8*LN(C78),-$B$9*LN(C78))</x:f>
+        <x:v>4.815117259811935</x:v>
       </x:c>
       <x:c r="F78" s="13"/>
       <x:c r="G78" s="13"/>
@@ -6421,11 +6572,12 @@
         <x:v>0.7312444200506434</x:v>
       </x:c>
       <x:c r="D79" s="10" t="n">
+        <x:f>IF(B79&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E79" s="11" t="n">
-        <x:f>IF(B79&lt;=$B$7,-LN(C79)/$B$8,-LN(C79)/$B$9)</x:f>
-        <x:v>1.3347042445679296</x:v>
+        <x:f>IF(B79&lt;=$B$7,-$B$8*LN(C79),-$B$9*LN(C79))</x:f>
+        <x:v>1.3349720170367119</x:v>
       </x:c>
       <x:c r="F79" s="13"/>
       <x:c r="G79" s="13"/>
@@ -6449,11 +6601,12 @@
         <x:v>0.23524025443475693</x:v>
       </x:c>
       <x:c r="D80" s="10" t="n">
+        <x:f>IF(B80&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E80" s="11" t="n">
-        <x:f>IF(B80&lt;=$B$7,-LN(C80)/$B$8,-LN(C80)/$B$9)</x:f>
-        <x:v>6.170824701793845</x:v>
+        <x:f>IF(B80&lt;=$B$7,-$B$8*LN(C80),-$B$9*LN(C80))</x:f>
+        <x:v>6.17206271161628</x:v>
       </x:c>
       <x:c r="F80" s="13"/>
       <x:c r="G80" s="13"/>
@@ -6477,11 +6630,12 @@
         <x:v>0.7574882268672809</x:v>
       </x:c>
       <x:c r="D81" s="10" t="n">
+        <x:f>IF(B81&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E81" s="11" t="n">
-        <x:f>IF(B81&lt;=$B$7,-LN(C81)/$B$8,-LN(C81)/$B$9)</x:f>
-        <x:v>1.1843501046886997</x:v>
+        <x:f>IF(B81&lt;=$B$7,-$B$8*LN(C81),-$B$9*LN(C81))</x:f>
+        <x:v>1.1845877126477107</x:v>
       </x:c>
       <x:c r="F81" s="13"/>
       <x:c r="G81" s="13"/>
@@ -6505,11 +6659,12 @@
         <x:v>0.3148747206432745</x:v>
       </x:c>
       <x:c r="D82" s="10" t="n">
+        <x:f>IF(B82&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E82" s="11" t="n">
-        <x:f>IF(B82&lt;=$B$7,-LN(C82)/$B$8,-LN(C82)/$B$9)</x:f>
-        <x:v>4.927543435404313</x:v>
+        <x:f>IF(B82&lt;=$B$7,-$B$8*LN(C82),-$B$9*LN(C82))</x:f>
+        <x:v>4.9285320143169065</x:v>
       </x:c>
       <x:c r="F82" s="13"/>
       <x:c r="G82" s="13"/>
@@ -6533,11 +6688,12 @@
         <x:v>0.2661728778621182</x:v>
       </x:c>
       <x:c r="D83" s="10" t="n">
+        <x:f>IF(B83&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E83" s="11" t="n">
-        <x:f>IF(B83&lt;=$B$7,-LN(C83)/$B$8,-LN(C83)/$B$9)</x:f>
-        <x:v>5.644039968694115</x:v>
+        <x:f>IF(B83&lt;=$B$7,-$B$8*LN(C83),-$B$9*LN(C83))</x:f>
+        <x:v>5.6451722933439195</x:v>
       </x:c>
       <x:c r="F83" s="13"/>
       <x:c r="G83" s="13"/>
@@ -6561,11 +6717,12 @@
         <x:v>0.7409614379284903</x:v>
       </x:c>
       <x:c r="D84" s="10" t="n">
+        <x:f>IF(B84&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E84" s="11" t="n">
-        <x:f>IF(B84&lt;=$B$7,-LN(C84)/$B$8,-LN(C84)/$B$9)</x:f>
-        <x:v>1.2784142709794282</x:v>
+        <x:f>IF(B84&lt;=$B$7,-$B$8*LN(C84),-$B$9*LN(C84))</x:f>
+        <x:v>1.2786707503806587</x:v>
       </x:c>
       <x:c r="F84" s="13"/>
       <x:c r="G84" s="13"/>
@@ -6589,11 +6746,12 @@
         <x:v>0.023392819217406213</x:v>
       </x:c>
       <x:c r="D85" s="10" t="n">
+        <x:f>IF(B85&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E85" s="11" t="n">
-        <x:f>IF(B85&lt;=$B$7,-LN(C85)/$B$8,-LN(C85)/$B$9)</x:f>
-        <x:v>16.01319331455243</x:v>
+        <x:f>IF(B85&lt;=$B$7,-$B$8*LN(C85),-$B$9*LN(C85))</x:f>
+        <x:v>16.016405930624025</x:v>
       </x:c>
       <x:c r="F85" s="13"/>
       <x:c r="G85" s="13"/>
@@ -6617,11 +6775,12 @@
         <x:v>0.9148582954658195</x:v>
       </x:c>
       <x:c r="D86" s="10" t="n">
+        <x:f>IF(B86&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E86" s="11" t="n">
-        <x:f>IF(B86&lt;=$B$7,-LN(C86)/$B$8,-LN(C86)/$B$9)</x:f>
-        <x:v>0.37944813843292735</x:v>
+        <x:f>IF(B86&lt;=$B$7,-$B$8*LN(C86),-$B$9*LN(C86))</x:f>
+        <x:v>0.3795242644849846</x:v>
       </x:c>
       <x:c r="F86" s="13"/>
       <x:c r="G86" s="13"/>
@@ -6645,11 +6804,12 @@
         <x:v>0.5146371809532866</x:v>
       </x:c>
       <x:c r="D87" s="10" t="n">
+        <x:f>IF(B87&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E87" s="11" t="n">
-        <x:f>IF(B87&lt;=$B$7,-LN(C87)/$B$8,-LN(C87)/$B$9)</x:f>
-        <x:v>2.832631256722071</x:v>
+        <x:f>IF(B87&lt;=$B$7,-$B$8*LN(C87),-$B$9*LN(C87))</x:f>
+        <x:v>2.833199547913059</x:v>
       </x:c>
       <x:c r="F87" s="13"/>
       <x:c r="G87" s="13"/>
@@ -6673,11 +6833,12 @@
         <x:v>0.9992185010341927</x:v>
       </x:c>
       <x:c r="D88" s="10" t="n">
+        <x:f>IF(B88&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E88" s="11" t="n">
-        <x:f>IF(B88&lt;=$B$7,-LN(C88)/$B$8,-LN(C88)/$B$9)</x:f>
-        <x:v>0.0033337148186476564</x:v>
+        <x:f>IF(B88&lt;=$B$7,-$B$8*LN(C88),-$B$9*LN(C88))</x:f>
+        <x:v>0.0033343836387633025</x:v>
       </x:c>
       <x:c r="F88" s="13"/>
       <x:c r="G88" s="13"/>
@@ -6701,11 +6862,12 @@
         <x:v>0.9116476870840415</x:v>
       </x:c>
       <x:c r="D89" s="10" t="n">
+        <x:f>IF(B89&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E89" s="11" t="n">
-        <x:f>IF(B89&lt;=$B$7,-LN(C89)/$B$8,-LN(C89)/$B$9)</x:f>
-        <x:v>0.3944390126901184</x:v>
+        <x:f>IF(B89&lt;=$B$7,-$B$8*LN(C89),-$B$9*LN(C89))</x:f>
+        <x:v>0.39451814625745507</x:v>
       </x:c>
       <x:c r="F89" s="13"/>
       <x:c r="G89" s="13"/>
@@ -6729,11 +6891,12 @@
         <x:v>0.7544773974223062</x:v>
       </x:c>
       <x:c r="D90" s="10" t="n">
+        <x:f>IF(B90&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E90" s="11" t="n">
-        <x:f>IF(B90&lt;=$B$7,-LN(C90)/$B$8,-LN(C90)/$B$9)</x:f>
-        <x:v>1.2013327402268068</x:v>
+        <x:f>IF(B90&lt;=$B$7,-$B$8*LN(C90),-$B$9*LN(C90))</x:f>
+        <x:v>1.2015737552943686</x:v>
       </x:c>
       <x:c r="F90" s="13"/>
       <x:c r="G90" s="13"/>
@@ -6757,11 +6920,12 @@
         <x:v>0.3761906282743439</x:v>
       </x:c>
       <x:c r="D91" s="10" t="n">
+        <x:f>IF(B91&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E91" s="11" t="n">
-        <x:f>IF(B91&lt;=$B$7,-LN(C91)/$B$8,-LN(C91)/$B$9)</x:f>
-        <x:v>4.168864759381816</x:v>
+        <x:f>IF(B91&lt;=$B$7,-$B$8*LN(C91),-$B$9*LN(C91))</x:f>
+        <x:v>4.169701129846046</x:v>
       </x:c>
       <x:c r="F91" s="13"/>
       <x:c r="G91" s="13"/>
@@ -6785,11 +6949,12 @@
         <x:v>0.31381584133487195</x:v>
       </x:c>
       <x:c r="D92" s="10" t="n">
+        <x:f>IF(B92&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E92" s="11" t="n">
-        <x:f>IF(B92&lt;=$B$7,-LN(C92)/$B$8,-LN(C92)/$B$9)</x:f>
-        <x:v>78.10762994676445</x:v>
+        <x:f>IF(B92&lt;=$B$7,-$B$8*LN(C92),-$B$9*LN(C92))</x:f>
+        <x:v>77.86079227157461</x:v>
       </x:c>
       <x:c r="F92" s="13"/>
       <x:c r="G92" s="13"/>
@@ -6813,11 +6978,12 @@
         <x:v>0.9663678969955072</x:v>
       </x:c>
       <x:c r="D93" s="10" t="n">
+        <x:f>IF(B93&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E93" s="11" t="n">
-        <x:f>IF(B93&lt;=$B$7,-LN(C93)/$B$8,-LN(C93)/$B$9)</x:f>
-        <x:v>0.14587869894828634</x:v>
+        <x:f>IF(B93&lt;=$B$7,-$B$8*LN(C93),-$B$9*LN(C93))</x:f>
+        <x:v>0.1459079655813394</x:v>
       </x:c>
       <x:c r="F93" s="13"/>
       <x:c r="G93" s="13"/>
@@ -6841,11 +7007,12 @@
         <x:v>0.7872251447988674</x:v>
       </x:c>
       <x:c r="D94" s="10" t="n">
+        <x:f>IF(B94&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E94" s="11" t="n">
-        <x:f>IF(B94&lt;=$B$7,-LN(C94)/$B$8,-LN(C94)/$B$9)</x:f>
-        <x:v>1.02015432755792</x:v>
+        <x:f>IF(B94&lt;=$B$7,-$B$8*LN(C94),-$B$9*LN(C94))</x:f>
+        <x:v>1.0203589940553413</x:v>
       </x:c>
       <x:c r="F94" s="13"/>
       <x:c r="G94" s="13"/>
@@ -6869,11 +7036,12 @@
         <x:v>0.6610920851817355</x:v>
       </x:c>
       <x:c r="D95" s="10" t="n">
+        <x:f>IF(B95&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E95" s="11" t="n">
-        <x:f>IF(B95&lt;=$B$7,-LN(C95)/$B$8,-LN(C95)/$B$9)</x:f>
-        <x:v>1.7647613271094778</x:v>
+        <x:f>IF(B95&lt;=$B$7,-$B$8*LN(C95),-$B$9*LN(C95))</x:f>
+        <x:v>1.7651153789522696</x:v>
       </x:c>
       <x:c r="F95" s="13"/>
       <x:c r="G95" s="13"/>
@@ -6897,11 +7065,12 @@
         <x:v>0.8352985790697858</x:v>
       </x:c>
       <x:c r="D96" s="10" t="n">
+        <x:f>IF(B96&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E96" s="11" t="n">
-        <x:f>IF(B96&lt;=$B$7,-LN(C96)/$B$8,-LN(C96)/$B$9)</x:f>
-        <x:v>0.7673983104563501</x:v>
+        <x:f>IF(B96&lt;=$B$7,-$B$8*LN(C96),-$B$9*LN(C96))</x:f>
+        <x:v>0.767552268264581</x:v>
       </x:c>
       <x:c r="F96" s="13"/>
       <x:c r="G96" s="13"/>
@@ -6925,11 +7094,12 @@
         <x:v>0.26835064438637346</x:v>
       </x:c>
       <x:c r="D97" s="10" t="n">
+        <x:f>IF(B97&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E97" s="11" t="n">
-        <x:f>IF(B97&lt;=$B$7,-LN(C97)/$B$8,-LN(C97)/$B$9)</x:f>
-        <x:v>5.609293779735669</x:v>
+        <x:f>IF(B97&lt;=$B$7,-$B$8*LN(C97),-$B$9*LN(C97))</x:f>
+        <x:v>5.610419133498225</x:v>
       </x:c>
       <x:c r="F97" s="13"/>
       <x:c r="G97" s="13"/>
@@ -6953,11 +7123,12 @@
         <x:v>0.6033744410378858</x:v>
       </x:c>
       <x:c r="D98" s="10" t="n">
+        <x:f>IF(B98&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E98" s="11" t="n">
-        <x:f>IF(B98&lt;=$B$7,-LN(C98)/$B$8,-LN(C98)/$B$9)</x:f>
-        <x:v>2.15431152893835</x:v>
+        <x:f>IF(B98&lt;=$B$7,-$B$8*LN(C98),-$B$9*LN(C98))</x:f>
+        <x:v>2.154743733540214</x:v>
       </x:c>
       <x:c r="F98" s="13"/>
       <x:c r="G98" s="13"/>
@@ -6981,11 +7152,12 @@
         <x:v>0.23288410843815655</x:v>
       </x:c>
       <x:c r="D99" s="10" t="n">
+        <x:f>IF(B99&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E99" s="11" t="n">
-        <x:f>IF(B99&lt;=$B$7,-LN(C99)/$B$8,-LN(C99)/$B$9)</x:f>
-        <x:v>6.213749167585412</x:v>
+        <x:f>IF(B99&lt;=$B$7,-$B$8*LN(C99),-$B$9*LN(C99))</x:f>
+        <x:v>6.214995789046136</x:v>
       </x:c>
       <x:c r="F99" s="13"/>
       <x:c r="G99" s="13"/>
@@ -7009,11 +7181,12 @@
         <x:v>0.656655682134442</x:v>
       </x:c>
       <x:c r="D100" s="10" t="n">
+        <x:f>IF(B100&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E100" s="11" t="n">
-        <x:f>IF(B100&lt;=$B$7,-LN(C100)/$B$8,-LN(C100)/$B$9)</x:f>
-        <x:v>1.7934731406287732</x:v>
+        <x:f>IF(B100&lt;=$B$7,-$B$8*LN(C100),-$B$9*LN(C100))</x:f>
+        <x:v>1.7938329527238612</x:v>
       </x:c>
       <x:c r="F100" s="13"/>
       <x:c r="G100" s="13"/>
@@ -7037,11 +7210,12 @@
         <x:v>0.6089033785974607</x:v>
       </x:c>
       <x:c r="D101" s="10" t="n">
+        <x:f>IF(B101&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E101" s="11" t="n">
-        <x:f>IF(B101&lt;=$B$7,-LN(C101)/$B$8,-LN(C101)/$B$9)</x:f>
-        <x:v>2.11541571936406</x:v>
+        <x:f>IF(B101&lt;=$B$7,-$B$8*LN(C101),-$B$9*LN(C101))</x:f>
+        <x:v>2.115840120569031</x:v>
       </x:c>
       <x:c r="F101" s="13"/>
       <x:c r="G101" s="13"/>
@@ -7065,11 +7239,12 @@
         <x:v>0.8069310997379944</x:v>
       </x:c>
       <x:c r="D102" s="10" t="n">
+        <x:f>IF(B102&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E102" s="11" t="n">
-        <x:f>IF(B102&lt;=$B$7,-LN(C102)/$B$8,-LN(C102)/$B$9)</x:f>
-        <x:v>0.914728018897833</x:v>
+        <x:f>IF(B102&lt;=$B$7,-$B$8*LN(C102),-$B$9*LN(C102))</x:f>
+        <x:v>0.9149115344451022</x:v>
       </x:c>
       <x:c r="F102" s="13"/>
       <x:c r="G102" s="13"/>
@@ -7093,11 +7268,12 @@
         <x:v>0.7134710712125525</x:v>
       </x:c>
       <x:c r="D103" s="10" t="n">
+        <x:f>IF(B103&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E103" s="11" t="n">
-        <x:f>IF(B103&lt;=$B$7,-LN(C103)/$B$8,-LN(C103)/$B$9)</x:f>
-        <x:v>1.439626863993082</x:v>
+        <x:f>IF(B103&lt;=$B$7,-$B$8*LN(C103),-$B$9*LN(C103))</x:f>
+        <x:v>1.4399156863603335</x:v>
       </x:c>
       <x:c r="F103" s="13"/>
       <x:c r="G103" s="13"/>
@@ -7121,11 +7297,12 @@
         <x:v>0.9715230910805985</x:v>
       </x:c>
       <x:c r="D104" s="10" t="n">
+        <x:f>IF(B104&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E104" s="11" t="n">
-        <x:f>IF(B104&lt;=$B$7,-LN(C104)/$B$8,-LN(C104)/$B$9)</x:f>
-        <x:v>0.12319170371798885</x:v>
+        <x:f>IF(B104&lt;=$B$7,-$B$8*LN(C104),-$B$9*LN(C104))</x:f>
+        <x:v>0.12321641881631291</x:v>
       </x:c>
       <x:c r="F104" s="13"/>
       <x:c r="G104" s="13"/>
@@ -7149,11 +7326,12 @@
         <x:v>0.22617192787583917</x:v>
       </x:c>
       <x:c r="D105" s="10" t="n">
+        <x:f>IF(B105&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E105" s="11" t="n">
-        <x:f>IF(B105&lt;=$B$7,-LN(C105)/$B$8,-LN(C105)/$B$9)</x:f>
-        <x:v>6.338455687243668</x:v>
+        <x:f>IF(B105&lt;=$B$7,-$B$8*LN(C105),-$B$9*LN(C105))</x:f>
+        <x:v>6.339727327709747</x:v>
       </x:c>
       <x:c r="F105" s="13"/>
       <x:c r="G105" s="13"/>
@@ -7177,11 +7355,12 @@
         <x:v>0.4550869696540758</x:v>
       </x:c>
       <x:c r="D106" s="10" t="n">
+        <x:f>IF(B106&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E106" s="11" t="n">
-        <x:f>IF(B106&lt;=$B$7,-LN(C106)/$B$8,-LN(C106)/$B$9)</x:f>
-        <x:v>3.3570065155987834</x:v>
+        <x:f>IF(B106&lt;=$B$7,-$B$8*LN(C106),-$B$9*LN(C106))</x:f>
+        <x:v>3.357680008566277</x:v>
       </x:c>
       <x:c r="F106" s="13"/>
       <x:c r="G106" s="13"/>
@@ -7205,11 +7384,12 @@
         <x:v>0.7506972880801186</x:v>
       </x:c>
       <x:c r="D107" s="10" t="n">
+        <x:f>IF(B107&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E107" s="11" t="n">
-        <x:f>IF(B107&lt;=$B$7,-LN(C107)/$B$8,-LN(C107)/$B$9)</x:f>
-        <x:v>1.2227507270801523</x:v>
+        <x:f>IF(B107&lt;=$B$7,-$B$8*LN(C107),-$B$9*LN(C107))</x:f>
+        <x:v>1.2229960390900811</x:v>
       </x:c>
       <x:c r="F107" s="13"/>
       <x:c r="G107" s="13"/>
@@ -7233,11 +7413,12 @@
         <x:v>0.2948868441162631</x:v>
       </x:c>
       <x:c r="D108" s="10" t="n">
+        <x:f>IF(B108&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E108" s="11" t="n">
-        <x:f>IF(B108&lt;=$B$7,-LN(C108)/$B$8,-LN(C108)/$B$9)</x:f>
-        <x:v>5.2071983878506</x:v>
+        <x:f>IF(B108&lt;=$B$7,-$B$8*LN(C108),-$B$9*LN(C108))</x:f>
+        <x:v>5.208243071999488</x:v>
       </x:c>
       <x:c r="F108" s="13"/>
       <x:c r="G108" s="13"/>
@@ -7261,11 +7442,12 @@
         <x:v>0.10396862437482923</x:v>
       </x:c>
       <x:c r="D109" s="10" t="n">
+        <x:f>IF(B109&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E109" s="11" t="n">
-        <x:f>IF(B109&lt;=$B$7,-LN(C109)/$B$8,-LN(C109)/$B$9)</x:f>
-        <x:v>9.652563158870299</x:v>
+        <x:f>IF(B109&lt;=$B$7,-$B$8*LN(C109),-$B$9*LN(C109))</x:f>
+        <x:v>9.654499685765787</x:v>
       </x:c>
       <x:c r="F109" s="13"/>
       <x:c r="G109" s="13"/>
@@ -7289,11 +7471,12 @@
         <x:v>0.5601730596972629</x:v>
       </x:c>
       <x:c r="D110" s="10" t="n">
+        <x:f>IF(B110&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E110" s="11" t="n">
-        <x:f>IF(B110&lt;=$B$7,-LN(C110)/$B$8,-LN(C110)/$B$9)</x:f>
-        <x:v>2.4711029999780303</x:v>
+        <x:f>IF(B110&lt;=$B$7,-$B$8*LN(C110),-$B$9*LN(C110))</x:f>
+        <x:v>2.471598760258716</x:v>
       </x:c>
       <x:c r="F110" s="13"/>
       <x:c r="G110" s="13"/>
@@ -7317,11 +7500,12 @@
         <x:v>0.8484251400223002</x:v>
       </x:c>
       <x:c r="D111" s="10" t="n">
+        <x:f>IF(B111&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E111" s="11" t="n">
-        <x:f>IF(B111&lt;=$B$7,-LN(C111)/$B$8,-LN(C111)/$B$9)</x:f>
-        <x:v>0.7009094014968967</x:v>
+        <x:f>IF(B111&lt;=$B$7,-$B$8*LN(C111),-$B$9*LN(C111))</x:f>
+        <x:v>0.7010500200958076</x:v>
       </x:c>
       <x:c r="F111" s="13"/>
       <x:c r="G111" s="13"/>
@@ -7345,11 +7529,12 @@
         <x:v>0.7462862021056935</x:v>
       </x:c>
       <x:c r="D112" s="10" t="n">
+        <x:f>IF(B112&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E112" s="11" t="n">
-        <x:f>IF(B112&lt;=$B$7,-LN(C112)/$B$8,-LN(C112)/$B$9)</x:f>
-        <x:v>1.24788058578438</x:v>
+        <x:f>IF(B112&lt;=$B$7,-$B$8*LN(C112),-$B$9*LN(C112))</x:f>
+        <x:v>1.2481309394238178</x:v>
       </x:c>
       <x:c r="F112" s="13"/>
       <x:c r="G112" s="13"/>
@@ -7373,11 +7558,12 @@
         <x:v>0.8331004291540012</x:v>
       </x:c>
       <x:c r="D113" s="10" t="n">
+        <x:f>IF(B113&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E113" s="11" t="n">
-        <x:f>IF(B113&lt;=$B$7,-LN(C113)/$B$8,-LN(C113)/$B$9)</x:f>
-        <x:v>0.7786344704502737</x:v>
+        <x:f>IF(B113&lt;=$B$7,-$B$8*LN(C113),-$B$9*LN(C113))</x:f>
+        <x:v>0.7787906824914655</x:v>
       </x:c>
       <x:c r="F113" s="13"/>
       <x:c r="G113" s="13"/>
@@ -7401,11 +7587,12 @@
         <x:v>0.6541126639349386</x:v>
       </x:c>
       <x:c r="D114" s="10" t="n">
+        <x:f>IF(B114&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E114" s="11" t="n">
-        <x:f>IF(B114&lt;=$B$7,-LN(C114)/$B$8,-LN(C114)/$B$9)</x:f>
-        <x:v>1.8100188101693655</x:v>
+        <x:f>IF(B114&lt;=$B$7,-$B$8*LN(C114),-$B$9*LN(C114))</x:f>
+        <x:v>1.8103819417075426</x:v>
       </x:c>
       <x:c r="F114" s="13"/>
       <x:c r="G114" s="13"/>
@@ -7429,11 +7616,12 @@
         <x:v>0.7591131994267926</x:v>
       </x:c>
       <x:c r="D115" s="10" t="n">
+        <x:f>IF(B115&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E115" s="11" t="n">
-        <x:f>IF(B115&lt;=$B$7,-LN(C115)/$B$8,-LN(C115)/$B$9)</x:f>
-        <x:v>1.1752124442450433</x:v>
+        <x:f>IF(B115&lt;=$B$7,-$B$8*LN(C115),-$B$9*LN(C115))</x:f>
+        <x:v>1.1754482189785245</x:v>
       </x:c>
       <x:c r="F115" s="13"/>
       <x:c r="G115" s="13"/>
@@ -7457,11 +7645,12 @@
         <x:v>0.39551677356939763</x:v>
       </x:c>
       <x:c r="D116" s="10" t="n">
+        <x:f>IF(B116&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E116" s="11" t="n">
-        <x:f>IF(B116&lt;=$B$7,-LN(C116)/$B$8,-LN(C116)/$B$9)</x:f>
-        <x:v>3.9552438944291017</x:v>
+        <x:f>IF(B116&lt;=$B$7,-$B$8*LN(C116),-$B$9*LN(C116))</x:f>
+        <x:v>3.9560374076186773</x:v>
       </x:c>
       <x:c r="F116" s="13"/>
       <x:c r="G116" s="13"/>
@@ -7485,11 +7674,12 @@
         <x:v>0.03519705717917532</x:v>
       </x:c>
       <x:c r="D117" s="10" t="n">
+        <x:f>IF(B117&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E117" s="11" t="n">
-        <x:f>IF(B117&lt;=$B$7,-LN(C117)/$B$8,-LN(C117)/$B$9)</x:f>
-        <x:v>14.271154525572722</x:v>
+        <x:f>IF(B117&lt;=$B$7,-$B$8*LN(C117),-$B$9*LN(C117))</x:f>
+        <x:v>14.27401764846698</x:v>
       </x:c>
       <x:c r="F117" s="13"/>
       <x:c r="G117" s="13"/>
@@ -7513,11 +7703,12 @@
         <x:v>0.4153744865907356</x:v>
       </x:c>
       <x:c r="D118" s="10" t="n">
+        <x:f>IF(B118&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E118" s="11" t="n">
-        <x:f>IF(B118&lt;=$B$7,-LN(C118)/$B$8,-LN(C118)/$B$9)</x:f>
-        <x:v>3.746355781619003</x:v>
+        <x:f>IF(B118&lt;=$B$7,-$B$8*LN(C118),-$B$9*LN(C118))</x:f>
+        <x:v>3.7471073870332092</x:v>
       </x:c>
       <x:c r="F118" s="13"/>
       <x:c r="G118" s="13"/>
@@ -7541,11 +7732,12 @@
         <x:v>0.43889435508754104</x:v>
       </x:c>
       <x:c r="D119" s="10" t="n">
+        <x:f>IF(B119&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E119" s="11" t="n">
-        <x:f>IF(B119&lt;=$B$7,-LN(C119)/$B$8,-LN(C119)/$B$9)</x:f>
-        <x:v>3.511495070517852</x:v>
+        <x:f>IF(B119&lt;=$B$7,-$B$8*LN(C119),-$B$9*LN(C119))</x:f>
+        <x:v>3.512199557454172</x:v>
       </x:c>
       <x:c r="F119" s="13"/>
       <x:c r="G119" s="13"/>
@@ -7569,11 +7761,12 @@
         <x:v>0.6708336396841332</x:v>
       </x:c>
       <x:c r="D120" s="10" t="n">
+        <x:f>IF(B120&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E120" s="11" t="n">
-        <x:f>IF(B120&lt;=$B$7,-LN(C120)/$B$8,-LN(C120)/$B$9)</x:f>
-        <x:v>1.7023855054229453</x:v>
+        <x:f>IF(B120&lt;=$B$7,-$B$8*LN(C120),-$B$9*LN(C120))</x:f>
+        <x:v>1.7027270432366304</x:v>
       </x:c>
       <x:c r="F120" s="13"/>
       <x:c r="G120" s="13"/>
@@ -7597,11 +7790,12 @@
         <x:v>0.34903910232242197</x:v>
       </x:c>
       <x:c r="D121" s="10" t="n">
+        <x:f>IF(B121&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E121" s="11" t="n">
-        <x:f>IF(B121&lt;=$B$7,-LN(C121)/$B$8,-LN(C121)/$B$9)</x:f>
-        <x:v>4.488299357346055</x:v>
+        <x:f>IF(B121&lt;=$B$7,-$B$8*LN(C121),-$B$9*LN(C121))</x:f>
+        <x:v>4.489199813761355</x:v>
       </x:c>
       <x:c r="F121" s="13"/>
       <x:c r="G121" s="13"/>
@@ -7625,11 +7819,12 @@
         <x:v>0.35842576704453677</x:v>
       </x:c>
       <x:c r="D122" s="10" t="n">
+        <x:f>IF(B122&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E122" s="11" t="n">
-        <x:f>IF(B122&lt;=$B$7,-LN(C122)/$B$8,-LN(C122)/$B$9)</x:f>
-        <x:v>4.3751395521367025</x:v>
+        <x:f>IF(B122&lt;=$B$7,-$B$8*LN(C122),-$B$9*LN(C122))</x:f>
+        <x:v>4.376017306083998</x:v>
       </x:c>
       <x:c r="F122" s="13"/>
       <x:c r="G122" s="13"/>
@@ -7653,11 +7848,12 @@
         <x:v>0.5651539372047409</x:v>
       </x:c>
       <x:c r="D123" s="10" t="n">
+        <x:f>IF(B123&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E123" s="11" t="n">
-        <x:f>IF(B123&lt;=$B$7,-LN(C123)/$B$8,-LN(C123)/$B$9)</x:f>
-        <x:v>2.4333553223328446</x:v>
+        <x:f>IF(B123&lt;=$B$7,-$B$8*LN(C123),-$B$9*LN(C123))</x:f>
+        <x:v>2.4338435095583946</x:v>
       </x:c>
       <x:c r="F123" s="13"/>
       <x:c r="G123" s="13"/>
@@ -7681,11 +7877,12 @@
         <x:v>0.8296544792829081</x:v>
       </x:c>
       <x:c r="D124" s="10" t="n">
+        <x:f>IF(B124&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E124" s="11" t="n">
-        <x:f>IF(B124&lt;=$B$7,-LN(C124)/$B$8,-LN(C124)/$B$9)</x:f>
-        <x:v>0.7963087457960638</x:v>
+        <x:f>IF(B124&lt;=$B$7,-$B$8*LN(C124),-$B$9*LN(C124))</x:f>
+        <x:v>0.796468503704711</x:v>
       </x:c>
       <x:c r="F124" s="13"/>
       <x:c r="G124" s="13"/>
@@ -7709,11 +7906,12 @@
         <x:v>0.9793861623620614</x:v>
       </x:c>
       <x:c r="D125" s="10" t="n">
+        <x:f>IF(B125&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E125" s="11" t="n">
-        <x:f>IF(B125&lt;=$B$7,-LN(C125)/$B$8,-LN(C125)/$B$9)</x:f>
-        <x:v>0.08881867715653013</x:v>
+        <x:f>IF(B125&lt;=$B$7,-$B$8*LN(C125),-$B$9*LN(C125))</x:f>
+        <x:v>0.0888364962325936</x:v>
       </x:c>
       <x:c r="F125" s="13"/>
       <x:c r="G125" s="13"/>
@@ -7737,11 +7935,12 @@
         <x:v>0.5856854048324749</x:v>
       </x:c>
       <x:c r="D126" s="10" t="n">
+        <x:f>IF(B126&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E126" s="11" t="n">
-        <x:f>IF(B126&lt;=$B$7,-LN(C126)/$B$8,-LN(C126)/$B$9)</x:f>
-        <x:v>36.05459295052873</x:v>
+        <x:f>IF(B126&lt;=$B$7,-$B$8*LN(C126),-$B$9*LN(C126))</x:f>
+        <x:v>35.9406523289801</x:v>
       </x:c>
       <x:c r="F126" s="13"/>
       <x:c r="G126" s="13"/>
@@ -7765,11 +7964,12 @@
         <x:v>0.6166078423848376</x:v>
       </x:c>
       <x:c r="D127" s="10" t="n">
+        <x:f>IF(B127&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E127" s="11" t="n">
-        <x:f>IF(B127&lt;=$B$7,-LN(C127)/$B$8,-LN(C127)/$B$9)</x:f>
-        <x:v>2.0618001248852122</x:v>
+        <x:f>IF(B127&lt;=$B$7,-$B$8*LN(C127),-$B$9*LN(C127))</x:f>
+        <x:v>2.0622137695647904</x:v>
       </x:c>
       <x:c r="F127" s="13"/>
       <x:c r="G127" s="13"/>
@@ -7793,11 +7993,12 @@
         <x:v>0.49176269385498017</x:v>
       </x:c>
       <x:c r="D128" s="10" t="n">
+        <x:f>IF(B128&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E128" s="11" t="n">
-        <x:f>IF(B128&lt;=$B$7,-LN(C128)/$B$8,-LN(C128)/$B$9)</x:f>
-        <x:v>3.0265036056815093</x:v>
+        <x:f>IF(B128&lt;=$B$7,-$B$8*LN(C128),-$B$9*LN(C128))</x:f>
+        <x:v>3.0271107921391605</x:v>
       </x:c>
       <x:c r="F128" s="13"/>
       <x:c r="G128" s="13"/>
@@ -7821,11 +8022,12 @@
         <x:v>0.808304963982664</x:v>
       </x:c>
       <x:c r="D129" s="10" t="n">
+        <x:f>IF(B129&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E129" s="11" t="n">
-        <x:f>IF(B129&lt;=$B$7,-LN(C129)/$B$8,-LN(C129)/$B$9)</x:f>
-        <x:v>0.9074741750722838</x:v>
+        <x:f>IF(B129&lt;=$B$7,-$B$8*LN(C129),-$B$9*LN(C129))</x:f>
+        <x:v>0.9076562353311046</x:v>
       </x:c>
       <x:c r="F129" s="13"/>
       <x:c r="G129" s="13"/>
@@ -7849,11 +8051,12 @@
         <x:v>0.6019770846469328</x:v>
       </x:c>
       <x:c r="D130" s="10" t="n">
+        <x:f>IF(B130&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E130" s="11" t="n">
-        <x:f>IF(B130&lt;=$B$7,-LN(C130)/$B$8,-LN(C130)/$B$9)</x:f>
-        <x:v>2.164198287669847</x:v>
+        <x:f>IF(B130&lt;=$B$7,-$B$8*LN(C130),-$B$9*LN(C130))</x:f>
+        <x:v>2.164632475783642</x:v>
       </x:c>
       <x:c r="F130" s="13"/>
       <x:c r="G130" s="13"/>
@@ -7877,11 +8080,12 @@
         <x:v>0.5158806586405262</x:v>
       </x:c>
       <x:c r="D131" s="10" t="n">
+        <x:f>IF(B131&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E131" s="11" t="n">
-        <x:f>IF(B131&lt;=$B$7,-LN(C131)/$B$8,-LN(C131)/$B$9)</x:f>
-        <x:v>2.8223406028448053</x:v>
+        <x:f>IF(B131&lt;=$B$7,-$B$8*LN(C131),-$B$9*LN(C131))</x:f>
+        <x:v>2.8229068294931765</x:v>
       </x:c>
       <x:c r="F131" s="13"/>
       <x:c r="G131" s="13"/>
@@ -7905,11 +8109,12 @@
         <x:v>0.23501053254585713</x:v>
       </x:c>
       <x:c r="D132" s="10" t="n">
+        <x:f>IF(B132&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E132" s="11" t="n">
-        <x:f>IF(B132&lt;=$B$7,-LN(C132)/$B$8,-LN(C132)/$B$9)</x:f>
-        <x:v>6.1749908350796</x:v>
+        <x:f>IF(B132&lt;=$B$7,-$B$8*LN(C132),-$B$9*LN(C132))</x:f>
+        <x:v>6.176229680724504</x:v>
       </x:c>
       <x:c r="F132" s="13"/>
       <x:c r="G132" s="13"/>
@@ -7933,11 +8138,12 @@
         <x:v>0.0689974877750501</x:v>
       </x:c>
       <x:c r="D133" s="10" t="n">
+        <x:f>IF(B133&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E133" s="11" t="n">
-        <x:f>IF(B133&lt;=$B$7,-LN(C133)/$B$8,-LN(C133)/$B$9)</x:f>
-        <x:v>11.400937155084073</x:v>
+        <x:f>IF(B133&lt;=$B$7,-$B$8*LN(C133),-$B$9*LN(C133))</x:f>
+        <x:v>11.403224446145648</x:v>
       </x:c>
       <x:c r="F133" s="13"/>
       <x:c r="G133" s="13"/>
@@ -7961,11 +8167,12 @@
         <x:v>0.19148240133654326</x:v>
       </x:c>
       <x:c r="D134" s="10" t="n">
+        <x:f>IF(B134&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E134" s="11" t="n">
-        <x:f>IF(B134&lt;=$B$7,-LN(C134)/$B$8,-LN(C134)/$B$9)</x:f>
-        <x:v>7.04843115056076</x:v>
+        <x:f>IF(B134&lt;=$B$7,-$B$8*LN(C134),-$B$9*LN(C134))</x:f>
+        <x:v>7.049845228486944</x:v>
       </x:c>
       <x:c r="F134" s="13"/>
       <x:c r="G134" s="13"/>
@@ -7989,11 +8196,12 @@
         <x:v>0.8345837903907523</x:v>
       </x:c>
       <x:c r="D135" s="10" t="n">
+        <x:f>IF(B135&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E135" s="11" t="n">
-        <x:f>IF(B135&lt;=$B$7,-LN(C135)/$B$8,-LN(C135)/$B$9)</x:f>
-        <x:v>0.7710488082511058</x:v>
+        <x:f>IF(B135&lt;=$B$7,-$B$8*LN(C135),-$B$9*LN(C135))</x:f>
+        <x:v>0.771203498433427</x:v>
       </x:c>
       <x:c r="F135" s="13"/>
       <x:c r="G135" s="13"/>
@@ -8017,11 +8225,12 @@
         <x:v>0.25352221715729684</x:v>
       </x:c>
       <x:c r="D136" s="10" t="n">
+        <x:f>IF(B136&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E136" s="11" t="n">
-        <x:f>IF(B136&lt;=$B$7,-LN(C136)/$B$8,-LN(C136)/$B$9)</x:f>
-        <x:v>5.851679801857949</x:v>
+        <x:f>IF(B136&lt;=$B$7,-$B$8*LN(C136),-$B$9*LN(C136))</x:f>
+        <x:v>5.852853783849423</x:v>
       </x:c>
       <x:c r="F136" s="13"/>
       <x:c r="G136" s="13"/>
@@ -8045,11 +8254,12 @@
         <x:v>0.5821290932362899</x:v>
       </x:c>
       <x:c r="D137" s="10" t="n">
+        <x:f>IF(B137&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E137" s="11" t="n">
-        <x:f>IF(B137&lt;=$B$7,-LN(C137)/$B$8,-LN(C137)/$B$9)</x:f>
-        <x:v>2.3071623476500855</x:v>
+        <x:f>IF(B137&lt;=$B$7,-$B$8*LN(C137),-$B$9*LN(C137))</x:f>
+        <x:v>2.307625217653104</x:v>
       </x:c>
       <x:c r="F137" s="13"/>
       <x:c r="G137" s="13"/>
@@ -8073,11 +8283,12 @@
         <x:v>0.35719398490618914</x:v>
       </x:c>
       <x:c r="D138" s="10" t="n">
+        <x:f>IF(B138&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E138" s="11" t="n">
-        <x:f>IF(B138&lt;=$B$7,-LN(C138)/$B$8,-LN(C138)/$B$9)</x:f>
-        <x:v>4.389819086839975</x:v>
+        <x:f>IF(B138&lt;=$B$7,-$B$8*LN(C138),-$B$9*LN(C138))</x:f>
+        <x:v>4.390699785840652</x:v>
       </x:c>
       <x:c r="F138" s="13"/>
       <x:c r="G138" s="13"/>
@@ -8101,11 +8312,12 @@
         <x:v>0.5608935834607109</x:v>
       </x:c>
       <x:c r="D139" s="10" t="n">
+        <x:f>IF(B139&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E139" s="11" t="n">
-        <x:f>IF(B139&lt;=$B$7,-LN(C139)/$B$8,-LN(C139)/$B$9)</x:f>
-        <x:v>2.4656217802020692</x:v>
+        <x:f>IF(B139&lt;=$B$7,-$B$8*LN(C139),-$B$9*LN(C139))</x:f>
+        <x:v>2.4661164408235927</x:v>
       </x:c>
       <x:c r="F139" s="13"/>
       <x:c r="G139" s="13"/>
@@ -8129,11 +8341,12 @@
         <x:v>0.0783970671473071</x:v>
       </x:c>
       <x:c r="D140" s="10" t="n">
+        <x:f>IF(B140&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E140" s="11" t="n">
-        <x:f>IF(B140&lt;=$B$7,-LN(C140)/$B$8,-LN(C140)/$B$9)</x:f>
-        <x:v>10.856337917928558</x:v>
+        <x:f>IF(B140&lt;=$B$7,-$B$8*LN(C140),-$B$9*LN(C140))</x:f>
+        <x:v>10.858515949816931</x:v>
       </x:c>
       <x:c r="F140" s="13"/>
       <x:c r="G140" s="13"/>
@@ -8157,11 +8370,12 @@
         <x:v>0.5546566437697038</x:v>
       </x:c>
       <x:c r="D141" s="10" t="n">
+        <x:f>IF(B141&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E141" s="11" t="n">
-        <x:f>IF(B141&lt;=$B$7,-LN(C141)/$B$8,-LN(C141)/$B$9)</x:f>
-        <x:v>2.5133029847970776</x:v>
+        <x:f>IF(B141&lt;=$B$7,-$B$8*LN(C141),-$B$9*LN(C141))</x:f>
+        <x:v>2.5138072113684515</x:v>
       </x:c>
       <x:c r="F141" s="13"/>
       <x:c r="G141" s="13"/>
@@ -8185,11 +8399,12 @@
         <x:v>0.32286862551700324</x:v>
       </x:c>
       <x:c r="D142" s="10" t="n">
+        <x:f>IF(B142&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E142" s="11" t="n">
-        <x:f>IF(B142&lt;=$B$7,-LN(C142)/$B$8,-LN(C142)/$B$9)</x:f>
-        <x:v>4.820638916254212</x:v>
+        <x:f>IF(B142&lt;=$B$7,-$B$8*LN(C142),-$B$9*LN(C142))</x:f>
+        <x:v>4.821606047653521</x:v>
       </x:c>
       <x:c r="F142" s="13"/>
       <x:c r="G142" s="13"/>
@@ -8213,11 +8428,12 @@
         <x:v>0.4296294500818476</x:v>
       </x:c>
       <x:c r="D143" s="10" t="n">
+        <x:f>IF(B143&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E143" s="11" t="n">
-        <x:f>IF(B143&lt;=$B$7,-LN(C143)/$B$8,-LN(C143)/$B$9)</x:f>
-        <x:v>3.602472989047868</x:v>
+        <x:f>IF(B143&lt;=$B$7,-$B$8*LN(C143),-$B$9*LN(C143))</x:f>
+        <x:v>3.603195728253894</x:v>
       </x:c>
       <x:c r="F143" s="13"/>
       <x:c r="G143" s="13"/>
@@ -8241,11 +8457,12 @@
         <x:v>0.36091262463014573</x:v>
       </x:c>
       <x:c r="D144" s="10" t="n">
+        <x:f>IF(B144&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E144" s="11" t="n">
-        <x:f>IF(B144&lt;=$B$7,-LN(C144)/$B$8,-LN(C144)/$B$9)</x:f>
-        <x:v>4.345656008256892</x:v>
+        <x:f>IF(B144&lt;=$B$7,-$B$8*LN(C144),-$B$9*LN(C144))</x:f>
+        <x:v>4.346527847124975</x:v>
       </x:c>
       <x:c r="F144" s="13"/>
       <x:c r="G144" s="13"/>
@@ -8269,11 +8486,12 @@
         <x:v>0.9411566316848621</x:v>
       </x:c>
       <x:c r="D145" s="10" t="n">
+        <x:f>IF(B145&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E145" s="11" t="n">
-        <x:f>IF(B145&lt;=$B$7,-LN(C145)/$B$8,-LN(C145)/$B$9)</x:f>
-        <x:v>0.2586010606239236</x:v>
+        <x:f>IF(B145&lt;=$B$7,-$B$8*LN(C145),-$B$9*LN(C145))</x:f>
+        <x:v>0.25865294196371463</x:v>
       </x:c>
       <x:c r="F145" s="13"/>
       <x:c r="G145" s="13"/>
@@ -8297,11 +8515,12 @@
         <x:v>0.5974803984863684</x:v>
       </x:c>
       <x:c r="D146" s="10" t="n">
+        <x:f>IF(B146&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E146" s="11" t="n">
-        <x:f>IF(B146&lt;=$B$7,-LN(C146)/$B$8,-LN(C146)/$B$9)</x:f>
-        <x:v>34.71082079851131</x:v>
+        <x:f>IF(B146&lt;=$B$7,-$B$8*LN(C146),-$B$9*LN(C146))</x:f>
+        <x:v>34.601126799145625</x:v>
       </x:c>
       <x:c r="F146" s="13"/>
       <x:c r="G146" s="13"/>
@@ -8325,11 +8544,12 @@
         <x:v>0.8148319938918576</x:v>
       </x:c>
       <x:c r="D147" s="10" t="n">
+        <x:f>IF(B147&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E147" s="11" t="n">
-        <x:f>IF(B147&lt;=$B$7,-LN(C147)/$B$8,-LN(C147)/$B$9)</x:f>
-        <x:v>0.8731797872236688</x:v>
+        <x:f>IF(B147&lt;=$B$7,-$B$8*LN(C147),-$B$9*LN(C147))</x:f>
+        <x:v>0.8733549672369693</x:v>
       </x:c>
       <x:c r="F147" s="13"/>
       <x:c r="G147" s="13"/>
@@ -8353,11 +8573,12 @@
         <x:v>0.7182277793763205</x:v>
       </x:c>
       <x:c r="D148" s="10" t="n">
+        <x:f>IF(B148&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E148" s="11" t="n">
-        <x:f>IF(B148&lt;=$B$7,-LN(C148)/$B$8,-LN(C148)/$B$9)</x:f>
-        <x:v>1.4112922887393426</x:v>
+        <x:f>IF(B148&lt;=$B$7,-$B$8*LN(C148),-$B$9*LN(C148))</x:f>
+        <x:v>1.4115754265369986</x:v>
       </x:c>
       <x:c r="F148" s="13"/>
       <x:c r="G148" s="13"/>
@@ -8381,11 +8602,12 @@
         <x:v>0.36765330319758505</x:v>
       </x:c>
       <x:c r="D149" s="10" t="n">
+        <x:f>IF(B149&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E149" s="11" t="n">
-        <x:f>IF(B149&lt;=$B$7,-LN(C149)/$B$8,-LN(C149)/$B$9)</x:f>
-        <x:v>4.26675048010914</x:v>
+        <x:f>IF(B149&lt;=$B$7,-$B$8*LN(C149),-$B$9*LN(C149))</x:f>
+        <x:v>4.267606488707589</x:v>
       </x:c>
       <x:c r="F149" s="13"/>
       <x:c r="G149" s="13"/>
@@ -8409,11 +8631,12 @@
         <x:v>0.10217378928791732</x:v>
       </x:c>
       <x:c r="D150" s="10" t="n">
+        <x:f>IF(B150&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E150" s="11" t="n">
-        <x:f>IF(B150&lt;=$B$7,-LN(C150)/$B$8,-LN(C150)/$B$9)</x:f>
-        <x:v>9.726818628087786</x:v>
+        <x:f>IF(B150&lt;=$B$7,-$B$8*LN(C150),-$B$9*LN(C150))</x:f>
+        <x:v>9.728770052343789</x:v>
       </x:c>
       <x:c r="F150" s="13"/>
       <x:c r="G150" s="13"/>
@@ -8437,11 +8660,12 @@
         <x:v>0.18484113493468612</x:v>
       </x:c>
       <x:c r="D151" s="10" t="n">
+        <x:f>IF(B151&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E151" s="11" t="n">
-        <x:f>IF(B151&lt;=$B$7,-LN(C151)/$B$8,-LN(C151)/$B$9)</x:f>
-        <x:v>7.198951386516151</x:v>
+        <x:f>IF(B151&lt;=$B$7,-$B$8*LN(C151),-$B$9*LN(C151))</x:f>
+        <x:v>7.200395662274811</x:v>
       </x:c>
       <x:c r="F151" s="13"/>
       <x:c r="G151" s="13"/>
@@ -8465,11 +8689,12 @@
         <x:v>0.6415858938125893</x:v>
       </x:c>
       <x:c r="D152" s="10" t="n">
+        <x:f>IF(B152&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E152" s="11" t="n">
-        <x:f>IF(B152&lt;=$B$7,-LN(C152)/$B$8,-LN(C152)/$B$9)</x:f>
-        <x:v>1.8924722810552381</x:v>
+        <x:f>IF(B152&lt;=$B$7,-$B$8*LN(C152),-$B$9*LN(C152))</x:f>
+        <x:v>1.8928519546622282</x:v>
       </x:c>
       <x:c r="F152" s="13"/>
       <x:c r="G152" s="13"/>
@@ -8493,11 +8718,12 @@
         <x:v>0.617946783429943</x:v>
       </x:c>
       <x:c r="D153" s="10" t="n">
+        <x:f>IF(B153&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E153" s="11" t="n">
-        <x:f>IF(B153&lt;=$B$7,-LN(C153)/$B$8,-LN(C153)/$B$9)</x:f>
-        <x:v>32.440891174668174</x:v>
+        <x:f>IF(B153&lt;=$B$7,-$B$8*LN(C153),-$B$9*LN(C153))</x:f>
+        <x:v>32.3383706633673</x:v>
       </x:c>
       <x:c r="F153" s="13"/>
       <x:c r="G153" s="13"/>
@@ -8521,11 +8747,12 @@
         <x:v>0.3597168185515329</x:v>
       </x:c>
       <x:c r="D154" s="10" t="n">
+        <x:f>IF(B154&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E154" s="11" t="n">
-        <x:f>IF(B154&lt;=$B$7,-LN(C154)/$B$8,-LN(C154)/$B$9)</x:f>
-        <x:v>4.3598077348940905</x:v>
+        <x:f>IF(B154&lt;=$B$7,-$B$8*LN(C154),-$B$9*LN(C154))</x:f>
+        <x:v>4.360682412925077</x:v>
       </x:c>
       <x:c r="F154" s="13"/>
       <x:c r="G154" s="13"/>
@@ -8549,11 +8776,12 @@
         <x:v>0.1198742346605286</x:v>
       </x:c>
       <x:c r="D155" s="10" t="n">
+        <x:f>IF(B155&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E155" s="11" t="n">
-        <x:f>IF(B155&lt;=$B$7,-LN(C155)/$B$8,-LN(C155)/$B$9)</x:f>
-        <x:v>9.045547481580986</x:v>
+        <x:f>IF(B155&lt;=$B$7,-$B$8*LN(C155),-$B$9*LN(C155))</x:f>
+        <x:v>9.047362227125166</x:v>
       </x:c>
       <x:c r="F155" s="13"/>
       <x:c r="G155" s="13"/>
@@ -8577,11 +8805,12 @@
         <x:v>0.46701792802195996</x:v>
       </x:c>
       <x:c r="D156" s="10" t="n">
+        <x:f>IF(B156&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E156" s="11" t="n">
-        <x:f>IF(B156&lt;=$B$7,-LN(C156)/$B$8,-LN(C156)/$B$9)</x:f>
-        <x:v>3.246654691399309</x:v>
+        <x:f>IF(B156&lt;=$B$7,-$B$8*LN(C156),-$B$9*LN(C156))</x:f>
+        <x:v>3.24730604524458</x:v>
       </x:c>
       <x:c r="F156" s="13"/>
       <x:c r="G156" s="13"/>
@@ -8605,11 +8834,12 @@
         <x:v>0.6824412014102563</x:v>
       </x:c>
       <x:c r="D157" s="10" t="n">
+        <x:f>IF(B157&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E157" s="11" t="n">
-        <x:f>IF(B157&lt;=$B$7,-LN(C157)/$B$8,-LN(C157)/$B$9)</x:f>
-        <x:v>1.6292335528537896</x:v>
+        <x:f>IF(B157&lt;=$B$7,-$B$8*LN(C157),-$B$9*LN(C157))</x:f>
+        <x:v>1.629560414697862</x:v>
       </x:c>
       <x:c r="F157" s="13"/>
       <x:c r="G157" s="13"/>
@@ -8633,11 +8863,12 @@
         <x:v>0.746454167063348</x:v>
       </x:c>
       <x:c r="D158" s="10" t="n">
+        <x:f>IF(B158&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E158" s="11" t="n">
-        <x:f>IF(B158&lt;=$B$7,-LN(C158)/$B$8,-LN(C158)/$B$9)</x:f>
-        <x:v>1.246920975957603</x:v>
+        <x:f>IF(B158&lt;=$B$7,-$B$8*LN(C158),-$B$9*LN(C158))</x:f>
+        <x:v>1.2471711370771674</x:v>
       </x:c>
       <x:c r="F158" s="13"/>
       <x:c r="G158" s="13"/>
@@ -8661,11 +8892,12 @@
         <x:v>0.8921042209258303</x:v>
       </x:c>
       <x:c r="D159" s="10" t="n">
+        <x:f>IF(B159&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E159" s="11" t="n">
-        <x:f>IF(B159&lt;=$B$7,-LN(C159)/$B$8,-LN(C159)/$B$9)</x:f>
-        <x:v>0.48684541479329513</x:v>
+        <x:f>IF(B159&lt;=$B$7,-$B$8*LN(C159),-$B$9*LN(C159))</x:f>
+        <x:v>0.4869430872171037</x:v>
       </x:c>
       <x:c r="F159" s="13"/>
       <x:c r="G159" s="13"/>
@@ -8689,11 +8921,12 @@
         <x:v>0.4085455647436902</x:v>
       </x:c>
       <x:c r="D160" s="10" t="n">
+        <x:f>IF(B160&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E160" s="11" t="n">
-        <x:f>IF(B160&lt;=$B$7,-LN(C160)/$B$8,-LN(C160)/$B$9)</x:f>
-        <x:v>3.8170424142694745</x:v>
+        <x:f>IF(B160&lt;=$B$7,-$B$8*LN(C160),-$B$9*LN(C160))</x:f>
+        <x:v>3.817808201053232</x:v>
       </x:c>
       <x:c r="F160" s="13"/>
       <x:c r="G160" s="13"/>
@@ -8717,11 +8950,12 @@
         <x:v>0.36947281507309526</x:v>
       </x:c>
       <x:c r="D161" s="10" t="n">
+        <x:f>IF(B161&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E161" s="11" t="n">
-        <x:f>IF(B161&lt;=$B$7,-LN(C161)/$B$8,-LN(C161)/$B$9)</x:f>
-        <x:v>4.245699406260008</x:v>
+        <x:f>IF(B161&lt;=$B$7,-$B$8*LN(C161),-$B$9*LN(C161))</x:f>
+        <x:v>4.246551191527304</x:v>
       </x:c>
       <x:c r="F161" s="13"/>
       <x:c r="G161" s="13"/>
@@ -8745,11 +8979,12 @@
         <x:v>0.8067603007657453</x:v>
       </x:c>
       <x:c r="D162" s="10" t="n">
+        <x:f>IF(B162&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E162" s="11" t="n">
-        <x:f>IF(B162&lt;=$B$7,-LN(C162)/$B$8,-LN(C162)/$B$9)</x:f>
-        <x:v>14.471688470628298</x:v>
+        <x:f>IF(B162&lt;=$B$7,-$B$8*LN(C162),-$B$9*LN(C162))</x:f>
+        <x:v>14.425954680720753</x:v>
       </x:c>
       <x:c r="F162" s="13"/>
       <x:c r="G162" s="13"/>
@@ -8773,11 +9008,12 @@
         <x:v>0.6082377129932866</x:v>
       </x:c>
       <x:c r="D163" s="10" t="n">
+        <x:f>IF(B163&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E163" s="11" t="n">
-        <x:f>IF(B163&lt;=$B$7,-LN(C163)/$B$8,-LN(C163)/$B$9)</x:f>
-        <x:v>2.1200799016306258</x:v>
+        <x:f>IF(B163&lt;=$B$7,-$B$8*LN(C163),-$B$9*LN(C163))</x:f>
+        <x:v>2.120505238578182</x:v>
       </x:c>
       <x:c r="F163" s="13"/>
       <x:c r="G163" s="13"/>
@@ -8801,11 +9037,12 @@
         <x:v>0.6538843343732879</x:v>
       </x:c>
       <x:c r="D164" s="10" t="n">
+        <x:f>IF(B164&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E164" s="11" t="n">
-        <x:f>IF(B164&lt;=$B$7,-LN(C164)/$B$8,-LN(C164)/$B$9)</x:f>
-        <x:v>1.8115075392705635</x:v>
+        <x:f>IF(B164&lt;=$B$7,-$B$8*LN(C164),-$B$9*LN(C164))</x:f>
+        <x:v>1.8118709694821495</x:v>
       </x:c>
       <x:c r="F164" s="13"/>
       <x:c r="G164" s="13"/>
@@ -8829,11 +9066,12 @@
         <x:v>0.47913813625928015</x:v>
       </x:c>
       <x:c r="D165" s="10" t="n">
+        <x:f>IF(B165&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E165" s="11" t="n">
-        <x:f>IF(B165&lt;=$B$7,-LN(C165)/$B$8,-LN(C165)/$B$9)</x:f>
-        <x:v>3.137402202624843</x:v>
+        <x:f>IF(B165&lt;=$B$7,-$B$8*LN(C165),-$B$9*LN(C165))</x:f>
+        <x:v>3.138031637899945</x:v>
       </x:c>
       <x:c r="F165" s="13"/>
       <x:c r="G165" s="13"/>
@@ -8857,11 +9095,12 @@
         <x:v>0.6299925957573578</x:v>
       </x:c>
       <x:c r="D166" s="10" t="n">
+        <x:f>IF(B166&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E166" s="11" t="n">
-        <x:f>IF(B166&lt;=$B$7,-LN(C166)/$B$8,-LN(C166)/$B$9)</x:f>
-        <x:v>1.9702286802248545</x:v>
+        <x:f>IF(B166&lt;=$B$7,-$B$8*LN(C166),-$B$9*LN(C166))</x:f>
+        <x:v>1.9706239535596901</x:v>
       </x:c>
       <x:c r="F166" s="13"/>
       <x:c r="G166" s="13"/>
@@ -8885,11 +9124,12 @@
         <x:v>0.9145931465318426</x:v>
       </x:c>
       <x:c r="D167" s="10" t="n">
+        <x:f>IF(B167&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E167" s="11" t="n">
-        <x:f>IF(B167&lt;=$B$7,-LN(C167)/$B$8,-LN(C167)/$B$9)</x:f>
-        <x:v>0.3806841691952206</x:v>
+        <x:f>IF(B167&lt;=$B$7,-$B$8*LN(C167),-$B$9*LN(C167))</x:f>
+        <x:v>0.3807605432235692</x:v>
       </x:c>
       <x:c r="F167" s="13"/>
       <x:c r="G167" s="13"/>
@@ -8913,11 +9153,12 @@
         <x:v>0.5226467399625108</x:v>
       </x:c>
       <x:c r="D168" s="10" t="n">
+        <x:f>IF(B168&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E168" s="11" t="n">
-        <x:f>IF(B168&lt;=$B$7,-LN(C168)/$B$8,-LN(C168)/$B$9)</x:f>
-        <x:v>2.7667776040038508</x:v>
+        <x:f>IF(B168&lt;=$B$7,-$B$8*LN(C168),-$B$9*LN(C168))</x:f>
+        <x:v>2.7673326834325787</x:v>
       </x:c>
       <x:c r="F168" s="13"/>
       <x:c r="G168" s="13"/>
@@ -8941,11 +9182,12 @@
         <x:v>0.5396220557158813</x:v>
       </x:c>
       <x:c r="D169" s="10" t="n">
+        <x:f>IF(B169&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E169" s="11" t="n">
-        <x:f>IF(B169&lt;=$B$7,-LN(C169)/$B$8,-LN(C169)/$B$9)</x:f>
-        <x:v>2.6304823644212196</x:v>
+        <x:f>IF(B169&lt;=$B$7,-$B$8*LN(C169),-$B$9*LN(C169))</x:f>
+        <x:v>2.6310100998799744</x:v>
       </x:c>
       <x:c r="F169" s="13"/>
       <x:c r="G169" s="13"/>
@@ -8969,11 +9211,12 @@
         <x:v>0.2899444632930681</x:v>
       </x:c>
       <x:c r="D170" s="10" t="n">
+        <x:f>IF(B170&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E170" s="11" t="n">
-        <x:f>IF(B170&lt;=$B$7,-LN(C170)/$B$8,-LN(C170)/$B$9)</x:f>
-        <x:v>5.279271986933337</x:v>
+        <x:f>IF(B170&lt;=$B$7,-$B$8*LN(C170),-$B$9*LN(C170))</x:f>
+        <x:v>5.280331130709246</x:v>
       </x:c>
       <x:c r="F170" s="13"/>
       <x:c r="G170" s="13"/>
@@ -8997,11 +9240,12 @@
         <x:v>0.2646788986166939</x:v>
       </x:c>
       <x:c r="D171" s="10" t="n">
+        <x:f>IF(B171&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E171" s="11" t="n">
-        <x:f>IF(B171&lt;=$B$7,-LN(C171)/$B$8,-LN(C171)/$B$9)</x:f>
-        <x:v>5.668041155309703</x:v>
+        <x:f>IF(B171&lt;=$B$7,-$B$8*LN(C171),-$B$9*LN(C171))</x:f>
+        <x:v>5.669178295151353</x:v>
       </x:c>
       <x:c r="F171" s="13"/>
       <x:c r="G171" s="13"/>
@@ -9025,11 +9269,12 @@
         <x:v>0.6870453822193667</x:v>
       </x:c>
       <x:c r="D172" s="10" t="n">
+        <x:f>IF(B172&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E172" s="11" t="n">
-        <x:f>IF(B172&lt;=$B$7,-LN(C172)/$B$8,-LN(C172)/$B$9)</x:f>
-        <x:v>1.600561650923045</x:v>
+        <x:f>IF(B172&lt;=$B$7,-$B$8*LN(C172),-$B$9*LN(C172))</x:f>
+        <x:v>1.6008827605220068</x:v>
       </x:c>
       <x:c r="F172" s="13"/>
       <x:c r="G172" s="13"/>
@@ -9053,11 +9298,12 @@
         <x:v>0.106025968096219</x:v>
       </x:c>
       <x:c r="D173" s="10" t="n">
+        <x:f>IF(B173&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E173" s="11" t="n">
-        <x:f>IF(B173&lt;=$B$7,-LN(C173)/$B$8,-LN(C173)/$B$9)</x:f>
-        <x:v>9.569008067653694</x:v>
+        <x:f>IF(B173&lt;=$B$7,-$B$8*LN(C173),-$B$9*LN(C173))</x:f>
+        <x:v>9.570927831469913</x:v>
       </x:c>
       <x:c r="F173" s="13"/>
       <x:c r="G173" s="13"/>
@@ -9081,11 +9327,12 @@
         <x:v>0.34679847478400916</x:v>
       </x:c>
       <x:c r="D174" s="10" t="n">
+        <x:f>IF(B174&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E174" s="11" t="n">
-        <x:f>IF(B174&lt;=$B$7,-LN(C174)/$B$8,-LN(C174)/$B$9)</x:f>
-        <x:v>4.5157608140096395</x:v>
+        <x:f>IF(B174&lt;=$B$7,-$B$8*LN(C174),-$B$9*LN(C174))</x:f>
+        <x:v>4.5166667798268</x:v>
       </x:c>
       <x:c r="F174" s="13"/>
       <x:c r="G174" s="13"/>
@@ -9109,11 +9356,12 @@
         <x:v>0.7492714127292857</x:v>
       </x:c>
       <x:c r="D175" s="10" t="n">
+        <x:f>IF(B175&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E175" s="11" t="n">
-        <x:f>IF(B175&lt;=$B$7,-LN(C175)/$B$8,-LN(C175)/$B$9)</x:f>
-        <x:v>19.453901934604968</x:v>
+        <x:f>IF(B175&lt;=$B$7,-$B$8*LN(C175),-$B$9*LN(C175))</x:f>
+        <x:v>19.392423229769324</x:v>
       </x:c>
       <x:c r="F175" s="13"/>
       <x:c r="G175" s="13"/>
@@ -9137,11 +9385,12 @@
         <x:v>0.45509608450811356</x:v>
       </x:c>
       <x:c r="D176" s="10" t="n">
+        <x:f>IF(B176&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E176" s="11" t="n">
-        <x:f>IF(B176&lt;=$B$7,-LN(C176)/$B$8,-LN(C176)/$B$9)</x:f>
-        <x:v>3.3569211110011743</x:v>
+        <x:f>IF(B176&lt;=$B$7,-$B$8*LN(C176),-$B$9*LN(C176))</x:f>
+        <x:v>3.3575945868345345</x:v>
       </x:c>
       <x:c r="F176" s="13"/>
       <x:c r="G176" s="13"/>
@@ -9165,11 +9414,12 @@
         <x:v>0.6216958969598636</x:v>
       </x:c>
       <x:c r="D177" s="10" t="n">
+        <x:f>IF(B177&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E177" s="11" t="n">
-        <x:f>IF(B177&lt;=$B$7,-LN(C177)/$B$8,-LN(C177)/$B$9)</x:f>
-        <x:v>2.0267582529115478</x:v>
+        <x:f>IF(B177&lt;=$B$7,-$B$8*LN(C177),-$B$9*LN(C177))</x:f>
+        <x:v>2.0271648673830422</x:v>
       </x:c>
       <x:c r="F177" s="13"/>
       <x:c r="G177" s="13"/>
@@ -9193,11 +9443,12 @@
         <x:v>0.41157948679756373</x:v>
       </x:c>
       <x:c r="D178" s="10" t="n">
+        <x:f>IF(B178&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E178" s="11" t="n">
-        <x:f>IF(B178&lt;=$B$7,-LN(C178)/$B$8,-LN(C178)/$B$9)</x:f>
-        <x:v>3.7854933414929186</x:v>
+        <x:f>IF(B178&lt;=$B$7,-$B$8*LN(C178),-$B$9*LN(C178))</x:f>
+        <x:v>3.7862527988047057</x:v>
       </x:c>
       <x:c r="F178" s="13"/>
       <x:c r="G178" s="13"/>
@@ -9221,11 +9472,12 @@
         <x:v>0.4889933237573132</x:v>
       </x:c>
       <x:c r="D179" s="10" t="n">
+        <x:f>IF(B179&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E179" s="11" t="n">
-        <x:f>IF(B179&lt;=$B$7,-LN(C179)/$B$8,-LN(C179)/$B$9)</x:f>
-        <x:v>3.0505849900305324</x:v>
+        <x:f>IF(B179&lt;=$B$7,-$B$8*LN(C179),-$B$9*LN(C179))</x:f>
+        <x:v>3.0511970077695447</x:v>
       </x:c>
       <x:c r="F179" s="13"/>
       <x:c r="G179" s="13"/>
@@ -9249,11 +9501,12 @@
         <x:v>0.11632101784925908</x:v>
       </x:c>
       <x:c r="D180" s="10" t="n">
+        <x:f>IF(B180&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E180" s="11" t="n">
-        <x:f>IF(B180&lt;=$B$7,-LN(C180)/$B$8,-LN(C180)/$B$9)</x:f>
-        <x:v>9.173852483284161</x:v>
+        <x:f>IF(B180&lt;=$B$7,-$B$8*LN(C180),-$B$9*LN(C180))</x:f>
+        <x:v>9.175692969772228</x:v>
       </x:c>
       <x:c r="F180" s="13"/>
       <x:c r="G180" s="13"/>
@@ -9277,11 +9530,12 @@
         <x:v>0.8420506197726354</x:v>
       </x:c>
       <x:c r="D181" s="10" t="n">
+        <x:f>IF(B181&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E181" s="11" t="n">
-        <x:f>IF(B181&lt;=$B$7,-LN(C181)/$B$8,-LN(C181)/$B$9)</x:f>
-        <x:v>0.733068279915833</x:v>
+        <x:f>IF(B181&lt;=$B$7,-$B$8*LN(C181),-$B$9*LN(C181))</x:f>
+        <x:v>0.7332153503277973</x:v>
       </x:c>
       <x:c r="F181" s="13"/>
       <x:c r="G181" s="13"/>
@@ -9305,11 +9559,12 @@
         <x:v>0.7731077660573646</x:v>
       </x:c>
       <x:c r="D182" s="10" t="n">
+        <x:f>IF(B182&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E182" s="11" t="n">
-        <x:f>IF(B182&lt;=$B$7,-LN(C182)/$B$8,-LN(C182)/$B$9)</x:f>
-        <x:v>1.0973172959398347</x:v>
+        <x:f>IF(B182&lt;=$B$7,-$B$8*LN(C182),-$B$9*LN(C182))</x:f>
+        <x:v>1.0975374431091924</x:v>
       </x:c>
       <x:c r="F182" s="13"/>
       <x:c r="G182" s="13"/>
@@ -9333,11 +9588,12 @@
         <x:v>0.5893915829947218</x:v>
       </x:c>
       <x:c r="D183" s="10" t="n">
+        <x:f>IF(B183&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E183" s="11" t="n">
-        <x:f>IF(B183&lt;=$B$7,-LN(C183)/$B$8,-LN(C183)/$B$9)</x:f>
-        <x:v>2.254293308637757</x:v>
+        <x:f>IF(B183&lt;=$B$7,-$B$8*LN(C183),-$B$9*LN(C183))</x:f>
+        <x:v>2.2547455718916347</x:v>
       </x:c>
       <x:c r="F183" s="13"/>
       <x:c r="G183" s="13"/>
@@ -9361,11 +9617,12 @@
         <x:v>0.3499518259195611</x:v>
       </x:c>
       <x:c r="D184" s="10" t="n">
+        <x:f>IF(B184&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E184" s="11" t="n">
-        <x:f>IF(B184&lt;=$B$7,-LN(C184)/$B$8,-LN(C184)/$B$9)</x:f>
-        <x:v>4.477163381914071</x:v>
+        <x:f>IF(B184&lt;=$B$7,-$B$8*LN(C184),-$B$9*LN(C184))</x:f>
+        <x:v>4.478061604195746</x:v>
       </x:c>
       <x:c r="F184" s="13"/>
       <x:c r="G184" s="13"/>
@@ -9389,11 +9646,12 @@
         <x:v>0.8209097929066047</x:v>
       </x:c>
       <x:c r="D185" s="10" t="n">
+        <x:f>IF(B185&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E185" s="11" t="n">
-        <x:f>IF(B185&lt;=$B$7,-LN(C185)/$B$8,-LN(C185)/$B$9)</x:f>
-        <x:v>0.8414918577653165</x:v>
+        <x:f>IF(B185&lt;=$B$7,-$B$8*LN(C185),-$B$9*LN(C185))</x:f>
+        <x:v>0.8416606804487919</x:v>
       </x:c>
       <x:c r="F185" s="13"/>
       <x:c r="G185" s="13"/>
@@ -9417,11 +9675,12 @@
         <x:v>0.0874521144432947</x:v>
       </x:c>
       <x:c r="D186" s="10" t="n">
+        <x:f>IF(B186&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E186" s="11" t="n">
-        <x:f>IF(B186&lt;=$B$7,-LN(C186)/$B$8,-LN(C186)/$B$9)</x:f>
-        <x:v>10.39024794126232</x:v>
+        <x:f>IF(B186&lt;=$B$7,-$B$8*LN(C186),-$B$9*LN(C186))</x:f>
+        <x:v>10.39233246474669</x:v>
       </x:c>
       <x:c r="F186" s="13"/>
       <x:c r="G186" s="13"/>
@@ -9445,11 +9704,12 @@
         <x:v>0.6585155831417069</x:v>
       </x:c>
       <x:c r="D187" s="10" t="n">
+        <x:f>IF(B187&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E187" s="11" t="n">
-        <x:f>IF(B187&lt;=$B$7,-LN(C187)/$B$8,-LN(C187)/$B$9)</x:f>
-        <x:v>1.7814125636348226</x:v>
+        <x:f>IF(B187&lt;=$B$7,-$B$8*LN(C187),-$B$9*LN(C187))</x:f>
+        <x:v>1.7817699560998768</x:v>
       </x:c>
       <x:c r="F187" s="13"/>
       <x:c r="G187" s="13"/>
@@ -9473,11 +9733,12 @@
         <x:v>0.6956327500520274</x:v>
       </x:c>
       <x:c r="D188" s="10" t="n">
+        <x:f>IF(B188&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E188" s="11" t="n">
-        <x:f>IF(B188&lt;=$B$7,-LN(C188)/$B$8,-LN(C188)/$B$9)</x:f>
-        <x:v>1.5475947170295614</x:v>
+        <x:f>IF(B188&lt;=$B$7,-$B$8*LN(C188),-$B$9*LN(C188))</x:f>
+        <x:v>1.547905200239411</x:v>
       </x:c>
       <x:c r="F188" s="13"/>
       <x:c r="G188" s="13"/>
@@ -9501,11 +9762,12 @@
         <x:v>0.45932207664009184</x:v>
       </x:c>
       <x:c r="D189" s="10" t="n">
+        <x:f>IF(B189&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E189" s="11" t="n">
-        <x:f>IF(B189&lt;=$B$7,-LN(C189)/$B$8,-LN(C189)/$B$9)</x:f>
-        <x:v>3.317507410593803</x:v>
+        <x:f>IF(B189&lt;=$B$7,-$B$8*LN(C189),-$B$9*LN(C189))</x:f>
+        <x:v>3.3181729791294194</x:v>
       </x:c>
       <x:c r="F189" s="13"/>
       <x:c r="G189" s="13"/>
@@ -9529,11 +9791,12 @@
         <x:v>0.12988299399148673</x:v>
       </x:c>
       <x:c r="D190" s="10" t="n">
+        <x:f>IF(B190&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E190" s="11" t="n">
-        <x:f>IF(B190&lt;=$B$7,-LN(C190)/$B$8,-LN(C190)/$B$9)</x:f>
-        <x:v>8.703603392755008</x:v>
+        <x:f>IF(B190&lt;=$B$7,-$B$8*LN(C190),-$B$9*LN(C190))</x:f>
+        <x:v>8.705349536424862</x:v>
       </x:c>
       <x:c r="F190" s="13"/>
       <x:c r="G190" s="13"/>
@@ -9557,11 +9820,12 @@
         <x:v>0.8869952833047137</x:v>
       </x:c>
       <x:c r="D191" s="10" t="n">
+        <x:f>IF(B191&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E191" s="11" t="n">
-        <x:f>IF(B191&lt;=$B$7,-LN(C191)/$B$8,-LN(C191)/$B$9)</x:f>
-        <x:v>0.5113355866723142</x:v>
+        <x:f>IF(B191&lt;=$B$7,-$B$8*LN(C191),-$B$9*LN(C191))</x:f>
+        <x:v>0.5114381723896944</x:v>
       </x:c>
       <x:c r="F191" s="13"/>
       <x:c r="G191" s="13"/>
@@ -9585,11 +9849,12 @@
         <x:v>0.08662375423591584</x:v>
       </x:c>
       <x:c r="D192" s="10" t="n">
+        <x:f>IF(B192&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E192" s="11" t="n">
-        <x:f>IF(B192&lt;=$B$7,-LN(C192)/$B$8,-LN(C192)/$B$9)</x:f>
-        <x:v>10.43083094734577</x:v>
+        <x:f>IF(B192&lt;=$B$7,-$B$8*LN(C192),-$B$9*LN(C192))</x:f>
+        <x:v>10.432923612717584</x:v>
       </x:c>
       <x:c r="F192" s="13"/>
       <x:c r="G192" s="13"/>
@@ -9613,11 +9878,12 @@
         <x:v>0.6168932601576671</x:v>
       </x:c>
       <x:c r="D193" s="10" t="n">
+        <x:f>IF(B193&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E193" s="11" t="n">
-        <x:f>IF(B193&lt;=$B$7,-LN(C193)/$B$8,-LN(C193)/$B$9)</x:f>
-        <x:v>2.0598267856240917</x:v>
+        <x:f>IF(B193&lt;=$B$7,-$B$8*LN(C193),-$B$9*LN(C193))</x:f>
+        <x:v>2.060240034406281</x:v>
       </x:c>
       <x:c r="F193" s="13"/>
       <x:c r="G193" s="13"/>
@@ -9641,11 +9907,12 @@
         <x:v>0.6093256518943235</x:v>
       </x:c>
       <x:c r="D194" s="10" t="n">
+        <x:f>IF(B194&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E194" s="11" t="n">
-        <x:f>IF(B194&lt;=$B$7,-LN(C194)/$B$8,-LN(C194)/$B$9)</x:f>
-        <x:v>2.1124595795563383</x:v>
+        <x:f>IF(B194&lt;=$B$7,-$B$8*LN(C194),-$B$9*LN(C194))</x:f>
+        <x:v>2.1128833876914537</x:v>
       </x:c>
       <x:c r="F194" s="13"/>
       <x:c r="G194" s="13"/>
@@ -9669,11 +9936,12 @@
         <x:v>0.6906193339964375</x:v>
       </x:c>
       <x:c r="D195" s="10" t="n">
+        <x:f>IF(B195&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E195" s="11" t="n">
-        <x:f>IF(B195&lt;=$B$7,-LN(C195)/$B$8,-LN(C195)/$B$9)</x:f>
-        <x:v>1.5784375105758328</x:v>
+        <x:f>IF(B195&lt;=$B$7,-$B$8*LN(C195),-$B$9*LN(C195))</x:f>
+        <x:v>1.5787541815617427</x:v>
       </x:c>
       <x:c r="F195" s="13"/>
       <x:c r="G195" s="13"/>
@@ -9697,11 +9965,12 @@
         <x:v>0.4455036501167342</x:v>
       </x:c>
       <x:c r="D196" s="10" t="n">
+        <x:f>IF(B196&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E196" s="11" t="n">
-        <x:f>IF(B196&lt;=$B$7,-LN(C196)/$B$8,-LN(C196)/$B$9)</x:f>
-        <x:v>3.4477603996645163</x:v>
+        <x:f>IF(B196&lt;=$B$7,-$B$8*LN(C196),-$B$9*LN(C196))</x:f>
+        <x:v>3.4484520999552326</x:v>
       </x:c>
       <x:c r="F196" s="13"/>
       <x:c r="G196" s="13"/>
@@ -9725,11 +9994,12 @@
         <x:v>0.7856143865501508</x:v>
       </x:c>
       <x:c r="D197" s="10" t="n">
+        <x:f>IF(B197&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E197" s="11" t="n">
-        <x:f>IF(B197&lt;=$B$7,-LN(C197)/$B$8,-LN(C197)/$B$9)</x:f>
-        <x:v>1.0288881906076408</x:v>
+        <x:f>IF(B197&lt;=$B$7,-$B$8*LN(C197),-$B$9*LN(C197))</x:f>
+        <x:v>1.0290946093195175</x:v>
       </x:c>
       <x:c r="F197" s="13"/>
       <x:c r="G197" s="13"/>
@@ -9753,11 +10023,12 @@
         <x:v>0.045313245500437915</x:v>
       </x:c>
       <x:c r="D198" s="10" t="n">
+        <x:f>IF(B198&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E198" s="11" t="n">
-        <x:f>IF(B198&lt;=$B$7,-LN(C198)/$B$8,-LN(C198)/$B$9)</x:f>
-        <x:v>13.193878286847852</x:v>
+        <x:f>IF(B198&lt;=$B$7,-$B$8*LN(C198),-$B$9*LN(C198))</x:f>
+        <x:v>13.196525283271262</x:v>
       </x:c>
       <x:c r="F198" s="13"/>
       <x:c r="G198" s="13"/>
@@ -9781,11 +10052,12 @@
         <x:v>0.9154132021358237</x:v>
       </x:c>
       <x:c r="D199" s="10" t="n">
+        <x:f>IF(B199&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E199" s="11" t="n">
-        <x:f>IF(B199&lt;=$B$7,-LN(C199)/$B$8,-LN(C199)/$B$9)</x:f>
-        <x:v>0.37686251830605777</x:v>
+        <x:f>IF(B199&lt;=$B$7,-$B$8*LN(C199),-$B$9*LN(C199))</x:f>
+        <x:v>0.3769381256230563</x:v>
       </x:c>
       <x:c r="F199" s="13"/>
       <x:c r="G199" s="13"/>
@@ -9809,11 +10081,12 @@
         <x:v>0.3423732219962403</x:v>
       </x:c>
       <x:c r="D200" s="10" t="n">
+        <x:f>IF(B200&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E200" s="11" t="n">
-        <x:f>IF(B200&lt;=$B$7,-LN(C200)/$B$8,-LN(C200)/$B$9)</x:f>
-        <x:v>4.570522510992422</x:v>
+        <x:f>IF(B200&lt;=$B$7,-$B$8*LN(C200),-$B$9*LN(C200))</x:f>
+        <x:v>4.571439463269583</x:v>
       </x:c>
       <x:c r="F200" s="13"/>
       <x:c r="G200" s="13"/>
@@ -9837,11 +10110,12 @@
         <x:v>0.3261898778146133</x:v>
       </x:c>
       <x:c r="D201" s="10" t="n">
+        <x:f>IF(B201&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E201" s="11" t="n">
-        <x:f>IF(B201&lt;=$B$7,-LN(C201)/$B$8,-LN(C201)/$B$9)</x:f>
-        <x:v>4.77699918249378</x:v>
+        <x:f>IF(B201&lt;=$B$7,-$B$8*LN(C201),-$B$9*LN(C201))</x:f>
+        <x:v>4.777957558755542</x:v>
       </x:c>
       <x:c r="F201" s="13"/>
       <x:c r="G201" s="13"/>
@@ -9865,11 +10139,12 @@
         <x:v>0.7074399673147127</x:v>
       </x:c>
       <x:c r="D202" s="10" t="n">
+        <x:f>IF(B202&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E202" s="11" t="n">
-        <x:f>IF(B202&lt;=$B$7,-LN(C202)/$B$8,-LN(C202)/$B$9)</x:f>
-        <x:v>1.4758255501555118</x:v>
+        <x:f>IF(B202&lt;=$B$7,-$B$8*LN(C202),-$B$9*LN(C202))</x:f>
+        <x:v>1.4761216348144655</x:v>
       </x:c>
       <x:c r="F202" s="13"/>
       <x:c r="G202" s="13"/>
@@ -9893,11 +10168,12 @@
         <x:v>0.6052172960480675</x:v>
       </x:c>
       <x:c r="D203" s="10" t="n">
+        <x:f>IF(B203&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E203" s="11" t="n">
-        <x:f>IF(B203&lt;=$B$7,-LN(C203)/$B$8,-LN(C203)/$B$9)</x:f>
-        <x:v>2.1413076726439217</x:v>
+        <x:f>IF(B203&lt;=$B$7,-$B$8*LN(C203),-$B$9*LN(C203))</x:f>
+        <x:v>2.1417372683721587</x:v>
       </x:c>
       <x:c r="F203" s="13"/>
       <x:c r="G203" s="13"/>
@@ -9921,11 +10197,12 @@
         <x:v>0.715558351832442</x:v>
       </x:c>
       <x:c r="D204" s="10" t="n">
+        <x:f>IF(B204&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E204" s="11" t="n">
-        <x:f>IF(B204&lt;=$B$7,-LN(C204)/$B$8,-LN(C204)/$B$9)</x:f>
-        <x:v>1.4271702428281186</x:v>
+        <x:f>IF(B204&lt;=$B$7,-$B$8*LN(C204),-$B$9*LN(C204))</x:f>
+        <x:v>1.427456566109737</x:v>
       </x:c>
       <x:c r="F204" s="13"/>
       <x:c r="G204" s="13"/>
@@ -9949,11 +10226,12 @@
         <x:v>0.2668656598543748</x:v>
       </x:c>
       <x:c r="D205" s="10" t="n">
+        <x:f>IF(B205&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E205" s="11" t="n">
-        <x:f>IF(B205&lt;=$B$7,-LN(C205)/$B$8,-LN(C205)/$B$9)</x:f>
-        <x:v>5.632955917985528</x:v>
+        <x:f>IF(B205&lt;=$B$7,-$B$8*LN(C205),-$B$9*LN(C205))</x:f>
+        <x:v>5.634086018919004</x:v>
       </x:c>
       <x:c r="F205" s="13"/>
       <x:c r="G205" s="13"/>
@@ -9977,11 +10255,12 @@
         <x:v>0.6173141699982807</x:v>
       </x:c>
       <x:c r="D206" s="10" t="n">
+        <x:f>IF(B206&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E206" s="11" t="n">
-        <x:f>IF(B206&lt;=$B$7,-LN(C206)/$B$8,-LN(C206)/$B$9)</x:f>
-        <x:v>2.0569183381995155</x:v>
+        <x:f>IF(B206&lt;=$B$7,-$B$8*LN(C206),-$B$9*LN(C206))</x:f>
+        <x:v>2.057331003480041</x:v>
       </x:c>
       <x:c r="F206" s="13"/>
       <x:c r="G206" s="13"/>
@@ -10005,11 +10284,12 @@
         <x:v>0.33176509046461433</x:v>
       </x:c>
       <x:c r="D207" s="10" t="n">
+        <x:f>IF(B207&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E207" s="11" t="n">
-        <x:f>IF(B207&lt;=$B$7,-LN(C207)/$B$8,-LN(C207)/$B$9)</x:f>
-        <x:v>4.704732862669173</x:v>
+        <x:f>IF(B207&lt;=$B$7,-$B$8*LN(C207),-$B$9*LN(C207))</x:f>
+        <x:v>4.705676740639686</x:v>
       </x:c>
       <x:c r="F207" s="13"/>
       <x:c r="G207" s="13"/>
@@ -10033,11 +10313,12 @@
         <x:v>0.654813144239597</x:v>
       </x:c>
       <x:c r="D208" s="10" t="n">
+        <x:f>IF(B208&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E208" s="11" t="n">
-        <x:f>IF(B208&lt;=$B$7,-LN(C208)/$B$8,-LN(C208)/$B$9)</x:f>
-        <x:v>1.8054548566019573</x:v>
+        <x:f>IF(B208&lt;=$B$7,-$B$8*LN(C208),-$B$9*LN(C208))</x:f>
+        <x:v>1.8058170725057388</x:v>
       </x:c>
       <x:c r="F208" s="13"/>
       <x:c r="G208" s="13"/>
@@ -10061,11 +10342,12 @@
         <x:v>0.6647572874790058</x:v>
       </x:c>
       <x:c r="D209" s="10" t="n">
+        <x:f>IF(B209&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E209" s="11" t="n">
-        <x:f>IF(B209&lt;=$B$7,-LN(C209)/$B$8,-LN(C209)/$B$9)</x:f>
-        <x:v>1.7411855972327683</x:v>
+        <x:f>IF(B209&lt;=$B$7,-$B$8*LN(C209),-$B$9*LN(C209))</x:f>
+        <x:v>1.7415349192401544</x:v>
       </x:c>
       <x:c r="F209" s="13"/>
       <x:c r="G209" s="13"/>
@@ -10089,11 +10371,12 @@
         <x:v>0.6130114913685247</x:v>
       </x:c>
       <x:c r="D210" s="10" t="n">
+        <x:f>IF(B210&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E210" s="11" t="n">
-        <x:f>IF(B210&lt;=$B$7,-LN(C210)/$B$8,-LN(C210)/$B$9)</x:f>
-        <x:v>2.0867433672685824</x:v>
+        <x:f>IF(B210&lt;=$B$7,-$B$8*LN(C210),-$B$9*LN(C210))</x:f>
+        <x:v>2.0871620161381297</x:v>
       </x:c>
       <x:c r="F210" s="13"/>
       <x:c r="G210" s="13"/>
@@ -10117,11 +10400,12 @@
         <x:v>0.08726125152315944</x:v>
       </x:c>
       <x:c r="D211" s="10" t="n">
+        <x:f>IF(B211&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E211" s="11" t="n">
-        <x:f>IF(B211&lt;=$B$7,-LN(C211)/$B$8,-LN(C211)/$B$9)</x:f>
-        <x:v>10.399564507672126</x:v>
+        <x:f>IF(B211&lt;=$B$7,-$B$8*LN(C211),-$B$9*LN(C211))</x:f>
+        <x:v>10.401650900274692</x:v>
       </x:c>
       <x:c r="F211" s="13"/>
       <x:c r="G211" s="13"/>
@@ -10145,11 +10429,12 @@
         <x:v>0.24702305148821324</x:v>
       </x:c>
       <x:c r="D212" s="10" t="n">
+        <x:f>IF(B212&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E212" s="11" t="n">
-        <x:f>IF(B212&lt;=$B$7,-LN(C212)/$B$8,-LN(C212)/$B$9)</x:f>
-        <x:v>5.9624183773186</x:v>
+        <x:f>IF(B212&lt;=$B$7,-$B$8*LN(C212),-$B$9*LN(C212))</x:f>
+        <x:v>5.963614576023522</x:v>
       </x:c>
       <x:c r="F212" s="13"/>
       <x:c r="G212" s="13"/>
@@ -10173,11 +10458,12 @@
         <x:v>0.5296780694043264</x:v>
       </x:c>
       <x:c r="D213" s="10" t="n">
+        <x:f>IF(B213&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E213" s="11" t="n">
-        <x:f>IF(B213&lt;=$B$7,-LN(C213)/$B$8,-LN(C213)/$B$9)</x:f>
-        <x:v>2.7097934141385833</x:v>
+        <x:f>IF(B213&lt;=$B$7,-$B$8*LN(C213),-$B$9*LN(C213))</x:f>
+        <x:v>2.7103370612239557</x:v>
       </x:c>
       <x:c r="F213" s="13"/>
       <x:c r="G213" s="13"/>
@@ -10201,11 +10487,12 @@
         <x:v>0.4760279793990776</x:v>
       </x:c>
       <x:c r="D214" s="10" t="n">
+        <x:f>IF(B214&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E214" s="11" t="n">
-        <x:f>IF(B214&lt;=$B$7,-LN(C214)/$B$8,-LN(C214)/$B$9)</x:f>
-        <x:v>3.165171519637911</x:v>
+        <x:f>IF(B214&lt;=$B$7,-$B$8*LN(C214),-$B$9*LN(C214))</x:f>
+        <x:v>3.1658065260787627</x:v>
       </x:c>
       <x:c r="F214" s="13"/>
       <x:c r="G214" s="13"/>
@@ -10229,11 +10516,12 @@
         <x:v>0.7394597617676482</x:v>
       </x:c>
       <x:c r="D215" s="10" t="n">
+        <x:f>IF(B215&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E215" s="11" t="n">
-        <x:f>IF(B215&lt;=$B$7,-LN(C215)/$B$8,-LN(C215)/$B$9)</x:f>
-        <x:v>1.2870649742942615</x:v>
+        <x:f>IF(B215&lt;=$B$7,-$B$8*LN(C215),-$B$9*LN(C215))</x:f>
+        <x:v>1.2873231892261856</x:v>
       </x:c>
       <x:c r="F215" s="13"/>
       <x:c r="G215" s="13"/>
@@ -10257,11 +10545,12 @@
         <x:v>0.48440799850504845</x:v>
       </x:c>
       <x:c r="D216" s="10" t="n">
+        <x:f>IF(B216&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E216" s="11" t="n">
-        <x:f>IF(B216&lt;=$B$7,-LN(C216)/$B$8,-LN(C216)/$B$9)</x:f>
-        <x:v>3.09075867831533</x:v>
+        <x:f>IF(B216&lt;=$B$7,-$B$8*LN(C216),-$B$9*LN(C216))</x:f>
+        <x:v>3.0913787558231904</x:v>
       </x:c>
       <x:c r="F216" s="13"/>
       <x:c r="G216" s="13"/>
@@ -10285,11 +10574,12 @@
         <x:v>0.310467193252407</x:v>
       </x:c>
       <x:c r="D217" s="10" t="n">
+        <x:f>IF(B217&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E217" s="11" t="n">
-        <x:f>IF(B217&lt;=$B$7,-LN(C217)/$B$8,-LN(C217)/$B$9)</x:f>
-        <x:v>4.987653189457403</x:v>
+        <x:f>IF(B217&lt;=$B$7,-$B$8*LN(C217),-$B$9*LN(C217))</x:f>
+        <x:v>4.988653827773649</x:v>
       </x:c>
       <x:c r="F217" s="13"/>
       <x:c r="G217" s="13"/>
@@ -10313,11 +10603,12 @@
         <x:v>0.12073321721982211</x:v>
       </x:c>
       <x:c r="D218" s="10" t="n">
+        <x:f>IF(B218&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E218" s="11" t="n">
-        <x:f>IF(B218&lt;=$B$7,-LN(C218)/$B$8,-LN(C218)/$B$9)</x:f>
-        <x:v>9.015100980174267</x:v>
+        <x:f>IF(B218&lt;=$B$7,-$B$8*LN(C218),-$B$9*LN(C218))</x:f>
+        <x:v>9.016909617447736</x:v>
       </x:c>
       <x:c r="F218" s="13"/>
       <x:c r="G218" s="13"/>
@@ -10341,11 +10632,12 @@
         <x:v>0.04924204514827579</x:v>
       </x:c>
       <x:c r="D219" s="10" t="n">
+        <x:f>IF(B219&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E219" s="11" t="n">
-        <x:f>IF(B219&lt;=$B$7,-LN(C219)/$B$8,-LN(C219)/$B$9)</x:f>
-        <x:v>12.839322613362274</x:v>
+        <x:f>IF(B219&lt;=$B$7,-$B$8*LN(C219),-$B$9*LN(C219))</x:f>
+        <x:v>12.84189847773647</x:v>
       </x:c>
       <x:c r="F219" s="13"/>
       <x:c r="G219" s="13"/>
@@ -10369,11 +10661,12 @@
         <x:v>0.23522550787311047</x:v>
       </x:c>
       <x:c r="D220" s="10" t="n">
+        <x:f>IF(B220&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E220" s="11" t="n">
-        <x:f>IF(B220&lt;=$B$7,-LN(C220)/$B$8,-LN(C220)/$B$9)</x:f>
-        <x:v>6.171092016606696</x:v>
+        <x:f>IF(B220&lt;=$B$7,-$B$8*LN(C220),-$B$9*LN(C220))</x:f>
+        <x:v>6.172330080058651</x:v>
       </x:c>
       <x:c r="F220" s="13"/>
       <x:c r="G220" s="13"/>
@@ -10397,11 +10690,12 @@
         <x:v>0.943817850551568</x:v>
       </x:c>
       <x:c r="D221" s="10" t="n">
+        <x:f>IF(B221&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E221" s="11" t="n">
-        <x:f>IF(B221&lt;=$B$7,-LN(C221)/$B$8,-LN(C221)/$B$9)</x:f>
-        <x:v>3.8969327300110836</x:v>
+        <x:f>IF(B221&lt;=$B$7,-$B$8*LN(C221),-$B$9*LN(C221))</x:f>
+        <x:v>3.884617546256273</x:v>
       </x:c>
       <x:c r="F221" s="13"/>
       <x:c r="G221" s="13"/>
@@ -10425,11 +10719,12 @@
         <x:v>0.8463234481168911</x:v>
       </x:c>
       <x:c r="D222" s="10" t="n">
+        <x:f>IF(B222&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E222" s="11" t="n">
-        <x:f>IF(B222&lt;=$B$7,-LN(C222)/$B$8,-LN(C222)/$B$9)</x:f>
-        <x:v>0.7114854703943148</x:v>
+        <x:f>IF(B222&lt;=$B$7,-$B$8*LN(C222),-$B$9*LN(C222))</x:f>
+        <x:v>0.7116282107966815</x:v>
       </x:c>
       <x:c r="F222" s="13"/>
       <x:c r="G222" s="13"/>
@@ -10453,11 +10748,12 @@
         <x:v>0.25069509202148765</x:v>
       </x:c>
       <x:c r="D223" s="10" t="n">
+        <x:f>IF(B223&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E223" s="11" t="n">
-        <x:f>IF(B223&lt;=$B$7,-LN(C223)/$B$8,-LN(C223)/$B$9)</x:f>
-        <x:v>5.899497879252444</x:v>
+        <x:f>IF(B223&lt;=$B$7,-$B$8*LN(C223),-$B$9*LN(C223))</x:f>
+        <x:v>5.900681454653611</x:v>
       </x:c>
       <x:c r="F223" s="13"/>
       <x:c r="G223" s="13"/>
@@ -10481,11 +10777,12 @@
         <x:v>0.2769738248316571</x:v>
       </x:c>
       <x:c r="D224" s="10" t="n">
+        <x:f>IF(B224&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E224" s="11" t="n">
-        <x:f>IF(B224&lt;=$B$7,-LN(C224)/$B$8,-LN(C224)/$B$9)</x:f>
-        <x:v>5.4744257637039695</x:v>
+        <x:f>IF(B224&lt;=$B$7,-$B$8*LN(C224),-$B$9*LN(C224))</x:f>
+        <x:v>5.475524059830529</x:v>
       </x:c>
       <x:c r="F224" s="13"/>
       <x:c r="G224" s="13"/>
@@ -10509,11 +10806,12 @@
         <x:v>0.46560536173637956</x:v>
       </x:c>
       <x:c r="D225" s="10" t="n">
+        <x:f>IF(B225&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E225" s="11" t="n">
-        <x:f>IF(B225&lt;=$B$7,-LN(C225)/$B$8,-LN(C225)/$B$9)</x:f>
-        <x:v>3.2595717369165977</x:v>
+        <x:f>IF(B225&lt;=$B$7,-$B$8*LN(C225),-$B$9*LN(C225))</x:f>
+        <x:v>3.2602256822192515</x:v>
       </x:c>
       <x:c r="F225" s="13"/>
       <x:c r="G225" s="13"/>
@@ -10537,11 +10835,12 @@
         <x:v>0.6512747005326673</x:v>
       </x:c>
       <x:c r="D226" s="10" t="n">
+        <x:f>IF(B226&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E226" s="11" t="n">
-        <x:f>IF(B226&lt;=$B$7,-LN(C226)/$B$8,-LN(C226)/$B$9)</x:f>
-        <x:v>1.8285596050012907</x:v>
+        <x:f>IF(B226&lt;=$B$7,-$B$8*LN(C226),-$B$9*LN(C226))</x:f>
+        <x:v>1.8289264562507261</x:v>
       </x:c>
       <x:c r="F226" s="13"/>
       <x:c r="G226" s="13"/>
@@ -10565,11 +10864,12 @@
         <x:v>0.19368958414997905</x:v>
       </x:c>
       <x:c r="D227" s="10" t="n">
+        <x:f>IF(B227&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E227" s="11" t="n">
-        <x:f>IF(B227&lt;=$B$7,-LN(C227)/$B$8,-LN(C227)/$B$9)</x:f>
-        <x:v>6.999560440941547</x:v>
+        <x:f>IF(B227&lt;=$B$7,-$B$8*LN(C227),-$B$9*LN(C227))</x:f>
+        <x:v>7.0009647142757245</x:v>
       </x:c>
       <x:c r="F227" s="13"/>
       <x:c r="G227" s="13"/>
@@ -10593,11 +10893,12 @@
         <x:v>0.3920950422761962</x:v>
       </x:c>
       <x:c r="D228" s="10" t="n">
+        <x:f>IF(B228&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E228" s="11" t="n">
-        <x:f>IF(B228&lt;=$B$7,-LN(C228)/$B$8,-LN(C228)/$B$9)</x:f>
-        <x:v>3.992294617591483</x:v>
+        <x:f>IF(B228&lt;=$B$7,-$B$8*LN(C228),-$B$9*LN(C228))</x:f>
+        <x:v>3.993095564011043</x:v>
       </x:c>
       <x:c r="F228" s="13"/>
       <x:c r="G228" s="13"/>
@@ -10621,11 +10922,12 @@
         <x:v>0.1847153011476621</x:v>
       </x:c>
       <x:c r="D229" s="10" t="n">
+        <x:f>IF(B229&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E229" s="11" t="n">
-        <x:f>IF(B229&lt;=$B$7,-LN(C229)/$B$8,-LN(C229)/$B$9)</x:f>
-        <x:v>7.2018552539856255</x:v>
+        <x:f>IF(B229&lt;=$B$7,-$B$8*LN(C229),-$B$9*LN(C229))</x:f>
+        <x:v>7.203300112327105</x:v>
       </x:c>
       <x:c r="F229" s="13"/>
       <x:c r="G229" s="13"/>
@@ -10649,11 +10951,12 @@
         <x:v>0.6102959130657837</x:v>
       </x:c>
       <x:c r="D230" s="10" t="n">
+        <x:f>IF(B230&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E230" s="11" t="n">
-        <x:f>IF(B230&lt;=$B$7,-LN(C230)/$B$8,-LN(C230)/$B$9)</x:f>
-        <x:v>2.105674984578049</x:v>
+        <x:f>IF(B230&lt;=$B$7,-$B$8*LN(C230),-$B$9*LN(C230))</x:f>
+        <x:v>2.1060974315668615</x:v>
       </x:c>
       <x:c r="F230" s="13"/>
       <x:c r="G230" s="13"/>
@@ -10677,11 +10980,12 @@
         <x:v>0.04895801970269531</x:v>
       </x:c>
       <x:c r="D231" s="10" t="n">
+        <x:f>IF(B231&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E231" s="11" t="n">
-        <x:f>IF(B231&lt;=$B$7,-LN(C231)/$B$8,-LN(C231)/$B$9)</x:f>
-        <x:v>12.86398908119394</x:v>
+        <x:f>IF(B231&lt;=$B$7,-$B$8*LN(C231),-$B$9*LN(C231))</x:f>
+        <x:v>12.866569894230745</x:v>
       </x:c>
       <x:c r="F231" s="13"/>
       <x:c r="G231" s="13"/>
@@ -10705,11 +11009,12 @@
         <x:v>0.5261782257584855</x:v>
       </x:c>
       <x:c r="D232" s="10" t="n">
+        <x:f>IF(B232&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E232" s="11" t="n">
-        <x:f>IF(B232&lt;=$B$7,-LN(C232)/$B$8,-LN(C232)/$B$9)</x:f>
-        <x:v>2.7380621050789493</x:v>
+        <x:f>IF(B232&lt;=$B$7,-$B$8*LN(C232),-$B$9*LN(C232))</x:f>
+        <x:v>2.7386114235160037</x:v>
       </x:c>
       <x:c r="F232" s="13"/>
       <x:c r="G232" s="13"/>
@@ -10733,11 +11038,12 @@
         <x:v>0.4193716220324859</x:v>
       </x:c>
       <x:c r="D233" s="10" t="n">
+        <x:f>IF(B233&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E233" s="11" t="n">
-        <x:f>IF(B233&lt;=$B$7,-LN(C233)/$B$8,-LN(C233)/$B$9)</x:f>
-        <x:v>3.7055183840092885</x:v>
+        <x:f>IF(B233&lt;=$B$7,-$B$8*LN(C233),-$B$9*LN(C233))</x:f>
+        <x:v>3.706261796499241</x:v>
       </x:c>
       <x:c r="F233" s="13"/>
       <x:c r="G233" s="13"/>
@@ -10761,11 +11067,12 @@
         <x:v>0.3137820594711229</x:v>
       </x:c>
       <x:c r="D234" s="10" t="n">
+        <x:f>IF(B234&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E234" s="11" t="n">
-        <x:f>IF(B234&lt;=$B$7,-LN(C234)/$B$8,-LN(C234)/$B$9)</x:f>
-        <x:v>4.942366316405406</x:v>
+        <x:f>IF(B234&lt;=$B$7,-$B$8*LN(C234),-$B$9*LN(C234))</x:f>
+        <x:v>4.943357869129955</x:v>
       </x:c>
       <x:c r="F234" s="13"/>
       <x:c r="G234" s="13"/>
@@ -10789,11 +11096,12 @@
         <x:v>0.5756728382548317</x:v>
       </x:c>
       <x:c r="D235" s="10" t="n">
+        <x:f>IF(B235&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E235" s="11" t="n">
-        <x:f>IF(B235&lt;=$B$7,-LN(C235)/$B$8,-LN(C235)/$B$9)</x:f>
-        <x:v>2.3547189899156273</x:v>
+        <x:f>IF(B235&lt;=$B$7,-$B$8*LN(C235),-$B$9*LN(C235))</x:f>
+        <x:v>2.355191400878419</x:v>
       </x:c>
       <x:c r="F235" s="13"/>
       <x:c r="G235" s="13"/>
@@ -10817,11 +11125,12 @@
         <x:v>0.008662538486532867</x:v>
       </x:c>
       <x:c r="D236" s="10" t="n">
+        <x:f>IF(B236&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E236" s="11" t="n">
-        <x:f>IF(B236&lt;=$B$7,-LN(C236)/$B$8,-LN(C236)/$B$9)</x:f>
-        <x:v>20.24926936453914</x:v>
+        <x:f>IF(B236&lt;=$B$7,-$B$8*LN(C236),-$B$9*LN(C236))</x:f>
+        <x:v>20.25333183521071</x:v>
       </x:c>
       <x:c r="F236" s="13"/>
       <x:c r="G236" s="13"/>
@@ -10845,11 +11154,12 @@
         <x:v>0.7959647815441713</x:v>
       </x:c>
       <x:c r="D237" s="10" t="n">
+        <x:f>IF(B237&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E237" s="11" t="n">
-        <x:f>IF(B237&lt;=$B$7,-LN(C237)/$B$8,-LN(C237)/$B$9)</x:f>
-        <x:v>0.9730755634295968</x:v>
+        <x:f>IF(B237&lt;=$B$7,-$B$8*LN(C237),-$B$9*LN(C237))</x:f>
+        <x:v>0.973270784840626</x:v>
       </x:c>
       <x:c r="F237" s="13"/>
       <x:c r="G237" s="13"/>
@@ -10873,11 +11183,12 @@
         <x:v>0.3697672736598179</x:v>
       </x:c>
       <x:c r="D238" s="10" t="n">
+        <x:f>IF(B238&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E238" s="11" t="n">
-        <x:f>IF(B238&lt;=$B$7,-LN(C238)/$B$8,-LN(C238)/$B$9)</x:f>
-        <x:v>4.242302379142515</x:v>
+        <x:f>IF(B238&lt;=$B$7,-$B$8*LN(C238),-$B$9*LN(C238))</x:f>
+        <x:v>4.243153482887789</x:v>
       </x:c>
       <x:c r="F238" s="13"/>
       <x:c r="G238" s="13"/>
@@ -10901,11 +11212,12 @@
         <x:v>0.9515245457878336</x:v>
       </x:c>
       <x:c r="D239" s="10" t="n">
+        <x:f>IF(B239&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E239" s="11" t="n">
-        <x:f>IF(B239&lt;=$B$7,-LN(C239)/$B$8,-LN(C239)/$B$9)</x:f>
-        <x:v>0.21188367302935837</x:v>
+        <x:f>IF(B239&lt;=$B$7,-$B$8*LN(C239),-$B$9*LN(C239))</x:f>
+        <x:v>0.21192618178322847</x:v>
       </x:c>
       <x:c r="F239" s="13"/>
       <x:c r="G239" s="13"/>
@@ -10929,11 +11241,12 @@
         <x:v>0.8360403663245961</x:v>
       </x:c>
       <x:c r="D240" s="10" t="n">
+        <x:f>IF(B240&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E240" s="11" t="n">
-        <x:f>IF(B240&lt;=$B$7,-LN(C240)/$B$8,-LN(C240)/$B$9)</x:f>
-        <x:v>0.7636132297820757</x:v>
+        <x:f>IF(B240&lt;=$B$7,-$B$8*LN(C240),-$B$9*LN(C240))</x:f>
+        <x:v>0.7637664282157853</x:v>
       </x:c>
       <x:c r="F240" s="13"/>
       <x:c r="G240" s="13"/>
@@ -10957,11 +11270,12 @@
         <x:v>0.11037986574228853</x:v>
       </x:c>
       <x:c r="D241" s="10" t="n">
+        <x:f>IF(B241&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E241" s="11" t="n">
-        <x:f>IF(B241&lt;=$B$7,-LN(C241)/$B$8,-LN(C241)/$B$9)</x:f>
-        <x:v>9.397403779139205</x:v>
+        <x:f>IF(B241&lt;=$B$7,-$B$8*LN(C241),-$B$9*LN(C241))</x:f>
+        <x:v>9.399289115175504</x:v>
       </x:c>
       <x:c r="F241" s="13"/>
       <x:c r="G241" s="13"/>
@@ -10985,11 +11299,12 @@
         <x:v>0.9683779746992514</x:v>
       </x:c>
       <x:c r="D242" s="10" t="n">
+        <x:f>IF(B242&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E242" s="11" t="n">
-        <x:f>IF(B242&lt;=$B$7,-LN(C242)/$B$8,-LN(C242)/$B$9)</x:f>
-        <x:v>0.13701838007735734</x:v>
+        <x:f>IF(B242&lt;=$B$7,-$B$8*LN(C242),-$B$9*LN(C242))</x:f>
+        <x:v>0.13704586912599953</x:v>
       </x:c>
       <x:c r="F242" s="13"/>
       <x:c r="G242" s="13"/>
@@ -11013,11 +11328,12 @@
         <x:v>0.16529983968939632</x:v>
       </x:c>
       <x:c r="D243" s="10" t="n">
+        <x:f>IF(B243&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E243" s="11" t="n">
-        <x:f>IF(B243&lt;=$B$7,-LN(C243)/$B$8,-LN(C243)/$B$9)</x:f>
-        <x:v>7.675406729646369</x:v>
+        <x:f>IF(B243&lt;=$B$7,-$B$8*LN(C243),-$B$9*LN(C243))</x:f>
+        <x:v>7.676946593340719</x:v>
       </x:c>
       <x:c r="F243" s="13"/>
       <x:c r="G243" s="13"/>
@@ -11041,11 +11357,12 @@
         <x:v>0.01756044279318303</x:v>
       </x:c>
       <x:c r="D244" s="10" t="n">
+        <x:f>IF(B244&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E244" s="11" t="n">
-        <x:f>IF(B244&lt;=$B$7,-LN(C244)/$B$8,-LN(C244)/$B$9)</x:f>
-        <x:v>272.4186899393175</x:v>
+        <x:f>IF(B244&lt;=$B$7,-$B$8*LN(C244),-$B$9*LN(C244))</x:f>
+        <x:v>271.5577856185909</x:v>
       </x:c>
       <x:c r="F244" s="13"/>
       <x:c r="G244" s="13"/>
@@ -11069,11 +11386,12 @@
         <x:v>0.751824714592658</x:v>
       </x:c>
       <x:c r="D245" s="10" t="n">
+        <x:f>IF(B245&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E245" s="11" t="n">
-        <x:f>IF(B245&lt;=$B$7,-LN(C245)/$B$8,-LN(C245)/$B$9)</x:f>
-        <x:v>1.216351496451575</x:v>
+        <x:f>IF(B245&lt;=$B$7,-$B$8*LN(C245),-$B$9*LN(C245))</x:f>
+        <x:v>1.216595524628182</x:v>
       </x:c>
       <x:c r="F245" s="13"/>
       <x:c r="G245" s="13"/>
@@ -11097,11 +11415,12 @@
         <x:v>0.5087859918130562</x:v>
       </x:c>
       <x:c r="D246" s="10" t="n">
+        <x:f>IF(B246&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E246" s="11" t="n">
-        <x:f>IF(B246&lt;=$B$7,-LN(C246)/$B$8,-LN(C246)/$B$9)</x:f>
-        <x:v>2.881390156867786</x:v>
+        <x:f>IF(B246&lt;=$B$7,-$B$8*LN(C246),-$B$9*LN(C246))</x:f>
+        <x:v>2.881968230219219</x:v>
       </x:c>
       <x:c r="F246" s="13"/>
       <x:c r="G246" s="13"/>
@@ -11125,11 +11444,12 @@
         <x:v>0.9719597337534651</x:v>
       </x:c>
       <x:c r="D247" s="10" t="n">
+        <x:f>IF(B247&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E247" s="11" t="n">
-        <x:f>IF(B247&lt;=$B$7,-LN(C247)/$B$8,-LN(C247)/$B$9)</x:f>
-        <x:v>0.12127565849552803</x:v>
+        <x:f>IF(B247&lt;=$B$7,-$B$8*LN(C247),-$B$9*LN(C247))</x:f>
+        <x:v>0.12129998919096914</x:v>
       </x:c>
       <x:c r="F247" s="13"/>
       <x:c r="G247" s="13"/>
@@ -11153,11 +11473,12 @@
         <x:v>0.9834309740690514</x:v>
       </x:c>
       <x:c r="D248" s="10" t="n">
+        <x:f>IF(B248&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E248" s="11" t="n">
-        <x:f>IF(B248&lt;=$B$7,-LN(C248)/$B$8,-LN(C248)/$B$9)</x:f>
-        <x:v>0.07124432352681778</x:v>
+        <x:f>IF(B248&lt;=$B$7,-$B$8*LN(C248),-$B$9*LN(C248))</x:f>
+        <x:v>0.07125861678202779</x:v>
       </x:c>
       <x:c r="F248" s="13"/>
       <x:c r="G248" s="13"/>
@@ -11181,11 +11502,12 @@
         <x:v>0.68915804696735</x:v>
       </x:c>
       <x:c r="D249" s="10" t="n">
+        <x:f>IF(B249&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E249" s="11" t="n">
-        <x:f>IF(B249&lt;=$B$7,-LN(C249)/$B$8,-LN(C249)/$B$9)</x:f>
-        <x:v>1.5874695733738393</x:v>
+        <x:f>IF(B249&lt;=$B$7,-$B$8*LN(C249),-$B$9*LN(C249))</x:f>
+        <x:v>1.5877880563999547</x:v>
       </x:c>
       <x:c r="F249" s="13"/>
       <x:c r="G249" s="13"/>
@@ -11209,11 +11531,12 @@
         <x:v>0.28866168938111514</x:v>
       </x:c>
       <x:c r="D250" s="10" t="n">
+        <x:f>IF(B250&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E250" s="11" t="n">
-        <x:f>IF(B250&lt;=$B$7,-LN(C250)/$B$8,-LN(C250)/$B$9)</x:f>
-        <x:v>5.298179223626401</x:v>
+        <x:f>IF(B250&lt;=$B$7,-$B$8*LN(C250),-$B$9*LN(C250))</x:f>
+        <x:v>5.2992421606302615</x:v>
       </x:c>
       <x:c r="F250" s="13"/>
       <x:c r="G250" s="13"/>
@@ -11237,11 +11560,12 @@
         <x:v>0.4102176831802353</x:v>
       </x:c>
       <x:c r="D251" s="10" t="n">
+        <x:f>IF(B251&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E251" s="11" t="n">
-        <x:f>IF(B251&lt;=$B$7,-LN(C251)/$B$8,-LN(C251)/$B$9)</x:f>
-        <x:v>3.799625565656846</x:v>
+        <x:f>IF(B251&lt;=$B$7,-$B$8*LN(C251),-$B$9*LN(C251))</x:f>
+        <x:v>3.800387858218891</x:v>
       </x:c>
       <x:c r="F251" s="13"/>
       <x:c r="G251" s="13"/>
@@ -11265,11 +11589,12 @@
         <x:v>0.05552276398520917</x:v>
       </x:c>
       <x:c r="D252" s="10" t="n">
+        <x:f>IF(B252&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E252" s="11" t="n">
-        <x:f>IF(B252&lt;=$B$7,-LN(C252)/$B$8,-LN(C252)/$B$9)</x:f>
-        <x:v>12.327434184369862</x:v>
+        <x:f>IF(B252&lt;=$B$7,-$B$8*LN(C252),-$B$9*LN(C252))</x:f>
+        <x:v>12.329907352113752</x:v>
       </x:c>
       <x:c r="F252" s="13"/>
       <x:c r="G252" s="13"/>
@@ -11293,11 +11618,12 @@
         <x:v>0.019717585644684732</x:v>
       </x:c>
       <x:c r="D253" s="10" t="n">
+        <x:f>IF(B253&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E253" s="11" t="n">
-        <x:f>IF(B253&lt;=$B$7,-LN(C253)/$B$8,-LN(C253)/$B$9)</x:f>
-        <x:v>16.742010455788993</x:v>
+        <x:f>IF(B253&lt;=$B$7,-$B$8*LN(C253),-$B$9*LN(C253))</x:f>
+        <x:v>16.74536928939604</x:v>
       </x:c>
       <x:c r="F253" s="13"/>
       <x:c r="G253" s="13"/>
@@ -11321,11 +11647,12 @@
         <x:v>0.25612709193956107</x:v>
       </x:c>
       <x:c r="D254" s="10" t="n">
+        <x:f>IF(B254&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E254" s="11" t="n">
-        <x:f>IF(B254&lt;=$B$7,-LN(C254)/$B$8,-LN(C254)/$B$9)</x:f>
-        <x:v>5.808090544358482</x:v>
+        <x:f>IF(B254&lt;=$B$7,-$B$8*LN(C254),-$B$9*LN(C254))</x:f>
+        <x:v>5.809255781339111</x:v>
       </x:c>
       <x:c r="F254" s="13"/>
       <x:c r="G254" s="13"/>
@@ -11349,11 +11676,12 @@
         <x:v>0.8826177095761523</x:v>
       </x:c>
       <x:c r="D255" s="10" t="n">
+        <x:f>IF(B255&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E255" s="11" t="n">
-        <x:f>IF(B255&lt;=$B$7,-LN(C255)/$B$8,-LN(C255)/$B$9)</x:f>
-        <x:v>0.532432374484301</x:v>
+        <x:f>IF(B255&lt;=$B$7,-$B$8*LN(C255),-$B$9*LN(C255))</x:f>
+        <x:v>0.5325391927041093</x:v>
       </x:c>
       <x:c r="F255" s="13"/>
       <x:c r="G255" s="13"/>
@@ -11377,11 +11705,12 @@
         <x:v>0.980572339030914</x:v>
       </x:c>
       <x:c r="D256" s="10" t="n">
+        <x:f>IF(B256&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E256" s="11" t="n">
-        <x:f>IF(B256&lt;=$B$7,-LN(C256)/$B$8,-LN(C256)/$B$9)</x:f>
-        <x:v>0.08365733283565994</x:v>
+        <x:f>IF(B256&lt;=$B$7,-$B$8*LN(C256),-$B$9*LN(C256))</x:f>
+        <x:v>0.08367411642695839</x:v>
       </x:c>
       <x:c r="F256" s="13"/>
       <x:c r="G256" s="13"/>
@@ -11405,11 +11734,12 @@
         <x:v>0.08064818230923265</x:v>
       </x:c>
       <x:c r="D257" s="10" t="n">
+        <x:f>IF(B257&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E257" s="11" t="n">
-        <x:f>IF(B257&lt;=$B$7,-LN(C257)/$B$8,-LN(C257)/$B$9)</x:f>
-        <x:v>10.735621513002998</x:v>
+        <x:f>IF(B257&lt;=$B$7,-$B$8*LN(C257),-$B$9*LN(C257))</x:f>
+        <x:v>10.737775326395102</x:v>
       </x:c>
       <x:c r="F257" s="13"/>
       <x:c r="G257" s="13"/>
@@ -11433,11 +11763,12 @@
         <x:v>0.8242090091807768</x:v>
       </x:c>
       <x:c r="D258" s="10" t="n">
+        <x:f>IF(B258&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E258" s="11" t="n">
-        <x:f>IF(B258&lt;=$B$7,-LN(C258)/$B$8,-LN(C258)/$B$9)</x:f>
-        <x:v>0.8243887756811645</x:v>
+        <x:f>IF(B258&lt;=$B$7,-$B$8*LN(C258),-$B$9*LN(C258))</x:f>
+        <x:v>0.8245541670917328</x:v>
       </x:c>
       <x:c r="F258" s="13"/>
       <x:c r="G258" s="13"/>
@@ -11461,11 +11792,12 @@
         <x:v>0.7981125259539112</x:v>
       </x:c>
       <x:c r="D259" s="10" t="n">
+        <x:f>IF(B259&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E259" s="11" t="n">
-        <x:f>IF(B259&lt;=$B$7,-LN(C259)/$B$8,-LN(C259)/$B$9)</x:f>
-        <x:v>0.961585200175647</x:v>
+        <x:f>IF(B259&lt;=$B$7,-$B$8*LN(C259),-$B$9*LN(C259))</x:f>
+        <x:v>0.9617781163546757</x:v>
       </x:c>
       <x:c r="F259" s="13"/>
       <x:c r="G259" s="13"/>
@@ -11489,11 +11821,12 @@
         <x:v>0.5258850733516738</x:v>
       </x:c>
       <x:c r="D260" s="10" t="n">
+        <x:f>IF(B260&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E260" s="11" t="n">
-        <x:f>IF(B260&lt;=$B$7,-LN(C260)/$B$8,-LN(C260)/$B$9)</x:f>
-        <x:v>2.740438463159151</x:v>
+        <x:f>IF(B260&lt;=$B$7,-$B$8*LN(C260),-$B$9*LN(C260))</x:f>
+        <x:v>2.740988258348469</x:v>
       </x:c>
       <x:c r="F260" s="13"/>
       <x:c r="G260" s="13"/>
@@ -11517,11 +11850,12 @@
         <x:v>0.12272994255181402</x:v>
       </x:c>
       <x:c r="D261" s="10" t="n">
+        <x:f>IF(B261&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E261" s="11" t="n">
-        <x:f>IF(B261&lt;=$B$7,-LN(C261)/$B$8,-LN(C261)/$B$9)</x:f>
-        <x:v>8.945156235531469</x:v>
+        <x:f>IF(B261&lt;=$B$7,-$B$8*LN(C261),-$B$9*LN(C261))</x:f>
+        <x:v>8.946950840275239</x:v>
       </x:c>
       <x:c r="F261" s="13"/>
       <x:c r="G261" s="13"/>
@@ -11545,11 +11879,12 @@
         <x:v>0.7477921609533951</x:v>
       </x:c>
       <x:c r="D262" s="10" t="n">
+        <x:f>IF(B262&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E262" s="11" t="n">
-        <x:f>IF(B262&lt;=$B$7,-LN(C262)/$B$8,-LN(C262)/$B$9)</x:f>
-        <x:v>1.239284511637106</x:v>
+        <x:f>IF(B262&lt;=$B$7,-$B$8*LN(C262),-$B$9*LN(C262))</x:f>
+        <x:v>1.239533140705722</x:v>
       </x:c>
       <x:c r="F262" s="13"/>
       <x:c r="G262" s="13"/>
@@ -11573,11 +11908,12 @@
         <x:v>0.7771416617324576</x:v>
       </x:c>
       <x:c r="D263" s="10" t="n">
+        <x:f>IF(B263&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E263" s="11" t="n">
-        <x:f>IF(B263&lt;=$B$7,-LN(C263)/$B$8,-LN(C263)/$B$9)</x:f>
-        <x:v>16.992535995389137</x:v>
+        <x:f>IF(B263&lt;=$B$7,-$B$8*LN(C263),-$B$9*LN(C263))</x:f>
+        <x:v>16.938835760424382</x:v>
       </x:c>
       <x:c r="F263" s="13"/>
       <x:c r="G263" s="13"/>
@@ -11601,11 +11937,12 @@
         <x:v>0.1375383137492463</x:v>
       </x:c>
       <x:c r="D264" s="10" t="n">
+        <x:f>IF(B264&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E264" s="11" t="n">
-        <x:f>IF(B264&lt;=$B$7,-LN(C264)/$B$8,-LN(C264)/$B$9)</x:f>
-        <x:v>133.70220996082955</x:v>
+        <x:f>IF(B264&lt;=$B$7,-$B$8*LN(C264),-$B$9*LN(C264))</x:f>
+        <x:v>133.2796809108895</x:v>
       </x:c>
       <x:c r="F264" s="13"/>
       <x:c r="G264" s="13"/>
@@ -11629,11 +11966,12 @@
         <x:v>0.5467063508694991</x:v>
       </x:c>
       <x:c r="D265" s="10" t="n">
+        <x:f>IF(B265&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E265" s="11" t="n">
-        <x:f>IF(B265&lt;=$B$7,-LN(C265)/$B$8,-LN(C265)/$B$9)</x:f>
-        <x:v>2.574866083336432</x:v>
+        <x:f>IF(B265&lt;=$B$7,-$B$8*LN(C265),-$B$9*LN(C265))</x:f>
+        <x:v>2.5753826608858965</x:v>
       </x:c>
       <x:c r="F265" s="13"/>
       <x:c r="G265" s="13"/>
@@ -11657,11 +11995,12 @@
         <x:v>0.06307230226229876</x:v>
       </x:c>
       <x:c r="D266" s="10" t="n">
+        <x:f>IF(B266&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E266" s="11" t="n">
-        <x:f>IF(B266&lt;=$B$7,-LN(C266)/$B$8,-LN(C266)/$B$9)</x:f>
-        <x:v>11.783806308018999</x:v>
+        <x:f>IF(B266&lt;=$B$7,-$B$8*LN(C266),-$B$9*LN(C266))</x:f>
+        <x:v>11.786170411467078</x:v>
       </x:c>
       <x:c r="F266" s="13"/>
       <x:c r="G266" s="13"/>
@@ -11685,11 +12024,12 @@
         <x:v>0.4192095877369866</x:v>
       </x:c>
       <x:c r="D267" s="10" t="n">
+        <x:f>IF(B267&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E267" s="11" t="n">
-        <x:f>IF(B267&lt;=$B$7,-LN(C267)/$B$8,-LN(C267)/$B$9)</x:f>
-        <x:v>3.7071662508005616</x:v>
+        <x:f>IF(B267&lt;=$B$7,-$B$8*LN(C267),-$B$9*LN(C267))</x:f>
+        <x:v>3.707909993890616</x:v>
       </x:c>
       <x:c r="F267" s="13"/>
       <x:c r="G267" s="13"/>
@@ -11713,11 +12053,12 @@
         <x:v>0.6610845046816394</x:v>
       </x:c>
       <x:c r="D268" s="10" t="n">
+        <x:f>IF(B268&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E268" s="11" t="n">
-        <x:f>IF(B268&lt;=$B$7,-LN(C268)/$B$8,-LN(C268)/$B$9)</x:f>
-        <x:v>1.7648102225847766</x:v>
+        <x:f>IF(B268&lt;=$B$7,-$B$8*LN(C268),-$B$9*LN(C268))</x:f>
+        <x:v>1.7651642842371291</x:v>
       </x:c>
       <x:c r="F268" s="13"/>
       <x:c r="G268" s="13"/>
@@ -11741,11 +12082,12 @@
         <x:v>0.7021123956656083</x:v>
       </x:c>
       <x:c r="D269" s="10" t="n">
+        <x:f>IF(B269&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E269" s="11" t="n">
-        <x:f>IF(B269&lt;=$B$7,-LN(C269)/$B$8,-LN(C269)/$B$9)</x:f>
-        <x:v>1.508059270310238</x:v>
+        <x:f>IF(B269&lt;=$B$7,-$B$8*LN(C269),-$B$9*LN(C269))</x:f>
+        <x:v>1.5083618217972243</x:v>
       </x:c>
       <x:c r="F269" s="13"/>
       <x:c r="G269" s="13"/>
@@ -11769,11 +12111,12 @@
         <x:v>0.08950934826862067</x:v>
       </x:c>
       <x:c r="D270" s="10" t="n">
+        <x:f>IF(B270&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E270" s="11" t="n">
-        <x:f>IF(B270&lt;=$B$7,-LN(C270)/$B$8,-LN(C270)/$B$9)</x:f>
-        <x:v>10.29109974887416</x:v>
+        <x:f>IF(B270&lt;=$B$7,-$B$8*LN(C270),-$B$9*LN(C270))</x:f>
+        <x:v>10.293164380943365</x:v>
       </x:c>
       <x:c r="F270" s="13"/>
       <x:c r="G270" s="13"/>
@@ -11797,11 +12140,12 @@
         <x:v>0.6329638411989436</x:v>
       </x:c>
       <x:c r="D271" s="10" t="n">
+        <x:f>IF(B271&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E271" s="11" t="n">
-        <x:f>IF(B271&lt;=$B$7,-LN(C271)/$B$8,-LN(C271)/$B$9)</x:f>
-        <x:v>1.9501649704573156</x:v>
+        <x:f>IF(B271&lt;=$B$7,-$B$8*LN(C271),-$B$9*LN(C271))</x:f>
+        <x:v>1.9505562185490162</x:v>
       </x:c>
       <x:c r="F271" s="13"/>
       <x:c r="G271" s="13"/>
@@ -11825,11 +12169,12 @@
         <x:v>0.12475431326311082</x:v>
       </x:c>
       <x:c r="D272" s="10" t="n">
+        <x:f>IF(B272&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E272" s="11" t="n">
-        <x:f>IF(B272&lt;=$B$7,-LN(C272)/$B$8,-LN(C272)/$B$9)</x:f>
-        <x:v>8.875395277862562</x:v>
+        <x:f>IF(B272&lt;=$B$7,-$B$8*LN(C272),-$B$9*LN(C272))</x:f>
+        <x:v>8.87717588694854</x:v>
       </x:c>
       <x:c r="F272" s="13"/>
       <x:c r="G272" s="13"/>
@@ -11853,11 +12198,12 @@
         <x:v>0.24860269424971193</x:v>
       </x:c>
       <x:c r="D273" s="10" t="n">
+        <x:f>IF(B273&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E273" s="11" t="n">
-        <x:f>IF(B273&lt;=$B$7,-LN(C273)/$B$8,-LN(C273)/$B$9)</x:f>
-        <x:v>5.935237293357709</x:v>
+        <x:f>IF(B273&lt;=$B$7,-$B$8*LN(C273),-$B$9*LN(C273))</x:f>
+        <x:v>5.936428038910005</x:v>
       </x:c>
       <x:c r="F273" s="13"/>
       <x:c r="G273" s="13"/>
@@ -11881,11 +12227,12 @@
         <x:v>0.4942804992897436</x:v>
       </x:c>
       <x:c r="D274" s="10" t="n">
+        <x:f>IF(B274&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E274" s="11" t="n">
-        <x:f>IF(B274&lt;=$B$7,-LN(C274)/$B$8,-LN(C274)/$B$9)</x:f>
-        <x:v>3.0047271372995494</x:v>
+        <x:f>IF(B274&lt;=$B$7,-$B$8*LN(C274),-$B$9*LN(C274))</x:f>
+        <x:v>3.0053299548951675</x:v>
       </x:c>
       <x:c r="F274" s="13"/>
       <x:c r="G274" s="13"/>
@@ -11909,11 +12256,12 @@
         <x:v>0.5287731507560238</x:v>
       </x:c>
       <x:c r="D275" s="10" t="n">
+        <x:f>IF(B275&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E275" s="11" t="n">
-        <x:f>IF(B275&lt;=$B$7,-LN(C275)/$B$8,-LN(C275)/$B$9)</x:f>
-        <x:v>2.717084615191658</x:v>
+        <x:f>IF(B275&lt;=$B$7,-$B$8*LN(C275),-$B$9*LN(C275))</x:f>
+        <x:v>2.717629725060201</x:v>
       </x:c>
       <x:c r="F275" s="13"/>
       <x:c r="G275" s="13"/>
@@ -11937,11 +12285,12 @@
         <x:v>0.5851597542641684</x:v>
       </x:c>
       <x:c r="D276" s="10" t="n">
+        <x:f>IF(B276&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E276" s="11" t="n">
-        <x:f>IF(B276&lt;=$B$7,-LN(C276)/$B$8,-LN(C276)/$B$9)</x:f>
-        <x:v>2.2850201724980974</x:v>
+        <x:f>IF(B276&lt;=$B$7,-$B$8*LN(C276),-$B$9*LN(C276))</x:f>
+        <x:v>2.2854786002698657</x:v>
       </x:c>
       <x:c r="F276" s="13"/>
       <x:c r="G276" s="13"/>
@@ -11965,11 +12314,12 @@
         <x:v>0.07977961783763021</x:v>
       </x:c>
       <x:c r="D277" s="10" t="n">
+        <x:f>IF(B277&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E277" s="11" t="n">
-        <x:f>IF(B277&lt;=$B$7,-LN(C277)/$B$8,-LN(C277)/$B$9)</x:f>
-        <x:v>10.781794391886486</x:v>
+        <x:f>IF(B277&lt;=$B$7,-$B$8*LN(C277),-$B$9*LN(C277))</x:f>
+        <x:v>10.783957468623498</x:v>
       </x:c>
       <x:c r="F277" s="13"/>
       <x:c r="G277" s="13"/>
@@ -11993,11 +12343,12 @@
         <x:v>0.4192333657993004</x:v>
       </x:c>
       <x:c r="D278" s="10" t="n">
+        <x:f>IF(B278&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E278" s="11" t="n">
-        <x:f>IF(B278&lt;=$B$7,-LN(C278)/$B$8,-LN(C278)/$B$9)</x:f>
-        <x:v>3.7069243912621297</x:v>
+        <x:f>IF(B278&lt;=$B$7,-$B$8*LN(C278),-$B$9*LN(C278))</x:f>
+        <x:v>3.7076680858295794</x:v>
       </x:c>
       <x:c r="F278" s="13"/>
       <x:c r="G278" s="13"/>
@@ -12021,11 +12372,12 @@
         <x:v>0.8738055614521727</x:v>
       </x:c>
       <x:c r="D279" s="10" t="n">
+        <x:f>IF(B279&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E279" s="11" t="n">
-        <x:f>IF(B279&lt;=$B$7,-LN(C279)/$B$8,-LN(C279)/$B$9)</x:f>
-        <x:v>0.5752198366400664</x:v>
+        <x:f>IF(B279&lt;=$B$7,-$B$8*LN(C279),-$B$9*LN(C279))</x:f>
+        <x:v>0.5753352390120724</x:v>
       </x:c>
       <x:c r="F279" s="13"/>
       <x:c r="G279" s="13"/>
@@ -12049,11 +12401,12 @@
         <x:v>0.03549731511157006</x:v>
       </x:c>
       <x:c r="D280" s="10" t="n">
+        <x:f>IF(B280&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E280" s="11" t="n">
-        <x:f>IF(B280&lt;=$B$7,-LN(C280)/$B$8,-LN(C280)/$B$9)</x:f>
-        <x:v>14.234932516381745</x:v>
+        <x:f>IF(B280&lt;=$B$7,-$B$8*LN(C280),-$B$9*LN(C280))</x:f>
+        <x:v>14.237788372305163</x:v>
       </x:c>
       <x:c r="F280" s="13"/>
       <x:c r="G280" s="13"/>
@@ -12077,11 +12430,12 @@
         <x:v>0.8095214165514335</x:v>
       </x:c>
       <x:c r="D281" s="10" t="n">
+        <x:f>IF(B281&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E281" s="11" t="n">
-        <x:f>IF(B281&lt;=$B$7,-LN(C281)/$B$8,-LN(C281)/$B$9)</x:f>
-        <x:v>0.9010617304616358</x:v>
+        <x:f>IF(B281&lt;=$B$7,-$B$8*LN(C281),-$B$9*LN(C281))</x:f>
+        <x:v>0.9012425042361053</x:v>
       </x:c>
       <x:c r="F281" s="13"/>
       <x:c r="G281" s="13"/>
@@ -12105,11 +12459,12 @@
         <x:v>0.6703390934271738</x:v>
       </x:c>
       <x:c r="D282" s="10" t="n">
+        <x:f>IF(B282&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E282" s="11" t="n">
-        <x:f>IF(B282&lt;=$B$7,-LN(C282)/$B$8,-LN(C282)/$B$9)</x:f>
-        <x:v>1.7055302291789032</x:v>
+        <x:f>IF(B282&lt;=$B$7,-$B$8*LN(C282),-$B$9*LN(C282))</x:f>
+        <x:v>1.705872397896736</x:v>
       </x:c>
       <x:c r="F282" s="13"/>
       <x:c r="G282" s="13"/>
@@ -12133,11 +12488,12 @@
         <x:v>0.10960655973758548</x:v>
       </x:c>
       <x:c r="D283" s="10" t="n">
+        <x:f>IF(B283&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E283" s="11" t="n">
-        <x:f>IF(B283&lt;=$B$7,-LN(C283)/$B$8,-LN(C283)/$B$9)</x:f>
-        <x:v>9.427382808416962</x:v>
+        <x:f>IF(B283&lt;=$B$7,-$B$8*LN(C283),-$B$9*LN(C283))</x:f>
+        <x:v>9.429274158938277</x:v>
       </x:c>
       <x:c r="F283" s="13"/>
       <x:c r="G283" s="13"/>
@@ -12161,11 +12517,12 @@
         <x:v>0.3762510808883235</x:v>
       </x:c>
       <x:c r="D284" s="10" t="n">
+        <x:f>IF(B284&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E284" s="11" t="n">
-        <x:f>IF(B284&lt;=$B$7,-LN(C284)/$B$8,-LN(C284)/$B$9)</x:f>
-        <x:v>4.168179582814076</x:v>
+        <x:f>IF(B284&lt;=$B$7,-$B$8*LN(C284),-$B$9*LN(C284))</x:f>
+        <x:v>4.169015815816077</x:v>
       </x:c>
       <x:c r="F284" s="13"/>
       <x:c r="G284" s="13"/>
@@ -12189,11 +12546,12 @@
         <x:v>0.8208103444194421</x:v>
       </x:c>
       <x:c r="D285" s="10" t="n">
+        <x:f>IF(B285&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E285" s="11" t="n">
-        <x:f>IF(B285&lt;=$B$7,-LN(C285)/$B$8,-LN(C285)/$B$9)</x:f>
-        <x:v>0.842008463632343</x:v>
+        <x:f>IF(B285&lt;=$B$7,-$B$8*LN(C285),-$B$9*LN(C285))</x:f>
+        <x:v>0.8421773899588756</x:v>
       </x:c>
       <x:c r="F285" s="13"/>
       <x:c r="G285" s="13"/>
@@ -12217,11 +12575,12 @@
         <x:v>0.9696454879594967</x:v>
       </x:c>
       <x:c r="D286" s="10" t="n">
+        <x:f>IF(B286&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E286" s="11" t="n">
-        <x:f>IF(B286&lt;=$B$7,-LN(C286)/$B$8,-LN(C286)/$B$9)</x:f>
-        <x:v>0.13144069717137732</x:v>
+        <x:f>IF(B286&lt;=$B$7,-$B$8*LN(C286),-$B$9*LN(C286))</x:f>
+        <x:v>0.13146706720812765</x:v>
       </x:c>
       <x:c r="F286" s="13"/>
       <x:c r="G286" s="13"/>
@@ -12245,11 +12604,12 @@
         <x:v>0.9321771984687075</x:v>
       </x:c>
       <x:c r="D287" s="10" t="n">
+        <x:f>IF(B287&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E287" s="11" t="n">
-        <x:f>IF(B287&lt;=$B$7,-LN(C287)/$B$8,-LN(C287)/$B$9)</x:f>
-        <x:v>0.2994797866585834</x:v>
+        <x:f>IF(B287&lt;=$B$7,-$B$8*LN(C287),-$B$9*LN(C287))</x:f>
+        <x:v>0.2995398692140636</x:v>
       </x:c>
       <x:c r="F287" s="13"/>
       <x:c r="G287" s="13"/>
@@ -12273,11 +12633,12 @@
         <x:v>0.44839585933368653</x:v>
       </x:c>
       <x:c r="D288" s="10" t="n">
+        <x:f>IF(B288&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E288" s="11" t="n">
-        <x:f>IF(B288&lt;=$B$7,-LN(C288)/$B$8,-LN(C288)/$B$9)</x:f>
-        <x:v>3.4201671531907922</x:v>
+        <x:f>IF(B288&lt;=$B$7,-$B$8*LN(C288),-$B$9*LN(C288))</x:f>
+        <x:v>3.420853317639572</x:v>
       </x:c>
       <x:c r="F288" s="13"/>
       <x:c r="G288" s="13"/>
@@ -12301,11 +12662,12 @@
         <x:v>0.8770607843762264</x:v>
       </x:c>
       <x:c r="D289" s="10" t="n">
+        <x:f>IF(B289&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E289" s="11" t="n">
-        <x:f>IF(B289&lt;=$B$7,-LN(C289)/$B$8,-LN(C289)/$B$9)</x:f>
-        <x:v>0.5593640235174678</x:v>
+        <x:f>IF(B289&lt;=$B$7,-$B$8*LN(C289),-$B$9*LN(C289))</x:f>
+        <x:v>0.5594762448475002</x:v>
       </x:c>
       <x:c r="F289" s="13"/>
       <x:c r="G289" s="13"/>
@@ -12329,11 +12691,12 @@
         <x:v>0.26973014033865184</x:v>
       </x:c>
       <x:c r="D290" s="10" t="n">
+        <x:f>IF(B290&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E290" s="11" t="n">
-        <x:f>IF(B290&lt;=$B$7,-LN(C290)/$B$8,-LN(C290)/$B$9)</x:f>
-        <x:v>5.587429550271898</x:v>
+        <x:f>IF(B290&lt;=$B$7,-$B$8*LN(C290),-$B$9*LN(C290))</x:f>
+        <x:v>5.588550517565523</x:v>
       </x:c>
       <x:c r="F290" s="13"/>
       <x:c r="G290" s="13"/>
@@ -12357,11 +12720,12 @@
         <x:v>0.43455222190823406</x:v>
       </x:c>
       <x:c r="D291" s="10" t="n">
+        <x:f>IF(B291&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E291" s="11" t="n">
-        <x:f>IF(B291&lt;=$B$7,-LN(C291)/$B$8,-LN(C291)/$B$9)</x:f>
-        <x:v>3.553891633272223</x:v>
+        <x:f>IF(B291&lt;=$B$7,-$B$8*LN(C291),-$B$9*LN(C291))</x:f>
+        <x:v>3.5546046259373014</x:v>
       </x:c>
       <x:c r="F291" s="13"/>
       <x:c r="G291" s="13"/>
@@ -12385,11 +12749,12 @@
         <x:v>0.129100305843167</x:v>
       </x:c>
       <x:c r="D292" s="10" t="n">
+        <x:f>IF(B292&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E292" s="11" t="n">
-        <x:f>IF(B292&lt;=$B$7,-LN(C292)/$B$8,-LN(C292)/$B$9)</x:f>
-        <x:v>8.729377201272186</x:v>
+        <x:f>IF(B292&lt;=$B$7,-$B$8*LN(C292),-$B$9*LN(C292))</x:f>
+        <x:v>8.731128515762741</x:v>
       </x:c>
       <x:c r="F292" s="13"/>
       <x:c r="G292" s="13"/>
@@ -12413,11 +12778,12 @@
         <x:v>0.29594737326260656</x:v>
       </x:c>
       <x:c r="D293" s="10" t="n">
+        <x:f>IF(B293&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E293" s="11" t="n">
-        <x:f>IF(B293&lt;=$B$7,-LN(C293)/$B$8,-LN(C293)/$B$9)</x:f>
-        <x:v>5.19189041391653</x:v>
+        <x:f>IF(B293&lt;=$B$7,-$B$8*LN(C293),-$B$9*LN(C293))</x:f>
+        <x:v>5.192932026932627</x:v>
       </x:c>
       <x:c r="F293" s="13"/>
       <x:c r="G293" s="13"/>
@@ -12441,11 +12807,12 @@
         <x:v>0.13065355166327208</x:v>
       </x:c>
       <x:c r="D294" s="10" t="n">
+        <x:f>IF(B294&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E294" s="11" t="n">
-        <x:f>IF(B294&lt;=$B$7,-LN(C294)/$B$8,-LN(C294)/$B$9)</x:f>
-        <x:v>8.678380317118286</x:v>
+        <x:f>IF(B294&lt;=$B$7,-$B$8*LN(C294),-$B$9*LN(C294))</x:f>
+        <x:v>8.680121400457162</x:v>
       </x:c>
       <x:c r="F294" s="13"/>
       <x:c r="G294" s="13"/>
@@ -12469,11 +12836,12 @@
         <x:v>0.8118781907251105</x:v>
       </x:c>
       <x:c r="D295" s="10" t="n">
+        <x:f>IF(B295&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E295" s="11" t="n">
-        <x:f>IF(B295&lt;=$B$7,-LN(C295)/$B$8,-LN(C295)/$B$9)</x:f>
-        <x:v>0.888665532854862</x:v>
+        <x:f>IF(B295&lt;=$B$7,-$B$8*LN(C295),-$B$9*LN(C295))</x:f>
+        <x:v>0.8888438196660583</x:v>
       </x:c>
       <x:c r="F295" s="13"/>
       <x:c r="G295" s="13"/>
@@ -12497,11 +12865,12 @@
         <x:v>0.4899300484685227</x:v>
       </x:c>
       <x:c r="D296" s="10" t="n">
+        <x:f>IF(B296&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E296" s="11" t="n">
-        <x:f>IF(B296&lt;=$B$7,-LN(C296)/$B$8,-LN(C296)/$B$9)</x:f>
-        <x:v>3.042424359981868</x:v>
+        <x:f>IF(B296&lt;=$B$7,-$B$8*LN(C296),-$B$9*LN(C296))</x:f>
+        <x:v>3.043034740510192</x:v>
       </x:c>
       <x:c r="F296" s="13"/>
       <x:c r="G296" s="13"/>
@@ -12525,11 +12894,12 @@
         <x:v>0.685733126825653</x:v>
       </x:c>
       <x:c r="D297" s="10" t="n">
+        <x:f>IF(B297&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E297" s="11" t="n">
-        <x:f>IF(B297&lt;=$B$7,-LN(C297)/$B$8,-LN(C297)/$B$9)</x:f>
-        <x:v>1.6087139162334703</x:v>
+        <x:f>IF(B297&lt;=$B$7,-$B$8*LN(C297),-$B$9*LN(C297))</x:f>
+        <x:v>1.609036661364961</x:v>
       </x:c>
       <x:c r="F297" s="13"/>
       <x:c r="G297" s="13"/>
@@ -12553,11 +12923,12 @@
         <x:v>0.15941225818824023</x:v>
       </x:c>
       <x:c r="D298" s="10" t="n">
+        <x:f>IF(B298&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E298" s="11" t="n">
-        <x:f>IF(B298&lt;=$B$7,-LN(C298)/$B$8,-LN(C298)/$B$9)</x:f>
-        <x:v>7.830055453250479</x:v>
+        <x:f>IF(B298&lt;=$B$7,-$B$8*LN(C298),-$B$9*LN(C298))</x:f>
+        <x:v>7.83162634304719</x:v>
       </x:c>
       <x:c r="F298" s="13"/>
       <x:c r="G298" s="13"/>
@@ -12581,11 +12952,12 @@
         <x:v>0.628991606994532</x:v>
       </x:c>
       <x:c r="D299" s="10" t="n">
+        <x:f>IF(B299&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E299" s="11" t="n">
-        <x:f>IF(B299&lt;=$B$7,-LN(C299)/$B$8,-LN(C299)/$B$9)</x:f>
-        <x:v>1.9770092984207204</x:v>
+        <x:f>IF(B299&lt;=$B$7,-$B$8*LN(C299),-$B$9*LN(C299))</x:f>
+        <x:v>1.9774059321040236</x:v>
       </x:c>
       <x:c r="F299" s="13"/>
       <x:c r="G299" s="13"/>
@@ -12609,11 +12981,12 @@
         <x:v>0.017550812917761505</x:v>
       </x:c>
       <x:c r="D300" s="10" t="n">
+        <x:f>IF(B300&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E300" s="11" t="n">
-        <x:f>IF(B300&lt;=$B$7,-LN(C300)/$B$8,-LN(C300)/$B$9)</x:f>
-        <x:v>17.23840038579976</x:v>
+        <x:f>IF(B300&lt;=$B$7,-$B$8*LN(C300),-$B$9*LN(C300))</x:f>
+        <x:v>17.2418588066806</x:v>
       </x:c>
       <x:c r="F300" s="13"/>
       <x:c r="G300" s="13"/>
@@ -12637,11 +13010,12 @@
         <x:v>0.24409756471868604</x:v>
       </x:c>
       <x:c r="D301" s="10" t="n">
+        <x:f>IF(B301&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E301" s="11" t="n">
-        <x:f>IF(B301&lt;=$B$7,-LN(C301)/$B$8,-LN(C301)/$B$9)</x:f>
-        <x:v>6.013219743034342</x:v>
+        <x:f>IF(B301&lt;=$B$7,-$B$8*LN(C301),-$B$9*LN(C301))</x:f>
+        <x:v>6.014426133665431</x:v>
       </x:c>
       <x:c r="F301" s="13"/>
       <x:c r="G301" s="13"/>
@@ -12665,11 +13039,12 @@
         <x:v>0.5118919563246891</x:v>
       </x:c>
       <x:c r="D302" s="10" t="n">
+        <x:f>IF(B302&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E302" s="11" t="n">
-        <x:f>IF(B302&lt;=$B$7,-LN(C302)/$B$8,-LN(C302)/$B$9)</x:f>
-        <x:v>2.855438243916828</x:v>
+        <x:f>IF(B302&lt;=$B$7,-$B$8*LN(C302),-$B$9*LN(C302))</x:f>
+        <x:v>2.856011110715702</x:v>
       </x:c>
       <x:c r="F302" s="13"/>
       <x:c r="G302" s="13"/>
@@ -12693,11 +13068,12 @@
         <x:v>0.6504970391979441</x:v>
       </x:c>
       <x:c r="D303" s="10" t="n">
+        <x:f>IF(B303&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E303" s="11" t="n">
-        <x:f>IF(B303&lt;=$B$7,-LN(C303)/$B$8,-LN(C303)/$B$9)</x:f>
-        <x:v>1.8336542742782578</x:v>
+        <x:f>IF(B303&lt;=$B$7,-$B$8*LN(C303),-$B$9*LN(C303))</x:f>
+        <x:v>1.834022147635906</x:v>
       </x:c>
       <x:c r="F303" s="13"/>
       <x:c r="G303" s="13"/>
@@ -12721,11 +13097,12 @@
         <x:v>0.8969315475551412</x:v>
       </x:c>
       <x:c r="D304" s="10" t="n">
+        <x:f>IF(B304&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E304" s="11" t="n">
-        <x:f>IF(B304&lt;=$B$7,-LN(C304)/$B$8,-LN(C304)/$B$9)</x:f>
-        <x:v>0.46383369942278313</x:v>
+        <x:f>IF(B304&lt;=$B$7,-$B$8*LN(C304),-$B$9*LN(C304))</x:f>
+        <x:v>0.4639267551655099</x:v>
       </x:c>
       <x:c r="F304" s="13"/>
       <x:c r="G304" s="13"/>
@@ -12749,11 +13126,12 @@
         <x:v>0.619464835501276</x:v>
       </x:c>
       <x:c r="D305" s="10" t="n">
+        <x:f>IF(B305&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E305" s="11" t="n">
-        <x:f>IF(B305&lt;=$B$7,-LN(C305)/$B$8,-LN(C305)/$B$9)</x:f>
-        <x:v>2.042088326957058</x:v>
+        <x:f>IF(B305&lt;=$B$7,-$B$8*LN(C305),-$B$9*LN(C305))</x:f>
+        <x:v>2.0424980169951366</x:v>
       </x:c>
       <x:c r="F305" s="13"/>
       <x:c r="G305" s="13"/>
@@ -12777,11 +13155,12 @@
         <x:v>0.4573206276400015</x:v>
       </x:c>
       <x:c r="D306" s="10" t="n">
+        <x:f>IF(B306&lt;=$B$7,1,2)</x:f>
         <x:v>2</x:v>
       </x:c>
       <x:c r="E306" s="11" t="n">
-        <x:f>IF(B306&lt;=$B$7,-LN(C306)/$B$8,-LN(C306)/$B$9)</x:f>
-        <x:v>52.72804152479681</x:v>
+        <x:f>IF(B306&lt;=$B$7,-$B$8*LN(C306),-$B$9*LN(C306))</x:f>
+        <x:v>52.56140905628938</x:v>
       </x:c>
       <x:c r="F306" s="13"/>
       <x:c r="G306" s="13"/>
@@ -12805,11 +13184,12 @@
         <x:v>0.23334524722304195</x:v>
       </x:c>
       <x:c r="D307" s="10" t="n">
+        <x:f>IF(B307&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E307" s="11" t="n">
-        <x:f>IF(B307&lt;=$B$7,-LN(C307)/$B$8,-LN(C307)/$B$9)</x:f>
-        <x:v>6.2053140244706</x:v>
+        <x:f>IF(B307&lt;=$B$7,-$B$8*LN(C307),-$B$9*LN(C307))</x:f>
+        <x:v>6.20655895364698</x:v>
       </x:c>
       <x:c r="F307" s="13"/>
       <x:c r="G307" s="13"/>
@@ -12833,11 +13213,12 @@
         <x:v>0.3570475484011695</x:v>
       </x:c>
       <x:c r="D308" s="10" t="n">
+        <x:f>IF(B308&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E308" s="11" t="n">
-        <x:f>IF(B308&lt;=$B$7,-LN(C308)/$B$8,-LN(C308)/$B$9)</x:f>
-        <x:v>4.3915675824175</x:v>
+        <x:f>IF(B308&lt;=$B$7,-$B$8*LN(C308),-$B$9*LN(C308))</x:f>
+        <x:v>4.392448632206735</x:v>
       </x:c>
       <x:c r="F308" s="13"/>
       <x:c r="G308" s="13"/>
@@ -12861,11 +13242,12 @@
         <x:v>0.33483184163924307</x:v>
       </x:c>
       <x:c r="D309" s="10" t="n">
+        <x:f>IF(B309&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E309" s="11" t="n">
-        <x:f>IF(B309&lt;=$B$7,-LN(C309)/$B$8,-LN(C309)/$B$9)</x:f>
-        <x:v>4.6654974186569405</x:v>
+        <x:f>IF(B309&lt;=$B$7,-$B$8*LN(C309),-$B$9*LN(C309))</x:f>
+        <x:v>4.666433425092055</x:v>
       </x:c>
       <x:c r="F309" s="13"/>
       <x:c r="G309" s="13"/>
@@ -12889,11 +13271,12 @@
         <x:v>0.005221663857810199</x:v>
       </x:c>
       <x:c r="D310" s="10" t="n">
+        <x:f>IF(B310&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E310" s="11" t="n">
-        <x:f>IF(B310&lt;=$B$7,-LN(C310)/$B$8,-LN(C310)/$B$9)</x:f>
-        <x:v>22.407735852551234</x:v>
+        <x:f>IF(B310&lt;=$B$7,-$B$8*LN(C310),-$B$9*LN(C310))</x:f>
+        <x:v>22.412231361405333</x:v>
       </x:c>
       <x:c r="F310" s="13"/>
       <x:c r="G310" s="13"/>
@@ -12917,11 +13300,12 @@
         <x:v>0.2819113073637709</x:v>
       </x:c>
       <x:c r="D311" s="10" t="n">
+        <x:f>IF(B311&lt;=$B$7,1,2)</x:f>
         <x:v>1</x:v>
       </x:c>
       <x:c r="E311" s="11" t="n">
-        <x:f>IF(B311&lt;=$B$7,-LN(C311)/$B$8,-LN(C311)/$B$9)</x:f>
-        <x:v>5.399080736710323</x:v>
+        <x:f>IF(B311&lt;=$B$7,-$B$8*LN(C311),-$B$9*LN(C311))</x:f>
+        <x:v>5.400163916885937</x:v>
       </x:c>
       <x:c r="F311" s="13"/>
       <x:c r="G311" s="13"/>
@@ -12936,7 +13320,7 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R111c082e205f439d"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R83021b64408448c6"/>
 </x:worksheet>
 </file>
 
@@ -18417,6 +18801,6 @@
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Ra7656558a01a4791"/>
+  <x:drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9951e9abe6104be0"/>
 </x:worksheet>
 </file>